--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -516,10 +516,10 @@
         <v>0.73964</v>
       </c>
       <c r="J2" t="n">
-        <v>6.81612</v>
+        <v>6.81613</v>
       </c>
       <c r="K2" t="n">
-        <v>2.86973</v>
+        <v>2.87895</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -559,10 +559,10 @@
         <v>0.59084</v>
       </c>
       <c r="J3" t="n">
-        <v>4.10206</v>
+        <v>4.1021</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5723</v>
+        <v>2.59393</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -602,10 +602,10 @@
         <v>0.73855</v>
       </c>
       <c r="J4" t="n">
-        <v>7.64427</v>
+        <v>7.64422</v>
       </c>
       <c r="K4" t="n">
-        <v>2.04896</v>
+        <v>2.06887</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -645,10 +645,10 @@
         <v>0.58997</v>
       </c>
       <c r="J5" t="n">
-        <v>0.78853</v>
+        <v>0.78852</v>
       </c>
       <c r="K5" t="n">
-        <v>1.83</v>
+        <v>1.84914</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -688,10 +688,10 @@
         <v>0.73855</v>
       </c>
       <c r="J6" t="n">
-        <v>1.84659</v>
+        <v>1.84658</v>
       </c>
       <c r="K6" t="n">
-        <v>1.70522</v>
+        <v>1.71065</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -731,10 +731,10 @@
         <v>0.88757</v>
       </c>
       <c r="J7" t="n">
-        <v>2.08452</v>
+        <v>2.08449</v>
       </c>
       <c r="K7" t="n">
-        <v>1.62355</v>
+        <v>1.64195</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>0.88757</v>
       </c>
       <c r="J8" t="n">
-        <v>4.63768</v>
+        <v>4.63764</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4588</v>
+        <v>1.4766</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0.73855</v>
       </c>
       <c r="J9" t="n">
-        <v>6.97373</v>
+        <v>6.97377</v>
       </c>
       <c r="K9" t="n">
-        <v>1.48372</v>
+        <v>1.50158</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -860,10 +860,10 @@
         <v>0.58997</v>
       </c>
       <c r="J10" t="n">
-        <v>7.98012</v>
+        <v>7.98008</v>
       </c>
       <c r="K10" t="n">
-        <v>0.99476</v>
+        <v>1.02416</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         <v>0.44183</v>
       </c>
       <c r="J11" t="n">
-        <v>5.82772</v>
+        <v>5.8278</v>
       </c>
       <c r="K11" t="n">
-        <v>0.77013</v>
+        <v>0.78565</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>0.44183</v>
       </c>
       <c r="J12" t="n">
-        <v>2.95028</v>
+        <v>2.9503</v>
       </c>
       <c r="K12" t="n">
-        <v>0.39063</v>
+        <v>0.41797</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         <v>0.29412</v>
       </c>
       <c r="J13" t="n">
-        <v>3.51151</v>
+        <v>3.51153</v>
       </c>
       <c r="K13" t="n">
-        <v>0.52117</v>
+        <v>0.54895</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         <v>0.14684</v>
       </c>
       <c r="J14" t="n">
-        <v>1.94712</v>
+        <v>1.94713</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2595</v>
+        <v>-0.23428</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         <v>0.29369</v>
       </c>
       <c r="J15" t="n">
-        <v>3.15426</v>
+        <v>3.15431</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.18191</v>
+        <v>-0.16943</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>0.14663</v>
       </c>
       <c r="J16" t="n">
-        <v>4.82055</v>
+        <v>4.82046</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.02615</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>5.38341</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.42974</v>
+        <v>-0.40491</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1204,10 +1204,10 @@
         <v>0.43988</v>
       </c>
       <c r="J18" t="n">
-        <v>4.36431</v>
+        <v>4.36429</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6628500000000001</v>
+        <v>-0.62581</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1247,10 +1247,10 @@
         <v>0.58651</v>
       </c>
       <c r="J19" t="n">
-        <v>3.86557</v>
+        <v>3.86553</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.96116</v>
+        <v>-0.93799</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1290,10 +1290,10 @@
         <v>0.73314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9769600000000001</v>
+        <v>0.97692</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.12694</v>
+        <v>-1.11732</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.18746</v>
+        <v>-1.18745</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.24208</v>
+        <v>-1.21983</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.91301</v>
+        <v>-2.91305</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.12753</v>
+        <v>-1.11775</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1419,10 +1419,10 @@
         <v>0.8797700000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.67758</v>
+        <v>-2.6775</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.23057</v>
+        <v>-1.20826</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1462,10 +1462,10 @@
         <v>0.73314</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.96165</v>
+        <v>-2.96163</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.98573</v>
+        <v>-0.97555</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1505,10 +1505,10 @@
         <v>0.73314</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.79348</v>
+        <v>-3.79345</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.8814</v>
+        <v>-0.87092</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         <v>0.73314</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.73927</v>
+        <v>-6.73928</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.57239</v>
+        <v>-0.56099</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         <v>0.43924</v>
       </c>
       <c r="J27" t="n">
-        <v>-7.32485</v>
+        <v>-7.32479</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.06509</v>
+        <v>-0.03916</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>0.43924</v>
       </c>
       <c r="J28" t="n">
-        <v>-7.12534</v>
+        <v>-7.1254</v>
       </c>
       <c r="K28" t="n">
-        <v>0.26076</v>
+        <v>0.26147</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-8.415520000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.95475</v>
+        <v>0.95738</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         <v>0.14599</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.85283</v>
+        <v>-7.85285</v>
       </c>
       <c r="K30" t="n">
-        <v>1.16446</v>
+        <v>1.16767</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1763,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.16306</v>
+        <v>-7.16309</v>
       </c>
       <c r="K31" t="n">
-        <v>1.27213</v>
+        <v>1.2888</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
         <v>-0.14556</v>
       </c>
       <c r="J32" t="n">
-        <v>-7.55988</v>
+        <v>-7.55994</v>
       </c>
       <c r="K32" t="n">
-        <v>1.297</v>
+        <v>1.32703</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1849,10 +1849,10 @@
         <v>-0.43605</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.48606</v>
+        <v>-8.48602</v>
       </c>
       <c r="K33" t="n">
-        <v>1.11359</v>
+        <v>1.1298</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         <v>-0.5814</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.68213</v>
+        <v>-7.68216</v>
       </c>
       <c r="K34" t="n">
-        <v>1.25836</v>
+        <v>1.27497</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         <v>-0.7267400000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.99352</v>
+        <v>-5.99345</v>
       </c>
       <c r="K35" t="n">
-        <v>1.32459</v>
+        <v>1.35455</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1978,10 +1978,10 @@
         <v>-0.43668</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.30626</v>
+        <v>-7.30623</v>
       </c>
       <c r="K36" t="n">
-        <v>1.04794</v>
+        <v>1.0771</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2021,10 +2021,10 @@
         <v>-0.58224</v>
       </c>
       <c r="J37" t="n">
-        <v>-7.43271</v>
+        <v>-7.4327</v>
       </c>
       <c r="K37" t="n">
-        <v>0.54923</v>
+        <v>0.56386</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>-3.37108</v>
       </c>
       <c r="K38" t="n">
-        <v>0.58877</v>
+        <v>0.61664</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2107,10 +2107,10 @@
         <v>-0.58309</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.19056</v>
+        <v>-2.19051</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.0521</v>
+        <v>-0.03918</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2150,10 +2150,10 @@
         <v>-0.58309</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.43976</v>
+        <v>-1.43983</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.14304</v>
+        <v>-0.11736</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>-0.49028</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.57002</v>
+        <v>-0.5456</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         <v>-1.02041</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8771600000000001</v>
+        <v>-0.87717</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.98293</v>
+        <v>-0.95967</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
         <v>-1.16618</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.88076</v>
+        <v>-0.88079</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.68635</v>
+        <v>-0.67515</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         <v>-1.16618</v>
       </c>
       <c r="J44" t="n">
-        <v>1.33263</v>
+        <v>1.3325</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.64666</v>
+        <v>-0.63537</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         <v>-1.0219</v>
       </c>
       <c r="J45" t="n">
-        <v>0.55989</v>
+        <v>0.55998</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.59601</v>
+        <v>-0.57158</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         <v>-0.87719</v>
       </c>
       <c r="J46" t="n">
-        <v>1.2863</v>
+        <v>1.28628</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.36246</v>
+        <v>-0.33744</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J47" t="n">
-        <v>0.98443</v>
+        <v>0.98446</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.2977</v>
+        <v>-0.28545</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2494,10 +2494,10 @@
         <v>-0.73099</v>
       </c>
       <c r="J48" t="n">
-        <v>2.60515</v>
+        <v>2.6052</v>
       </c>
       <c r="K48" t="n">
-        <v>0.46668</v>
+        <v>0.46784</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         <v>-0.58565</v>
       </c>
       <c r="J49" t="n">
-        <v>2.47553</v>
+        <v>2.47558</v>
       </c>
       <c r="K49" t="n">
-        <v>0.89739</v>
+        <v>0.92581</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2580,10 +2580,10 @@
         <v>-0.73206</v>
       </c>
       <c r="J50" t="n">
-        <v>1.36816</v>
+        <v>1.36814</v>
       </c>
       <c r="K50" t="n">
-        <v>1.00156</v>
+        <v>1.01708</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         <v>-0.58651</v>
       </c>
       <c r="J51" t="n">
-        <v>0.16892</v>
+        <v>0.16895</v>
       </c>
       <c r="K51" t="n">
-        <v>1.13385</v>
+        <v>1.14973</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         <v>-0.73314</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.72936</v>
+        <v>-0.72939</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9246</v>
+        <v>0.93995</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>-0.54606</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7557</v>
+        <v>0.77064</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         <v>-0.29455</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.36019</v>
+        <v>-0.36021</v>
       </c>
       <c r="K54" t="n">
-        <v>0.97962</v>
+        <v>1.00825</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -2795,10 +2795,10 @@
         <v>-0.14749</v>
       </c>
       <c r="J55" t="n">
-        <v>-1.19127</v>
+        <v>-1.19128</v>
       </c>
       <c r="K55" t="n">
-        <v>0.74325</v>
+        <v>0.77124</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         <v>-0.29499</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.05825</v>
+        <v>-2.05836</v>
       </c>
       <c r="K56" t="n">
-        <v>0.55975</v>
+        <v>0.58724</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -2881,10 +2881,10 @@
         <v>-0.44248</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.18502</v>
+        <v>-0.18493</v>
       </c>
       <c r="K57" t="n">
-        <v>0.43014</v>
+        <v>0.44421</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>-1.03702</v>
       </c>
       <c r="K58" t="n">
-        <v>0.22087</v>
+        <v>0.23441</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -2967,10 +2967,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.17943</v>
+        <v>-2.17944</v>
       </c>
       <c r="K59" t="n">
-        <v>0.07789</v>
+        <v>0.09109</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3010,10 +3010,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.12352</v>
+        <v>-1.12347</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.42581</v>
+        <v>-0.38805</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J61" t="n">
-        <v>-1.00908</v>
+        <v>-1.00905</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.42537</v>
+        <v>-0.41344</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>-0.75413</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.65679</v>
+        <v>-0.64541</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>1.25597</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.16753</v>
+        <v>-0.14208</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         <v>-0.14771</v>
       </c>
       <c r="J64" t="n">
-        <v>2.01069</v>
+        <v>2.01067</v>
       </c>
       <c r="K64" t="n">
-        <v>0.07742</v>
+        <v>0.10347</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0.7627</v>
+        <v>0.76272</v>
       </c>
       <c r="K65" t="n">
-        <v>0.21984</v>
+        <v>0.24627</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>1.11254</v>
       </c>
       <c r="K66" t="n">
-        <v>0.42685</v>
+        <v>0.44076</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
         <v>0.14771</v>
       </c>
       <c r="J67" t="n">
-        <v>2.19419</v>
+        <v>2.19418</v>
       </c>
       <c r="K67" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.70048</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3354,10 +3354,10 @@
         <v>0.29586</v>
       </c>
       <c r="J68" t="n">
-        <v>2.41858</v>
+        <v>2.4185</v>
       </c>
       <c r="K68" t="n">
-        <v>1.10032</v>
+        <v>1.1287</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3397,10 +3397,10 @@
         <v>0.44444</v>
       </c>
       <c r="J69" t="n">
-        <v>2.18365</v>
+        <v>2.18369</v>
       </c>
       <c r="K69" t="n">
-        <v>1.51849</v>
+        <v>1.53486</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         <v>0.44444</v>
       </c>
       <c r="J70" t="n">
-        <v>2.97353</v>
+        <v>2.97358</v>
       </c>
       <c r="K70" t="n">
-        <v>1.23153</v>
+        <v>1.26023</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3483,10 +3483,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>3.16062</v>
+        <v>3.16051</v>
       </c>
       <c r="K71" t="n">
-        <v>1.40096</v>
+        <v>1.43006</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         <v>0.89153</v>
       </c>
       <c r="J72" t="n">
-        <v>2.06426</v>
+        <v>2.0643</v>
       </c>
       <c r="K72" t="n">
-        <v>1.10146</v>
+        <v>1.10375</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
         <v>0.7418400000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>3.76244</v>
+        <v>3.76248</v>
       </c>
       <c r="K73" t="n">
-        <v>1.34628</v>
+        <v>1.37519</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.28817</v>
       </c>
       <c r="K74" t="n">
-        <v>1.41302</v>
+        <v>1.42913</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>1.56007</v>
       </c>
       <c r="K75" t="n">
-        <v>1.14883</v>
+        <v>1.16414</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>1.23793</v>
       </c>
       <c r="K76" t="n">
-        <v>1.17329</v>
+        <v>1.18863</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -3741,10 +3741,10 @@
         <v>0.14771</v>
       </c>
       <c r="J77" t="n">
-        <v>1.25013</v>
+        <v>1.25015</v>
       </c>
       <c r="K77" t="n">
-        <v>1.26452</v>
+        <v>1.29299</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>-0.04673</v>
       </c>
       <c r="K78" t="n">
-        <v>1.36528</v>
+        <v>1.381</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.37349</v>
+        <v>-1.37348</v>
       </c>
       <c r="K79" t="n">
-        <v>1.20838</v>
+        <v>1.22375</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -3870,10 +3870,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>-1.29681</v>
+        <v>-1.29686</v>
       </c>
       <c r="K80" t="n">
-        <v>0.87068</v>
+        <v>0.87235</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>-1.46387</v>
       </c>
       <c r="K81" t="n">
-        <v>1.18895</v>
+        <v>1.21701</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3956,10 +3956,10 @@
         <v>-0.29499</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.77298</v>
+        <v>-1.77293</v>
       </c>
       <c r="K82" t="n">
-        <v>1.47266</v>
+        <v>1.47549</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -3999,10 +3999,10 @@
         <v>-0.44183</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.09104</v>
+        <v>-1.09116</v>
       </c>
       <c r="K83" t="n">
-        <v>1.49674</v>
+        <v>1.51243</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         <v>-0.5891</v>
       </c>
       <c r="J84" t="n">
-        <v>-1.28654</v>
+        <v>-1.2865</v>
       </c>
       <c r="K84" t="n">
-        <v>2.08921</v>
+        <v>2.11919</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4085,10 +4085,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J85" t="n">
-        <v>-1.96698</v>
+        <v>-1.96697</v>
       </c>
       <c r="K85" t="n">
-        <v>1.76268</v>
+        <v>1.77886</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         <v>-0.73638</v>
       </c>
       <c r="J86" t="n">
-        <v>-1.70269</v>
+        <v>-1.70266</v>
       </c>
       <c r="K86" t="n">
-        <v>1.94299</v>
+        <v>1.97259</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>-1.2652</v>
       </c>
       <c r="K87" t="n">
-        <v>1.85043</v>
+        <v>1.86677</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4214,10 +4214,10 @@
         <v>-0.88365</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.99317</v>
+        <v>-0.99316</v>
       </c>
       <c r="K88" t="n">
-        <v>1.75863</v>
+        <v>1.77477</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4257,10 +4257,10 @@
         <v>-0.73746</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.57685</v>
+        <v>-0.57684</v>
       </c>
       <c r="K89" t="n">
-        <v>1.94954</v>
+        <v>1.95303</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4300,10 +4300,10 @@
         <v>-0.73746</v>
       </c>
       <c r="J90" t="n">
-        <v>0.14621</v>
+        <v>0.14623</v>
       </c>
       <c r="K90" t="n">
-        <v>1.58831</v>
+        <v>1.6168</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J91" t="n">
-        <v>0.38672</v>
+        <v>0.38673</v>
       </c>
       <c r="K91" t="n">
-        <v>1.575</v>
+        <v>1.59074</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         <v>-0.58997</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.28089</v>
+        <v>-0.28095</v>
       </c>
       <c r="K92" t="n">
-        <v>1.52323</v>
+        <v>1.55157</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4429,10 +4429,10 @@
         <v>-0.44313</v>
       </c>
       <c r="J93" t="n">
-        <v>-1.01726</v>
+        <v>-1.01727</v>
       </c>
       <c r="K93" t="n">
-        <v>1.30133</v>
+        <v>1.31629</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4472,10 +4472,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.34259</v>
+        <v>-1.34253</v>
       </c>
       <c r="K94" t="n">
-        <v>1.26199</v>
+        <v>1.28967</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4515,10 +4515,10 @@
         <v>-0.14793</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.92051</v>
+        <v>-1.92064</v>
       </c>
       <c r="K95" t="n">
-        <v>1.14696</v>
+        <v>1.16162</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4558,10 +4558,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.26394</v>
+        <v>-1.2639</v>
       </c>
       <c r="K96" t="n">
-        <v>1.18016</v>
+        <v>1.19482</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4601,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.95131</v>
+        <v>-1.95129</v>
       </c>
       <c r="K97" t="n">
-        <v>1.49366</v>
+        <v>1.52144</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.93977</v>
+        <v>-1.93974</v>
       </c>
       <c r="K98" t="n">
-        <v>1.54232</v>
+        <v>1.55759</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>-2.02241</v>
       </c>
       <c r="K99" t="n">
-        <v>1.86693</v>
+        <v>1.88277</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4730,10 +4730,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>-2.25762</v>
+        <v>-2.25761</v>
       </c>
       <c r="K100" t="n">
-        <v>2.25423</v>
+        <v>2.28328</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.59828</v>
+        <v>-1.59827</v>
       </c>
       <c r="K101" t="n">
-        <v>2.19973</v>
+        <v>2.22862</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>-1.14518</v>
       </c>
       <c r="K102" t="n">
-        <v>2.60163</v>
+        <v>2.60586</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>-0.72556</v>
       </c>
       <c r="K103" t="n">
-        <v>2.9261</v>
+        <v>2.95628</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -4902,10 +4902,10 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>-1.65099</v>
+        <v>-1.65101</v>
       </c>
       <c r="K104" t="n">
-        <v>3.16329</v>
+        <v>3.18096</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -4945,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.33989</v>
+        <v>-1.33991</v>
       </c>
       <c r="K105" t="n">
-        <v>3.35495</v>
+        <v>3.37289</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.70893</v>
+        <v>-1.70892</v>
       </c>
       <c r="K106" t="n">
-        <v>3.72632</v>
+        <v>3.74485</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J107" t="n">
-        <v>0.68673</v>
+        <v>0.68667</v>
       </c>
       <c r="K107" t="n">
-        <v>3.97508</v>
+        <v>3.99401</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5074,10 +5074,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J108" t="n">
-        <v>1.65399</v>
+        <v>1.65402</v>
       </c>
       <c r="K108" t="n">
-        <v>3.99553</v>
+        <v>4.01442</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5117,10 +5117,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>2.32126</v>
+        <v>2.32127</v>
       </c>
       <c r="K109" t="n">
-        <v>4.03166</v>
+        <v>4.05004</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5160,10 +5160,10 @@
         <v>0.14837</v>
       </c>
       <c r="J110" t="n">
-        <v>0.66954</v>
+        <v>0.66956</v>
       </c>
       <c r="K110" t="n">
-        <v>4.28501</v>
+        <v>4.30427</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>0.87769</v>
       </c>
       <c r="K111" t="n">
-        <v>3.78844</v>
+        <v>3.80683</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>1.75034</v>
       </c>
       <c r="K112" t="n">
-        <v>3.94366</v>
+        <v>3.96173</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>2.71015</v>
       </c>
       <c r="K113" t="n">
-        <v>3.97456</v>
+        <v>3.99265</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>2.88092</v>
       </c>
       <c r="K114" t="n">
-        <v>4.05949</v>
+        <v>4.07814</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>3.29156</v>
       </c>
       <c r="K115" t="n">
-        <v>3.97279</v>
+        <v>3.97859</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -5418,10 +5418,10 @@
         <v>-0.29674</v>
       </c>
       <c r="J116" t="n">
-        <v>3.94635</v>
+        <v>3.94634</v>
       </c>
       <c r="K116" t="n">
-        <v>4.06011</v>
+        <v>4.07816</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5461,10 +5461,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J117" t="n">
-        <v>3.91094</v>
+        <v>3.91093</v>
       </c>
       <c r="K117" t="n">
-        <v>3.78907</v>
+        <v>3.80665</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>-0.5934700000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>5.24191</v>
+        <v>5.24193</v>
       </c>
       <c r="K118" t="n">
-        <v>3.67656</v>
+        <v>3.6939</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5547,10 +5547,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J119" t="n">
-        <v>3.63185</v>
+        <v>3.6318</v>
       </c>
       <c r="K119" t="n">
-        <v>3.66731</v>
+        <v>3.68459</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         <v>-0.4451</v>
       </c>
       <c r="J120" t="n">
-        <v>1.8763</v>
+        <v>1.87632</v>
       </c>
       <c r="K120" t="n">
-        <v>3.32896</v>
+        <v>3.34568</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -5633,10 +5633,10 @@
         <v>-0.29674</v>
       </c>
       <c r="J121" t="n">
-        <v>1.44758</v>
+        <v>1.44759</v>
       </c>
       <c r="K121" t="n">
-        <v>3.1146</v>
+        <v>3.11868</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>3.30476</v>
       </c>
       <c r="K122" t="n">
-        <v>2.3209</v>
+        <v>2.33606</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5719,10 +5719,10 @@
         <v>-0.14815</v>
       </c>
       <c r="J123" t="n">
-        <v>3.27767</v>
+        <v>3.27766</v>
       </c>
       <c r="K123" t="n">
-        <v>2.66651</v>
+        <v>2.69404</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>2.21597</v>
       </c>
       <c r="K124" t="n">
-        <v>2.27407</v>
+        <v>2.28882</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
         <v>-0.2963</v>
       </c>
       <c r="J125" t="n">
-        <v>0.87879</v>
+        <v>0.87878</v>
       </c>
       <c r="K125" t="n">
-        <v>1.90543</v>
+        <v>1.91968</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>0.29782</v>
       </c>
       <c r="K126" t="n">
-        <v>1.59325</v>
+        <v>1.63069</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -5891,10 +5891,10 @@
         <v>-0.14859</v>
       </c>
       <c r="J127" t="n">
-        <v>-0.37753</v>
+        <v>-0.37752</v>
       </c>
       <c r="K127" t="n">
-        <v>1.44894</v>
+        <v>1.47437</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>-0.12895</v>
       </c>
       <c r="K128" t="n">
-        <v>1.46751</v>
+        <v>1.48105</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -5977,10 +5977,10 @@
         <v>-0.14903</v>
       </c>
       <c r="J129" t="n">
-        <v>0.65217</v>
+        <v>0.65218</v>
       </c>
       <c r="K129" t="n">
-        <v>0.98826</v>
+        <v>1.00116</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6020,10 +6020,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0.34646</v>
+        <v>0.34643</v>
       </c>
       <c r="K130" t="n">
-        <v>0.74169</v>
+        <v>0.76584</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         <v>-0.29806</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.46207</v>
+        <v>-6.46206</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.17341</v>
+        <v>-0.15048</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6106,10 +6106,10 @@
         <v>-0.59613</v>
       </c>
       <c r="J132" t="n">
-        <v>-7.12502</v>
+        <v>-7.12501</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.46189</v>
+        <v>-0.43936</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6149,10 +6149,10 @@
         <v>-0.89286</v>
       </c>
       <c r="J133" t="n">
-        <v>-7.87358</v>
+        <v>-7.87357</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.51879</v>
+        <v>-0.48482</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6192,10 +6192,10 @@
         <v>-1.3373</v>
       </c>
       <c r="J134" t="n">
-        <v>-7.89681</v>
+        <v>-7.89682</v>
       </c>
       <c r="K134" t="n">
-        <v>0.47448</v>
+        <v>0.50985</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6235,10 +6235,10 @@
         <v>-1.63205</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.86885</v>
+        <v>-7.86886</v>
       </c>
       <c r="K135" t="n">
-        <v>0.49636</v>
+        <v>0.50849</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6278,10 +6278,10 @@
         <v>-1.92878</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.13321</v>
+        <v>-7.13322</v>
       </c>
       <c r="K136" t="n">
-        <v>0.74885</v>
+        <v>0.76125</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>-6.80835</v>
       </c>
       <c r="K137" t="n">
-        <v>1.22345</v>
+        <v>1.23642</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>-6.60221</v>
       </c>
       <c r="K138" t="n">
-        <v>1.55673</v>
+        <v>1.56989</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>-5.48672</v>
       </c>
       <c r="K139" t="n">
-        <v>2.45335</v>
+        <v>2.46771</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6450,10 +6450,10 @@
         <v>-1.93741</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.03358</v>
+        <v>-5.03357</v>
       </c>
       <c r="K140" t="n">
-        <v>1.76768</v>
+        <v>1.79269</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -6493,10 +6493,10 @@
         <v>-1.79104</v>
       </c>
       <c r="J141" t="n">
-        <v>-5.26751</v>
+        <v>-5.26749</v>
       </c>
       <c r="K141" t="n">
-        <v>2.23348</v>
+        <v>2.25911</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
         <v>-1.9403</v>
       </c>
       <c r="J142" t="n">
-        <v>-5.50652</v>
+        <v>-5.50654</v>
       </c>
       <c r="K142" t="n">
-        <v>2.49626</v>
+        <v>2.51036</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         <v>-1.9432</v>
       </c>
       <c r="J143" t="n">
-        <v>-0.61922</v>
+        <v>-0.61918</v>
       </c>
       <c r="K143" t="n">
-        <v>3.43949</v>
+        <v>3.45467</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>1.44287</v>
       </c>
       <c r="K144" t="n">
-        <v>3.7703</v>
+        <v>3.78586</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>2.52602</v>
       </c>
       <c r="K145" t="n">
-        <v>4.05609</v>
+        <v>4.07145</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -6708,10 +6708,10 @@
         <v>-1.35542</v>
       </c>
       <c r="J146" t="n">
-        <v>3.65912</v>
+        <v>3.65909</v>
       </c>
       <c r="K146" t="n">
-        <v>3.80097</v>
+        <v>3.80447</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6751,10 +6751,10 @@
         <v>-1.20664</v>
       </c>
       <c r="J147" t="n">
-        <v>3.11969</v>
+        <v>3.11967</v>
       </c>
       <c r="K147" t="n">
-        <v>3.41144</v>
+        <v>3.43797</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         <v>-0.75643</v>
       </c>
       <c r="J148" t="n">
-        <v>2.80845</v>
+        <v>2.80844</v>
       </c>
       <c r="K148" t="n">
-        <v>2.98456</v>
+        <v>2.99908</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>2.05342</v>
       </c>
       <c r="K149" t="n">
-        <v>2.2805</v>
+        <v>2.30567</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>1.73332</v>
       </c>
       <c r="K150" t="n">
-        <v>2.11196</v>
+        <v>2.12524</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>0.23826</v>
       </c>
       <c r="K151" t="n">
-        <v>1.29286</v>
+        <v>1.31668</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6966,10 +6966,10 @@
         <v>-0.15198</v>
       </c>
       <c r="J152" t="n">
-        <v>0.67215</v>
+        <v>0.67216</v>
       </c>
       <c r="K152" t="n">
-        <v>1.68058</v>
+        <v>1.70467</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7009,10 +7009,10 @@
         <v>-0.30395</v>
       </c>
       <c r="J153" t="n">
-        <v>1.02748</v>
+        <v>1.02751</v>
       </c>
       <c r="K153" t="n">
-        <v>1.61036</v>
+        <v>1.63436</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7052,10 +7052,10 @@
         <v>-0.30441</v>
       </c>
       <c r="J154" t="n">
-        <v>1.09003</v>
+        <v>1.08997</v>
       </c>
       <c r="K154" t="n">
-        <v>1.7284</v>
+        <v>1.75242</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7095,10 +7095,10 @@
         <v>-0.30488</v>
       </c>
       <c r="J155" t="n">
-        <v>2.46873</v>
+        <v>2.46883</v>
       </c>
       <c r="K155" t="n">
-        <v>1.91446</v>
+        <v>1.93859</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7138,10 +7138,10 @@
         <v>-0.45732</v>
       </c>
       <c r="J156" t="n">
-        <v>1.92562</v>
+        <v>1.92559</v>
       </c>
       <c r="K156" t="n">
-        <v>1.9005</v>
+        <v>1.92458</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -7181,10 +7181,10 @@
         <v>-0.30534</v>
       </c>
       <c r="J157" t="n">
-        <v>2.43303</v>
+        <v>2.43304</v>
       </c>
       <c r="K157" t="n">
-        <v>1.8599</v>
+        <v>1.87249</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -7224,10 +7224,10 @@
         <v>-0.45802</v>
       </c>
       <c r="J158" t="n">
-        <v>1.33277</v>
+        <v>1.33274</v>
       </c>
       <c r="K158" t="n">
-        <v>2.05282</v>
+        <v>2.07685</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7267,10 +7267,10 @@
         <v>-0.61069</v>
       </c>
       <c r="J159" t="n">
-        <v>1.63254</v>
+        <v>1.63252</v>
       </c>
       <c r="K159" t="n">
-        <v>2.37699</v>
+        <v>2.40107</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -7310,10 +7310,10 @@
         <v>-0.9146300000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>1.61075</v>
+        <v>1.61073</v>
       </c>
       <c r="K160" t="n">
-        <v>2.75372</v>
+        <v>2.7784</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -7353,10 +7353,10 @@
         <v>-1.06545</v>
       </c>
       <c r="J161" t="n">
-        <v>2.49769</v>
+        <v>2.49768</v>
       </c>
       <c r="K161" t="n">
-        <v>3.45596</v>
+        <v>3.46982</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>3.27015</v>
       </c>
       <c r="K162" t="n">
-        <v>3.69176</v>
+        <v>3.71689</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>4.0691</v>
       </c>
       <c r="K163" t="n">
-        <v>3.70699</v>
+        <v>3.73209</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         <v>-1.36986</v>
       </c>
       <c r="J164" t="n">
-        <v>3.70528</v>
+        <v>3.70529</v>
       </c>
       <c r="K164" t="n">
-        <v>4.0599</v>
+        <v>4.0737</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7525,10 +7525,10 @@
         <v>-1.06707</v>
       </c>
       <c r="J165" t="n">
-        <v>2.92963</v>
+        <v>2.92964</v>
       </c>
       <c r="K165" t="n">
-        <v>3.9898</v>
+        <v>4.00355</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7568,10 +7568,10 @@
         <v>-0.91603</v>
       </c>
       <c r="J166" t="n">
-        <v>2.53473</v>
+        <v>2.53471</v>
       </c>
       <c r="K166" t="n">
-        <v>3.80627</v>
+        <v>3.83087</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -7611,10 +7611,10 @@
         <v>-0.76453</v>
       </c>
       <c r="J167" t="n">
-        <v>3.55962</v>
+        <v>3.55969</v>
       </c>
       <c r="K167" t="n">
-        <v>3.65813</v>
+        <v>3.67154</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>-0.45942</v>
       </c>
       <c r="J168" t="n">
-        <v>3.4745</v>
+        <v>3.47448</v>
       </c>
       <c r="K168" t="n">
-        <v>4.0373</v>
+        <v>4.06192</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>2.88883</v>
       </c>
       <c r="K169" t="n">
-        <v>3.70654</v>
+        <v>3.73085</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -7740,10 +7740,10 @@
         <v>-0.15337</v>
       </c>
       <c r="J170" t="n">
-        <v>2.8589</v>
+        <v>2.85888</v>
       </c>
       <c r="K170" t="n">
-        <v>3.21844</v>
+        <v>3.2423</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -7783,10 +7783,10 @@
         <v>0.15361</v>
       </c>
       <c r="J171" t="n">
-        <v>2.90655</v>
+        <v>2.90654</v>
       </c>
       <c r="K171" t="n">
-        <v>3.3742</v>
+        <v>3.38689</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
         <v>0.46154</v>
       </c>
       <c r="J172" t="n">
-        <v>3.1847</v>
+        <v>3.18469</v>
       </c>
       <c r="K172" t="n">
-        <v>3.24184</v>
+        <v>3.26557</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         <v>0.61538</v>
       </c>
       <c r="J173" t="n">
-        <v>2.86078</v>
+        <v>2.86077</v>
       </c>
       <c r="K173" t="n">
-        <v>3.51293</v>
+        <v>3.53677</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>2.58488</v>
       </c>
       <c r="K174" t="n">
-        <v>3.15282</v>
+        <v>3.16524</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>2.85953</v>
       </c>
       <c r="K175" t="n">
-        <v>3.16781</v>
+        <v>3.19092</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -7998,10 +7998,10 @@
         <v>1.54321</v>
       </c>
       <c r="J176" t="n">
-        <v>2.5597</v>
+        <v>2.55971</v>
       </c>
       <c r="K176" t="n">
-        <v>2.99542</v>
+        <v>3.00768</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8041,10 +8041,10 @@
         <v>1.69492</v>
       </c>
       <c r="J177" t="n">
-        <v>2.90967</v>
+        <v>2.90968</v>
       </c>
       <c r="K177" t="n">
-        <v>3.30385</v>
+        <v>3.32694</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8084,10 +8084,10 @@
         <v>1.69492</v>
       </c>
       <c r="J178" t="n">
-        <v>3.84692</v>
+        <v>3.8469</v>
       </c>
       <c r="K178" t="n">
-        <v>2.9865</v>
+        <v>2.99841</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -8127,10 +8127,10 @@
         <v>1.54083</v>
       </c>
       <c r="J179" t="n">
-        <v>2.44214</v>
+        <v>2.44219</v>
       </c>
       <c r="K179" t="n">
-        <v>2.80839</v>
+        <v>2.83109</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -8170,10 +8170,10 @@
         <v>1.38462</v>
       </c>
       <c r="J180" t="n">
-        <v>1.78549</v>
+        <v>1.78547</v>
       </c>
       <c r="K180" t="n">
-        <v>2.24612</v>
+        <v>2.25762</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -8213,10 +8213,10 @@
         <v>1.07527</v>
       </c>
       <c r="J181" t="n">
-        <v>1.81738</v>
+        <v>1.81739</v>
       </c>
       <c r="K181" t="n">
-        <v>2.8466</v>
+        <v>2.85835</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -8256,10 +8256,10 @@
         <v>1.07527</v>
       </c>
       <c r="J182" t="n">
-        <v>1.4518</v>
+        <v>1.45179</v>
       </c>
       <c r="K182" t="n">
-        <v>2.97061</v>
+        <v>2.9824</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -8299,10 +8299,10 @@
         <v>0.92025</v>
       </c>
       <c r="J183" t="n">
-        <v>1.7339</v>
+        <v>1.73389</v>
       </c>
       <c r="K183" t="n">
-        <v>2.61335</v>
+        <v>2.63545</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -8342,10 +8342,10 @@
         <v>0.7657</v>
       </c>
       <c r="J184" t="n">
-        <v>1.25115</v>
+        <v>1.25114</v>
       </c>
       <c r="K184" t="n">
-        <v>2.77371</v>
+        <v>2.79581</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>1.47674</v>
       </c>
       <c r="K185" t="n">
-        <v>1.97793</v>
+        <v>1.99958</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>1.51615</v>
       </c>
       <c r="K186" t="n">
-        <v>2.18318</v>
+        <v>2.20489</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -8471,10 +8471,10 @@
         <v>0.30441</v>
       </c>
       <c r="J187" t="n">
-        <v>1.01808</v>
+        <v>1.01809</v>
       </c>
       <c r="K187" t="n">
-        <v>2.32365</v>
+        <v>2.33475</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -8514,10 +8514,10 @@
         <v>0.15198</v>
       </c>
       <c r="J188" t="n">
-        <v>1.01257</v>
+        <v>1.01258</v>
       </c>
       <c r="K188" t="n">
-        <v>2.45291</v>
+        <v>2.47463</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -8557,10 +8557,10 @@
         <v>-0.15152</v>
       </c>
       <c r="J189" t="n">
-        <v>1.06062</v>
+        <v>1.06063</v>
       </c>
       <c r="K189" t="n">
-        <v>2.4038</v>
+        <v>2.42518</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>0.3828</v>
       </c>
       <c r="K190" t="n">
-        <v>2.87926</v>
+        <v>2.90079</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -8643,10 +8643,10 @@
         <v>0.15175</v>
       </c>
       <c r="J191" t="n">
-        <v>0.87202</v>
+        <v>0.87203</v>
       </c>
       <c r="K191" t="n">
-        <v>2.7626</v>
+        <v>2.78408</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -8686,10 +8686,10 @@
         <v>0.15175</v>
       </c>
       <c r="J192" t="n">
-        <v>1.49476</v>
+        <v>1.49477</v>
       </c>
       <c r="K192" t="n">
-        <v>3.08375</v>
+        <v>3.10533</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>1.2914</v>
       </c>
       <c r="K193" t="n">
-        <v>2.60379</v>
+        <v>2.6251</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -8772,10 +8772,10 @@
         <v>0.30395</v>
       </c>
       <c r="J194" t="n">
-        <v>1.42624</v>
+        <v>1.42623</v>
       </c>
       <c r="K194" t="n">
-        <v>2.30179</v>
+        <v>2.32296</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>0.91826</v>
       </c>
       <c r="K195" t="n">
-        <v>2.12744</v>
+        <v>2.14834</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>1.27211</v>
       </c>
       <c r="K196" t="n">
-        <v>1.87392</v>
+        <v>1.89467</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>0.67276</v>
       </c>
       <c r="K197" t="n">
-        <v>1.7354</v>
+        <v>1.75618</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>0.25473</v>
       </c>
       <c r="K198" t="n">
-        <v>1.90253</v>
+        <v>1.92327</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>1.03418</v>
       </c>
       <c r="K199" t="n">
-        <v>1.6322</v>
+        <v>1.65281</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>-0.23441</v>
       </c>
       <c r="K200" t="n">
-        <v>1.15163</v>
+        <v>1.17207</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>-0.20364</v>
       </c>
       <c r="K201" t="n">
-        <v>0.78582</v>
+        <v>0.79597</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -9116,10 +9116,10 @@
         <v>-1.36364</v>
       </c>
       <c r="J202" t="n">
-        <v>-0.6785</v>
+        <v>-0.67849</v>
       </c>
       <c r="K202" t="n">
-        <v>0.31096</v>
+        <v>0.32103</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>-0.9078000000000001</v>
       </c>
       <c r="K203" t="n">
-        <v>0.31096</v>
+        <v>0.33106</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>-1.06044</v>
       </c>
       <c r="K204" t="n">
-        <v>-0.23012</v>
+        <v>-0.21013</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>-0.9976699999999999</v>
       </c>
       <c r="K205" t="n">
-        <v>0.05995</v>
+        <v>0.07994</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -9288,10 +9288,10 @@
         <v>-0.90909</v>
       </c>
       <c r="J206" t="n">
-        <v>-0.33444</v>
+        <v>-0.33445</v>
       </c>
       <c r="K206" t="n">
-        <v>0.22</v>
+        <v>0.24002</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0.17909</v>
       </c>
       <c r="K207" t="n">
-        <v>0.38057</v>
+        <v>0.39059</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -9374,10 +9374,10 @@
         <v>-0.45593</v>
       </c>
       <c r="J208" t="n">
-        <v>-1.01098</v>
+        <v>-1.01099</v>
       </c>
       <c r="K208" t="n">
-        <v>0.04999</v>
+        <v>0.06998</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>-0.79054</v>
       </c>
       <c r="K209" t="n">
-        <v>0.22075</v>
+        <v>0.23078</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>-0.95639</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.53914</v>
+        <v>-0.52915</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>-3.18665</v>
       </c>
       <c r="K211" t="n">
-        <v>-1.28678</v>
+        <v>-1.26683</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>-3.2485</v>
       </c>
       <c r="K212" t="n">
-        <v>-1.56796</v>
+        <v>-1.54799</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>-4.50734</v>
       </c>
       <c r="K213" t="n">
-        <v>-1.63934</v>
+        <v>-1.61935</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>-5.04426</v>
       </c>
       <c r="K214" t="n">
-        <v>-2.39</v>
+        <v>-2.37</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>-6.30201</v>
       </c>
       <c r="K215" t="n">
-        <v>-3.11</v>
+        <v>-3.09969</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>-7.64505</v>
       </c>
       <c r="K216" t="n">
-        <v>-2.94826</v>
+        <v>-2.93793</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>-7.87262</v>
       </c>
       <c r="K217" t="n">
-        <v>-4.10384</v>
+        <v>-4.08347</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>-8.357839999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>-4.74955</v>
+        <v>-4.72912</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>-9.30087</v>
       </c>
       <c r="K219" t="n">
-        <v>-5.13818</v>
+        <v>-5.11772</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>-9.0524</v>
       </c>
       <c r="K220" t="n">
-        <v>-5.42566</v>
+        <v>-5.41459</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>-10.13408</v>
       </c>
       <c r="K221" t="n">
-        <v>-5.27633</v>
+        <v>-5.24577</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>-10.12126</v>
       </c>
       <c r="K222" t="n">
-        <v>-5.19976</v>
+        <v>-5.17916</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>-8.6998</v>
       </c>
       <c r="K223" t="n">
-        <v>-4.44624</v>
+        <v>-4.43524</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>-7.54172</v>
       </c>
       <c r="K224" t="n">
-        <v>-4.10917</v>
+        <v>-4.08805</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>-7.08652</v>
       </c>
       <c r="K225" t="n">
-        <v>-4.08537</v>
+        <v>-4.06421</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>-6.15609</v>
       </c>
       <c r="K226" t="n">
-        <v>-3.35007</v>
+        <v>-3.32889</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>-5.44009</v>
       </c>
       <c r="K227" t="n">
-        <v>-2.47704</v>
+        <v>-2.45589</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>-4.18288</v>
       </c>
       <c r="K228" t="n">
-        <v>-2.45919</v>
+        <v>-2.43802</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>-4.20568</v>
       </c>
       <c r="K229" t="n">
-        <v>-1.62432</v>
+        <v>-1.61341</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>-4.39814</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.57616</v>
+        <v>-0.55503</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -10363,10 +10363,10 @@
         <v>-1.39752</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.84335</v>
+        <v>-3.84336</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.1788</v>
+        <v>-0.15771</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>-3.5376</v>
       </c>
       <c r="K232" t="n">
-        <v>0.35922</v>
+        <v>0.38023</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -10449,10 +10449,10 @@
         <v>-1.09034</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.6379</v>
+        <v>-1.63789</v>
       </c>
       <c r="K233" t="n">
-        <v>0.85615</v>
+        <v>0.86635</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -10492,10 +10492,10 @@
         <v>-1.09204</v>
       </c>
       <c r="J234" t="n">
-        <v>-1.38236</v>
+        <v>-1.38235</v>
       </c>
       <c r="K234" t="n">
-        <v>1.22829</v>
+        <v>1.24907</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>-1.35605</v>
       </c>
       <c r="K235" t="n">
-        <v>1.33249</v>
+        <v>1.35321</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>-1.42166</v>
       </c>
       <c r="K236" t="n">
-        <v>1.57655</v>
+        <v>1.59704</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>-0.25822</v>
       </c>
       <c r="K237" t="n">
-        <v>1.79063</v>
+        <v>1.81106</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>0.24162</v>
       </c>
       <c r="K238" t="n">
-        <v>1.64299</v>
+        <v>1.66349</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>1.3296</v>
       </c>
       <c r="K239" t="n">
-        <v>1.84146</v>
+        <v>1.86184</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>1.6742</v>
       </c>
       <c r="K240" t="n">
-        <v>2.29873</v>
+        <v>2.31893</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>2.18738</v>
       </c>
       <c r="K241" t="n">
-        <v>2.09568</v>
+        <v>2.11595</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.69220750360216</v>
+        <v>11.68090719932215</v>
       </c>
       <c r="C242" t="n">
-        <v>11.37952974685452</v>
+        <v>11.3318132331983</v>
       </c>
       <c r="D242" t="n">
-        <v>10.10248406000553</v>
+        <v>10.10328109363019</v>
       </c>
       <c r="E242" t="n">
-        <v>7.275954246535954</v>
+        <v>7.275771662400277</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10836,10 +10836,10 @@
         <v>-0.31546</v>
       </c>
       <c r="J242" t="n">
-        <v>2.30585</v>
+        <v>2.30584</v>
       </c>
       <c r="K242" t="n">
-        <v>1.86492</v>
+        <v>1.885</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.21828150008466</v>
+        <v>12.21073280281228</v>
       </c>
       <c r="C243" t="n">
-        <v>12.44077231258514</v>
+        <v>12.40926470388992</v>
       </c>
       <c r="D243" t="n">
-        <v>7.715821957376612</v>
+        <v>7.717293596312369</v>
       </c>
       <c r="E243" t="n">
-        <v>9.006561309112037</v>
+        <v>9.006520143250118</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10882,7 +10882,7 @@
         <v>2.64201</v>
       </c>
       <c r="K243" t="n">
-        <v>2.27584</v>
+        <v>2.28517</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.869108752607797</v>
+        <v>3.873680974224403</v>
       </c>
       <c r="C244" t="n">
-        <v>7.185654520087748</v>
+        <v>7.187927437076924</v>
       </c>
       <c r="D244" t="n">
-        <v>6.067130674221533</v>
+        <v>6.067304321369793</v>
       </c>
       <c r="E244" t="n">
-        <v>8.726459483322158</v>
+        <v>8.726219241082966</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10925,7 +10925,7 @@
         <v>3.88705</v>
       </c>
       <c r="K244" t="n">
-        <v>2.16865</v>
+        <v>2.18855</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.886453187629058</v>
+        <v>3.88591955118085</v>
       </c>
       <c r="C245" t="n">
-        <v>7.407480124584631</v>
+        <v>7.411427942976867</v>
       </c>
       <c r="D245" t="n">
-        <v>4.895839255630818</v>
+        <v>4.895240332822581</v>
       </c>
       <c r="E245" t="n">
-        <v>8.558304970212971</v>
+        <v>8.559979368649362</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10968,7 +10968,7 @@
         <v>2.90178</v>
       </c>
       <c r="K245" t="n">
-        <v>1.85496</v>
+        <v>1.87493</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1483242555266884</v>
+        <v>0.1532861826856857</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.7069009704048668</v>
+        <v>-0.6828919657593135</v>
       </c>
       <c r="D246" t="n">
-        <v>1.936134532232092</v>
+        <v>1.935148213773696</v>
       </c>
       <c r="E246" t="n">
-        <v>9.480868656626097</v>
+        <v>9.481564238556327</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11008,10 +11008,10 @@
         <v>-0.47319</v>
       </c>
       <c r="J246" t="n">
-        <v>3.10554</v>
+        <v>3.10555</v>
       </c>
       <c r="K246" t="n">
-        <v>1.4749</v>
+        <v>1.49503</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.378358124149103</v>
+        <v>-0.3638146660678077</v>
       </c>
       <c r="C247" t="n">
-        <v>2.260721941177035</v>
+        <v>2.316925798545744</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.48480768431114</v>
+        <v>-1.485945253225873</v>
       </c>
       <c r="E247" t="n">
-        <v>9.120631494700216</v>
+        <v>9.120111413047404</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11051,10 +11051,10 @@
         <v>-0.31596</v>
       </c>
       <c r="J247" t="n">
-        <v>3.46133</v>
+        <v>3.46134</v>
       </c>
       <c r="K247" t="n">
-        <v>1.14799</v>
+        <v>1.16825</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -11070,16 +11070,16 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.551717075063563</v>
+        <v>-1.541412985089996</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.33020152509068</v>
+        <v>-2.302675731629356</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.072522082408358</v>
+        <v>-3.072449067066763</v>
       </c>
       <c r="E248" t="n">
-        <v>8.165937798509759</v>
+        <v>8.16528181146432</v>
       </c>
       <c r="F248" t="n">
         <v>4.402541385019254</v>
@@ -11097,7 +11097,7 @@
         <v>3.43695</v>
       </c>
       <c r="K248" t="n">
-        <v>1.36458</v>
+        <v>1.37414</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.485277978461053</v>
+        <v>1.480266607016767</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2460265408707141</v>
+        <v>-0.2312479805749779</v>
       </c>
       <c r="D249" t="n">
-        <v>2.477560411555579</v>
+        <v>2.478020887554067</v>
       </c>
       <c r="E249" t="n">
-        <v>7.168495651741957</v>
+        <v>7.167525944489195</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11140,7 +11140,7 @@
         <v>4.28892</v>
       </c>
       <c r="K249" t="n">
-        <v>1.23868</v>
+        <v>1.24831</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.86610274308874</v>
+        <v>4.857599815151104</v>
       </c>
       <c r="C250" t="n">
-        <v>4.688210250815361</v>
+        <v>4.6681628923539</v>
       </c>
       <c r="D250" t="n">
-        <v>6.276446577191619</v>
+        <v>6.277401962654205</v>
       </c>
       <c r="E250" t="n">
-        <v>8.298714951041063</v>
+        <v>8.2983422144417</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11183,7 +11183,7 @@
         <v>5.36402</v>
       </c>
       <c r="K250" t="n">
-        <v>1.60601</v>
+        <v>1.62585</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8693769520538464</v>
+        <v>0.8642423709991576</v>
       </c>
       <c r="C251" t="n">
-        <v>1.472939310836519</v>
+        <v>1.468253206631021</v>
       </c>
       <c r="D251" t="n">
-        <v>2.687916250751443</v>
+        <v>2.687932896377343</v>
       </c>
       <c r="E251" t="n">
-        <v>8.444346525231472</v>
+        <v>8.444116149118287</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11226,7 +11226,7 @@
         <v>4.69098</v>
       </c>
       <c r="K251" t="n">
-        <v>1.80817</v>
+        <v>1.81743</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.683982438244793</v>
+        <v>3.683160341395753</v>
       </c>
       <c r="C252" t="n">
-        <v>2.960633592110651</v>
+        <v>2.957114169548247</v>
       </c>
       <c r="D252" t="n">
-        <v>3.96728230081671</v>
+        <v>3.967268399521484</v>
       </c>
       <c r="E252" t="n">
-        <v>10.1878646582001</v>
+        <v>10.18943805476773</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11269,7 +11269,7 @@
         <v>4.78305</v>
       </c>
       <c r="K252" t="n">
-        <v>1.60505</v>
+        <v>1.62475</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.072988119024992</v>
+        <v>7.06945301752957</v>
       </c>
       <c r="C253" t="n">
-        <v>8.451458725532945</v>
+        <v>8.425329120105829</v>
       </c>
       <c r="D253" t="n">
-        <v>3.549130514941523</v>
+        <v>3.54998841021732</v>
       </c>
       <c r="E253" t="n">
-        <v>7.956220167520422</v>
+        <v>7.955371951717582</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11309,10 +11309,10 @@
         <v>-1.58228</v>
       </c>
       <c r="J253" t="n">
-        <v>4.94739</v>
+        <v>4.9474</v>
       </c>
       <c r="K253" t="n">
-        <v>2.47771</v>
+        <v>2.49689</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.412106024240916</v>
+        <v>7.407366300488616</v>
       </c>
       <c r="C254" t="n">
-        <v>7.314040375962416</v>
+        <v>7.305454473556572</v>
       </c>
       <c r="D254" t="n">
-        <v>5.648854472956399</v>
+        <v>5.650093057627426</v>
       </c>
       <c r="E254" t="n">
-        <v>8.18615754410661</v>
+        <v>8.186649137090573</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11352,10 +11352,10 @@
         <v>-1.89873</v>
       </c>
       <c r="J254" t="n">
-        <v>5.61767</v>
+        <v>5.61764</v>
       </c>
       <c r="K254" t="n">
-        <v>1.93422</v>
+        <v>1.94315</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.441126909574767</v>
+        <v>5.439755980259942</v>
       </c>
       <c r="C255" t="n">
-        <v>5.869088368262365</v>
+        <v>5.86674323561196</v>
       </c>
       <c r="D255" t="n">
-        <v>2.553048111304568</v>
+        <v>2.553078418150934</v>
       </c>
       <c r="E255" t="n">
-        <v>6.39502573682591</v>
+        <v>6.395400402807883</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11398,7 +11398,7 @@
         <v>5.94719</v>
       </c>
       <c r="K255" t="n">
-        <v>2.36942</v>
+        <v>2.38855</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.74643189644666</v>
+        <v>11.73978426487428</v>
       </c>
       <c r="C256" t="n">
-        <v>9.853377010146701</v>
+        <v>9.824114200518252</v>
       </c>
       <c r="D256" t="n">
-        <v>5.630939685062497</v>
+        <v>5.631449123740828</v>
       </c>
       <c r="E256" t="n">
-        <v>7.152924691632467</v>
+        <v>7.153732721814654</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11441,7 +11441,7 @@
         <v>5.6654</v>
       </c>
       <c r="K256" t="n">
-        <v>2.83359</v>
+        <v>2.84185</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.749669217530842</v>
+        <v>8.754365966609857</v>
       </c>
       <c r="C257" t="n">
-        <v>8.537167923018973</v>
+        <v>8.53559925646965</v>
       </c>
       <c r="D257" t="n">
-        <v>5.085995773470686</v>
+        <v>5.086253479206793</v>
       </c>
       <c r="E257" t="n">
-        <v>7.46721375948256</v>
+        <v>7.466457257460601</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11484,7 +11484,7 @@
         <v>6.14174</v>
       </c>
       <c r="K257" t="n">
-        <v>2.89124</v>
+        <v>2.90973</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.9007218430143</v>
+        <v>11.90156908493525</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74883648667469</v>
+        <v>11.74851831464241</v>
       </c>
       <c r="D258" t="n">
-        <v>8.753724867145207</v>
+        <v>8.754092251403932</v>
       </c>
       <c r="E258" t="n">
-        <v>7.925921027489435</v>
+        <v>7.926013622677064</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11524,10 +11524,10 @@
         <v>-2.85261</v>
       </c>
       <c r="J258" t="n">
-        <v>6.59555</v>
+        <v>6.59556</v>
       </c>
       <c r="K258" t="n">
-        <v>3.82435</v>
+        <v>3.84219</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.4780960159121</v>
+        <v>11.47480686580518</v>
       </c>
       <c r="C259" t="n">
-        <v>9.103049876326065</v>
+        <v>9.094922207882083</v>
       </c>
       <c r="D259" t="n">
-        <v>7.807605668015549</v>
+        <v>7.807816342267415</v>
       </c>
       <c r="E259" t="n">
-        <v>8.253447040871787</v>
+        <v>8.253994766143569</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11570,7 +11570,7 @@
         <v>6.63022</v>
       </c>
       <c r="K259" t="n">
-        <v>3.96203</v>
+        <v>3.97979</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.837994801251735</v>
+        <v>8.844225206517887</v>
       </c>
       <c r="C260" t="n">
-        <v>9.287031526038202</v>
+        <v>9.295815823383791</v>
       </c>
       <c r="D260" t="n">
-        <v>8.123853407908598</v>
+        <v>8.123120495041869</v>
       </c>
       <c r="E260" t="n">
-        <v>8.655654236852307</v>
+        <v>8.656392302274263</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11610,10 +11610,10 @@
         <v>-3.01587</v>
       </c>
       <c r="J260" t="n">
-        <v>6.90759</v>
+        <v>6.9076</v>
       </c>
       <c r="K260" t="n">
-        <v>4.3161</v>
+        <v>4.34381</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.53917755446974</v>
+        <v>12.53996053805857</v>
       </c>
       <c r="C261" t="n">
-        <v>10.31255993483846</v>
+        <v>10.30734806766995</v>
       </c>
       <c r="D261" t="n">
-        <v>5.616639458252171</v>
+        <v>5.616713620101832</v>
       </c>
       <c r="E261" t="n">
-        <v>10.3932291454456</v>
+        <v>10.39434974573929</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11653,10 +11653,10 @@
         <v>-3.02067</v>
       </c>
       <c r="J261" t="n">
-        <v>5.46905</v>
+        <v>5.46906</v>
       </c>
       <c r="K261" t="n">
-        <v>5.05861</v>
+        <v>5.08579</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.770365433449976</v>
+        <v>6.772424333664695</v>
       </c>
       <c r="C262" t="n">
-        <v>6.464234483440801</v>
+        <v>6.466904613596713</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.7639897509881699</v>
+        <v>-0.7646328559841487</v>
       </c>
       <c r="E262" t="n">
-        <v>8.715990667029549</v>
+        <v>8.715874651411282</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11696,10 +11696,10 @@
         <v>-2.86624</v>
       </c>
       <c r="J262" t="n">
-        <v>4.06078</v>
+        <v>4.06079</v>
       </c>
       <c r="K262" t="n">
-        <v>5.30637</v>
+        <v>5.31228</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.08630073425385</v>
+        <v>9.086825540356624</v>
       </c>
       <c r="C263" t="n">
-        <v>7.431164902822429</v>
+        <v>7.429461707157436</v>
       </c>
       <c r="D263" t="n">
-        <v>3.205367881565269</v>
+        <v>3.204845943068424</v>
       </c>
       <c r="E263" t="n">
-        <v>8.726665524341847</v>
+        <v>8.725891307995104</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11739,10 +11739,10 @@
         <v>-2.55591</v>
       </c>
       <c r="J263" t="n">
-        <v>3.9794</v>
+        <v>3.97938</v>
       </c>
       <c r="K263" t="n">
-        <v>4.74635</v>
+        <v>4.77356</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.49034211175042</v>
+        <v>13.48609143894739</v>
       </c>
       <c r="C264" t="n">
-        <v>11.26870338485211</v>
+        <v>11.25205955323327</v>
       </c>
       <c r="D264" t="n">
-        <v>4.643596545334217</v>
+        <v>4.643646638323262</v>
       </c>
       <c r="E264" t="n">
-        <v>6.334572943777483</v>
+        <v>6.332360751454247</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11785,7 +11785,7 @@
         <v>3.80671</v>
       </c>
       <c r="K264" t="n">
-        <v>5.32002</v>
+        <v>5.34623</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.077932531474708</v>
+        <v>8.076507004215493</v>
       </c>
       <c r="C265" t="n">
-        <v>5.795294900484493</v>
+        <v>5.793623313710539</v>
       </c>
       <c r="D265" t="n">
-        <v>2.716209217577692</v>
+        <v>2.715930781201892</v>
       </c>
       <c r="E265" t="n">
-        <v>7.364577496359859</v>
+        <v>7.363186389467602</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11828,7 +11828,7 @@
         <v>3.70125</v>
       </c>
       <c r="K265" t="n">
-        <v>4.57258</v>
+        <v>4.5891</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.555977755923022</v>
+        <v>2.556256505892263</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2322868915642484</v>
+        <v>-0.2139824722959038</v>
       </c>
       <c r="D266" t="n">
-        <v>2.17167324648988</v>
+        <v>2.17198178175162</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01018105609832</v>
+        <v>12.01074068525536</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11868,10 +11868,10 @@
         <v>-2.09677</v>
       </c>
       <c r="J266" t="n">
-        <v>2.88289</v>
+        <v>2.88285</v>
       </c>
       <c r="K266" t="n">
-        <v>4.69812</v>
+        <v>4.72473</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.065626699967529</v>
+        <v>5.068583232782187</v>
       </c>
       <c r="C267" t="n">
-        <v>1.653834638968643</v>
+        <v>1.67405104307814</v>
       </c>
       <c r="D267" t="n">
-        <v>3.455509139739354</v>
+        <v>3.455574794517191</v>
       </c>
       <c r="E267" t="n">
-        <v>13.52734150028705</v>
+        <v>13.52823197301927</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11914,7 +11914,7 @@
         <v>2.68754</v>
       </c>
       <c r="K267" t="n">
-        <v>4.52853</v>
+        <v>4.55505</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.848746210422573</v>
+        <v>5.845067646233892</v>
       </c>
       <c r="C268" t="n">
-        <v>3.423865668603554</v>
+        <v>3.418202156246997</v>
       </c>
       <c r="D268" t="n">
-        <v>0.8995441150669414</v>
+        <v>0.8997297575554342</v>
       </c>
       <c r="E268" t="n">
-        <v>15.10117350187177</v>
+        <v>15.10205865561842</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11957,7 +11957,7 @@
         <v>2.18414</v>
       </c>
       <c r="K268" t="n">
-        <v>4.7495</v>
+        <v>4.77573</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.33485816100758</v>
+        <v>2.33927506308429</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7169380817873883</v>
+        <v>0.7288508665144633</v>
       </c>
       <c r="D269" t="n">
-        <v>2.934736080325595</v>
+        <v>2.934988295179086</v>
       </c>
       <c r="E269" t="n">
-        <v>10.14448565384847</v>
+        <v>10.14349311026617</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12000,7 +12000,7 @@
         <v>2.61229</v>
       </c>
       <c r="K269" t="n">
-        <v>4.45</v>
+        <v>4.46598</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.662988895347285</v>
+        <v>2.66094177937819</v>
       </c>
       <c r="C270" t="n">
-        <v>0.341073842771622</v>
+        <v>0.3396648971739413</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.54245463593311</v>
+        <v>-1.542067343565623</v>
       </c>
       <c r="E270" t="n">
-        <v>11.78258580085492</v>
+        <v>11.78201516927002</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12040,10 +12040,10 @@
         <v>-1.14192</v>
       </c>
       <c r="J270" t="n">
-        <v>2.24572</v>
+        <v>2.24574</v>
       </c>
       <c r="K270" t="n">
-        <v>4.21962</v>
+        <v>4.23569</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.16840499788147</v>
+        <v>4.161722738120677</v>
       </c>
       <c r="C271" t="n">
-        <v>3.282017734817666</v>
+        <v>3.262635211183862</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.202331243572408</v>
+        <v>-1.201865723001461</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72378815957738</v>
+        <v>12.72401434568446</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12083,10 +12083,10 @@
         <v>-0.81699</v>
       </c>
       <c r="J271" t="n">
-        <v>2.03143</v>
+        <v>2.03146</v>
       </c>
       <c r="K271" t="n">
-        <v>4.27749</v>
+        <v>4.30342</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.854677332495338</v>
+        <v>3.855793088559722</v>
       </c>
       <c r="C272" t="n">
-        <v>2.839375581890669</v>
+        <v>2.830105124392079</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.902864280012218</v>
+        <v>-2.903159161760305</v>
       </c>
       <c r="E272" t="n">
-        <v>12.48863918197256</v>
+        <v>12.48945518346805</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12126,10 +12126,10 @@
         <v>-0.491</v>
       </c>
       <c r="J272" t="n">
-        <v>2.06697</v>
+        <v>2.06698</v>
       </c>
       <c r="K272" t="n">
-        <v>3.82228</v>
+        <v>3.8382</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.054865128600913</v>
+        <v>2.056384974819991</v>
       </c>
       <c r="C273" t="n">
-        <v>2.708189425091678</v>
+        <v>2.697177512147775</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1045298480682244</v>
+        <v>-0.1046646738985912</v>
       </c>
       <c r="E273" t="n">
-        <v>12.1488155961837</v>
+        <v>12.15007242674164</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12172,7 +12172,7 @@
         <v>2.86969</v>
       </c>
       <c r="K273" t="n">
-        <v>2.99472</v>
+        <v>3.01134</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1511387972938816</v>
+        <v>-0.1484509202047457</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2276273570108289</v>
+        <v>0.2330599416900725</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0456282647457229</v>
+        <v>0.04539309655713364</v>
       </c>
       <c r="E274" t="n">
-        <v>11.91576653239301</v>
+        <v>11.91688033205118</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12215,7 +12215,7 @@
         <v>2.13082</v>
       </c>
       <c r="K274" t="n">
-        <v>2.66082</v>
+        <v>2.6877</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3285895414159912</v>
+        <v>-0.3286722752122051</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4536040569475319</v>
+        <v>-0.4541003154710066</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.033169414100755</v>
+        <v>-2.032879633674178</v>
       </c>
       <c r="E275" t="n">
-        <v>10.89253773365242</v>
+        <v>10.8937726424023</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12255,10 +12255,10 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>2.58219</v>
+        <v>2.58216</v>
       </c>
       <c r="K275" t="n">
-        <v>2.75775</v>
+        <v>2.77453</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-4.034116703693281</v>
+        <v>-4.032698912550414</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.161730321837243</v>
+        <v>-4.146537689144647</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.712123366872488</v>
+        <v>-3.712249861182071</v>
       </c>
       <c r="E276" t="n">
-        <v>8.914129461868781</v>
+        <v>8.913984306999655</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12301,7 +12301,7 @@
         <v>2.63791</v>
       </c>
       <c r="K276" t="n">
-        <v>2.21599</v>
+        <v>2.23296</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.382340237328507</v>
+        <v>-3.382154795313663</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.721321429768387</v>
+        <v>-3.711510848265176</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.393823344749991</v>
+        <v>-3.394101114323578</v>
       </c>
       <c r="E277" t="n">
-        <v>10.77427944625449</v>
+        <v>10.77595309634778</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12341,10 +12341,10 @@
         <v>0.65789</v>
       </c>
       <c r="J277" t="n">
-        <v>2.55236</v>
+        <v>2.55237</v>
       </c>
       <c r="K277" t="n">
-        <v>2.56361</v>
+        <v>2.58046</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.317237634930748</v>
+        <v>3.318093219278317</v>
       </c>
       <c r="C278" t="n">
-        <v>3.627760355980558</v>
+        <v>3.628312236657072</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.565017860804574</v>
+        <v>-1.565652807992701</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127404229306865</v>
+        <v>6.127342609782849</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12384,10 +12384,10 @@
         <v>0.98847</v>
       </c>
       <c r="J278" t="n">
-        <v>3.58311</v>
+        <v>3.58306</v>
       </c>
       <c r="K278" t="n">
-        <v>2.94631</v>
+        <v>2.96253</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1632685936737599</v>
+        <v>-0.1599778575878674</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4616445794015211</v>
+        <v>0.4683003423314736</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.296760582737654</v>
+        <v>-0.2971120966861363</v>
       </c>
       <c r="E279" t="n">
-        <v>4.003451869216845</v>
+        <v>4.003005903496204</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12427,10 +12427,10 @@
         <v>1.32013</v>
       </c>
       <c r="J279" t="n">
-        <v>3.10548</v>
+        <v>3.1055</v>
       </c>
       <c r="K279" t="n">
-        <v>2.32984</v>
+        <v>2.34661</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.885030781333108</v>
+        <v>-1.885369579831797</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.184667014962227</v>
+        <v>-2.179190984307933</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7807904544285482</v>
+        <v>-0.7808962728500957</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4859442178563267</v>
+        <v>0.4846270127703445</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12470,10 +12470,10 @@
         <v>1.48515</v>
       </c>
       <c r="J280" t="n">
-        <v>3.13291</v>
+        <v>3.13292</v>
       </c>
       <c r="K280" t="n">
-        <v>2.30534</v>
+        <v>2.32203</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.162114823610239</v>
+        <v>2.164460956483194</v>
       </c>
       <c r="C281" t="n">
-        <v>1.858467756309801</v>
+        <v>1.86417755022954</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.077607401954729</v>
+        <v>-3.077612448370992</v>
       </c>
       <c r="E281" t="n">
-        <v>4.007933753738402</v>
+        <v>4.006861595270306</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12516,7 +12516,7 @@
         <v>2.52866</v>
       </c>
       <c r="K281" t="n">
-        <v>2.21158</v>
+        <v>2.23795</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.185412824795051</v>
+        <v>1.180664877006898</v>
       </c>
       <c r="C282" t="n">
-        <v>1.631669211513276</v>
+        <v>1.617144724619091</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2536800937758654</v>
+        <v>0.2542126345234541</v>
       </c>
       <c r="E282" t="n">
-        <v>1.011148961575703</v>
+        <v>1.010027733445407</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12559,7 +12559,7 @@
         <v>2.46732</v>
       </c>
       <c r="K282" t="n">
-        <v>2.41021</v>
+        <v>2.43624</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.179482908349239</v>
+        <v>1.172419941780611</v>
       </c>
       <c r="C283" t="n">
-        <v>0.5736114152817384</v>
+        <v>0.556347529099166</v>
       </c>
       <c r="D283" t="n">
-        <v>0.09201227658357514</v>
+        <v>0.09277845684152464</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1198248736752672</v>
+        <v>-0.1206534886659782</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12599,10 +12599,10 @@
         <v>1.64745</v>
       </c>
       <c r="J283" t="n">
-        <v>1.71537</v>
+        <v>1.71547</v>
       </c>
       <c r="K283" t="n">
-        <v>2.27467</v>
+        <v>2.29109</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.5794494035974</v>
+        <v>2.579690171681204</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.04457132202305703</v>
+        <v>-0.04544101648337184</v>
       </c>
       <c r="D284" t="n">
-        <v>2.836103928663625</v>
+        <v>2.835910383148899</v>
       </c>
       <c r="E284" t="n">
-        <v>0.787156726719318</v>
+        <v>0.7864773630498867</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12642,10 +12642,10 @@
         <v>1.48026</v>
       </c>
       <c r="J284" t="n">
-        <v>1.26787</v>
+        <v>1.26785</v>
       </c>
       <c r="K284" t="n">
-        <v>2.43856</v>
+        <v>2.46422</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4419999412918818</v>
+        <v>0.4466689080444786</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7824679892302511</v>
+        <v>-0.7733935407845172</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.462096992364625</v>
+        <v>-1.462483705154205</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2826134454298579</v>
+        <v>0.2818449199872175</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12685,10 +12685,10 @@
         <v>1.64474</v>
       </c>
       <c r="J285" t="n">
-        <v>0.55141</v>
+        <v>0.55138</v>
       </c>
       <c r="K285" t="n">
-        <v>2.98366</v>
+        <v>2.99924</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.667262585207332</v>
+        <v>4.668690803169739</v>
       </c>
       <c r="C286" t="n">
-        <v>1.845226171886294</v>
+        <v>1.855249216741117</v>
       </c>
       <c r="D286" t="n">
-        <v>2.917435749922159</v>
+        <v>2.917763949720853</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268405657167326</v>
+        <v>1.268321605814093</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12728,10 +12728,10 @@
         <v>1.47783</v>
       </c>
       <c r="J286" t="n">
-        <v>1.35616</v>
+        <v>1.35613</v>
       </c>
       <c r="K286" t="n">
-        <v>3.00009</v>
+        <v>3.02513</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.846056120261856</v>
+        <v>5.844541756931765</v>
       </c>
       <c r="C287" t="n">
-        <v>3.945026217877823</v>
+        <v>3.935159839686242</v>
       </c>
       <c r="D287" t="n">
-        <v>4.803924942773574</v>
+        <v>4.804874820454774</v>
       </c>
       <c r="E287" t="n">
-        <v>2.66916490293192</v>
+        <v>2.669709925236141</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12771,10 +12771,10 @@
         <v>1.31148</v>
       </c>
       <c r="J287" t="n">
-        <v>1.26578</v>
+        <v>1.26572</v>
       </c>
       <c r="K287" t="n">
-        <v>3.25273</v>
+        <v>3.27745</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.498431528514279</v>
+        <v>3.499862306200563</v>
       </c>
       <c r="C288" t="n">
-        <v>2.938889610639728</v>
+        <v>2.943995754343964</v>
       </c>
       <c r="D288" t="n">
-        <v>2.074337447290975</v>
+        <v>2.074469503879439</v>
       </c>
       <c r="E288" t="n">
-        <v>3.353174433481931</v>
+        <v>3.353930139421779</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12814,10 +12814,10 @@
         <v>0.982</v>
       </c>
       <c r="J288" t="n">
-        <v>0.52286</v>
+        <v>0.52284</v>
       </c>
       <c r="K288" t="n">
-        <v>3.69213</v>
+        <v>3.71596</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.863723675042221</v>
+        <v>6.861132552923221</v>
       </c>
       <c r="C289" t="n">
-        <v>6.024166351705462</v>
+        <v>6.017091638230632</v>
       </c>
       <c r="D289" t="n">
-        <v>2.155820017528742</v>
+        <v>2.156106685775772</v>
       </c>
       <c r="E289" t="n">
-        <v>3.799196930486826</v>
+        <v>3.800715758812645</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12860,7 +12860,7 @@
         <v>-0.27212</v>
       </c>
       <c r="K289" t="n">
-        <v>2.99</v>
+        <v>3.01489</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8594276196107975</v>
+        <v>0.8608783441057311</v>
       </c>
       <c r="C290" t="n">
-        <v>1.151393043219784</v>
+        <v>1.156307902309517</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.120464785416887</v>
+        <v>-2.121339799956545</v>
       </c>
       <c r="E290" t="n">
-        <v>2.410870334872328</v>
+        <v>2.41012281723274</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12900,10 +12900,10 @@
         <v>0.6525300000000001</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.031</v>
+        <v>-0.03102</v>
       </c>
       <c r="K290" t="n">
-        <v>3.38919</v>
+        <v>3.40386</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.207208021993591</v>
+        <v>3.210190005372993</v>
       </c>
       <c r="C291" t="n">
-        <v>3.302335422799185</v>
+        <v>3.30600599970563</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.155472621502396</v>
+        <v>-1.156377772779105</v>
       </c>
       <c r="E291" t="n">
-        <v>3.624701921116702</v>
+        <v>3.624570274770345</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12943,10 +12943,10 @@
         <v>0.4886</v>
       </c>
       <c r="J291" t="n">
-        <v>-0.23571</v>
+        <v>-0.23569</v>
       </c>
       <c r="K291" t="n">
-        <v>3.75388</v>
+        <v>3.76809</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.276604093897409</v>
+        <v>6.277806644191841</v>
       </c>
       <c r="C292" t="n">
-        <v>5.583273833367608</v>
+        <v>5.589130105142059</v>
       </c>
       <c r="D292" t="n">
-        <v>2.238689738159283</v>
+        <v>2.238158368864673</v>
       </c>
       <c r="E292" t="n">
-        <v>4.889407212780683</v>
+        <v>4.889303273598622</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -12986,10 +12986,10 @@
         <v>0.3252</v>
       </c>
       <c r="J292" t="n">
-        <v>-0.73887</v>
+        <v>-0.73882</v>
       </c>
       <c r="K292" t="n">
-        <v>3.08555</v>
+        <v>3.10982</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.526871392593978</v>
+        <v>3.527654180890272</v>
       </c>
       <c r="C293" t="n">
-        <v>2.375242654590926</v>
+        <v>2.383290190843024</v>
       </c>
       <c r="D293" t="n">
-        <v>2.540129163662597</v>
+        <v>2.540214623218628</v>
       </c>
       <c r="E293" t="n">
-        <v>4.245713238433457</v>
+        <v>4.245931878705367</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13029,10 +13029,10 @@
         <v>0.16234</v>
       </c>
       <c r="J293" t="n">
-        <v>-0.52383</v>
+        <v>-0.52376</v>
       </c>
       <c r="K293" t="n">
-        <v>3.72799</v>
+        <v>3.74181</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.360485775136194</v>
+        <v>8.354093925716732</v>
       </c>
       <c r="C294" t="n">
-        <v>5.916934926124573</v>
+        <v>5.900804410734906</v>
       </c>
       <c r="D294" t="n">
-        <v>4.170960654758415</v>
+        <v>4.171452749961602</v>
       </c>
       <c r="E294" t="n">
-        <v>6.247892821516321</v>
+        <v>6.248583344198799</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13072,10 +13072,10 @@
         <v>0.16234</v>
       </c>
       <c r="J294" t="n">
-        <v>-0.82298</v>
+        <v>-0.8229300000000001</v>
       </c>
       <c r="K294" t="n">
-        <v>3.35814</v>
+        <v>3.37235</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.69146455173244</v>
+        <v>6.68404994040348</v>
       </c>
       <c r="C295" t="n">
-        <v>5.398902291778995</v>
+        <v>5.378685150165019</v>
       </c>
       <c r="D295" t="n">
-        <v>6.059908672759584</v>
+        <v>6.0606056224495</v>
       </c>
       <c r="E295" t="n">
-        <v>6.939314497768101</v>
+        <v>6.940381522591776</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13115,10 +13115,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>-0.04698</v>
+        <v>-0.04685</v>
       </c>
       <c r="K295" t="n">
-        <v>3.75954</v>
+        <v>3.78253</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.19613313593521</v>
+        <v>5.198063790070306</v>
       </c>
       <c r="C296" t="n">
-        <v>5.720253772558292</v>
+        <v>5.712291099233924</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1316725948299124</v>
+        <v>0.1312825219072389</v>
       </c>
       <c r="E296" t="n">
-        <v>4.676712727892918</v>
+        <v>4.677126454987945</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13158,10 +13158,10 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0.2855</v>
+        <v>0.28549</v>
       </c>
       <c r="K296" t="n">
-        <v>3.5754</v>
+        <v>3.57969</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.855189348920884</v>
+        <v>3.8610460343939</v>
       </c>
       <c r="C297" t="n">
-        <v>4.005678363753629</v>
+        <v>4.013056291227746</v>
       </c>
       <c r="D297" t="n">
-        <v>2.992835890565515</v>
+        <v>2.992286037782366</v>
       </c>
       <c r="E297" t="n">
-        <v>4.089387339668971</v>
+        <v>4.089138194572528</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13201,10 +13201,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J297" t="n">
-        <v>0.32241</v>
+        <v>0.32236</v>
       </c>
       <c r="K297" t="n">
-        <v>3.51541</v>
+        <v>3.53852</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.42721865637896</v>
+        <v>2.429169381656648</v>
       </c>
       <c r="C298" t="n">
-        <v>1.064701269605717</v>
+        <v>1.072207497751942</v>
       </c>
       <c r="D298" t="n">
-        <v>0.4186885613877145</v>
+        <v>0.418796172969027</v>
       </c>
       <c r="E298" t="n">
-        <v>3.046170296115203</v>
+        <v>3.046329766948364</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13244,10 +13244,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J298" t="n">
-        <v>0.36177</v>
+        <v>0.36145</v>
       </c>
       <c r="K298" t="n">
-        <v>3.36437</v>
+        <v>3.37813</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.285056674635722</v>
+        <v>3.286348374986403</v>
       </c>
       <c r="C299" t="n">
-        <v>2.789004595274269</v>
+        <v>2.78786568076459</v>
       </c>
       <c r="D299" t="n">
-        <v>1.812145288843303</v>
+        <v>1.81275192177297</v>
       </c>
       <c r="E299" t="n">
-        <v>2.815922308022589</v>
+        <v>2.815479282391764</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13287,10 +13287,10 @@
         <v>-0.16181</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.01037</v>
+        <v>-0.01045</v>
       </c>
       <c r="K299" t="n">
-        <v>3.2421</v>
+        <v>3.25598</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.539288375544515</v>
+        <v>4.538876253491964</v>
       </c>
       <c r="C300" t="n">
-        <v>3.698228548452343</v>
+        <v>3.698847247969517</v>
       </c>
       <c r="D300" t="n">
-        <v>3.838654047738022</v>
+        <v>3.839018112116044</v>
       </c>
       <c r="E300" t="n">
-        <v>3.739920473143754</v>
+        <v>3.740187148604912</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13330,10 +13330,10 @@
         <v>0.16207</v>
       </c>
       <c r="J300" t="n">
-        <v>0.98017</v>
+        <v>0.9801800000000001</v>
       </c>
       <c r="K300" t="n">
-        <v>2.7755</v>
+        <v>2.78968</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.787050016599426</v>
+        <v>4.784019757239144</v>
       </c>
       <c r="C301" t="n">
-        <v>3.191196498709714</v>
+        <v>3.185370017392564</v>
       </c>
       <c r="D301" t="n">
-        <v>5.177118982649431</v>
+        <v>5.177808868506628</v>
       </c>
       <c r="E301" t="n">
-        <v>1.878418003519555</v>
+        <v>1.878186331831588</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13373,10 +13373,10 @@
         <v>0.32415</v>
       </c>
       <c r="J301" t="n">
-        <v>1.95798</v>
+        <v>1.95792</v>
       </c>
       <c r="K301" t="n">
-        <v>3.50765</v>
+        <v>3.53027</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.386549660944273</v>
+        <v>5.386305370842148</v>
       </c>
       <c r="C302" t="n">
-        <v>3.359610450919526</v>
+        <v>3.361635797076379</v>
       </c>
       <c r="D302" t="n">
-        <v>4.134489031907873</v>
+        <v>4.134328882951133</v>
       </c>
       <c r="E302" t="n">
-        <v>1.199493541520513</v>
+        <v>1.198764076513203</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13416,10 +13416,10 @@
         <v>0.32415</v>
       </c>
       <c r="J302" t="n">
-        <v>1.47847</v>
+        <v>1.47842</v>
       </c>
       <c r="K302" t="n">
-        <v>2.95028</v>
+        <v>2.97354</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.155533039872107</v>
+        <v>5.156612191450072</v>
       </c>
       <c r="C303" t="n">
-        <v>3.155056877185114</v>
+        <v>3.154459614347771</v>
       </c>
       <c r="D303" t="n">
-        <v>1.698858260960967</v>
+        <v>1.698277029242101</v>
       </c>
       <c r="E303" t="n">
-        <v>3.115682005693632</v>
+        <v>3.115006146620658</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13459,10 +13459,10 @@
         <v>0.32415</v>
       </c>
       <c r="J303" t="n">
-        <v>1.99491</v>
+        <v>1.99517</v>
       </c>
       <c r="K303" t="n">
-        <v>2.41204</v>
+        <v>2.43593</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>0.9869928416829543</v>
+        <v>0.9887337248025263</v>
       </c>
       <c r="C304" t="n">
-        <v>0.4927375950121382</v>
+        <v>0.5057348458960664</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.5983383160184874</v>
+        <v>-0.5989351588020497</v>
       </c>
       <c r="E304" t="n">
-        <v>3.856466870759423</v>
+        <v>3.856288611796366</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13502,10 +13502,10 @@
         <v>0.48622</v>
       </c>
       <c r="J304" t="n">
-        <v>2.73244</v>
+        <v>2.7326</v>
       </c>
       <c r="K304" t="n">
-        <v>3.10204</v>
+        <v>3.11566</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.052300163220665</v>
+        <v>1.050068259259773</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1584922576779446</v>
+        <v>0.1629277491386416</v>
       </c>
       <c r="D305" t="n">
-        <v>2.191785289661508</v>
+        <v>2.192272630448699</v>
       </c>
       <c r="E305" t="n">
-        <v>1.984548233741656</v>
+        <v>1.984210598915692</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13545,10 +13545,10 @@
         <v>0.48622</v>
       </c>
       <c r="J305" t="n">
-        <v>2.49368</v>
+        <v>2.49373</v>
       </c>
       <c r="K305" t="n">
-        <v>2.43814</v>
+        <v>2.45266</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.5592271823780859</v>
+        <v>0.5559850166789504</v>
       </c>
       <c r="C306" t="n">
-        <v>0.03428449096030128</v>
+        <v>0.033161118844105</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.252475326034586</v>
+        <v>-1.252204127951362</v>
       </c>
       <c r="E306" t="n">
-        <v>2.335269300962062</v>
+        <v>2.334943899394748</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13588,10 +13588,10 @@
         <v>0.48622</v>
       </c>
       <c r="J306" t="n">
-        <v>2.96864</v>
+        <v>2.96893</v>
       </c>
       <c r="K306" t="n">
-        <v>2.44802</v>
+        <v>2.47147</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.268092337813399</v>
+        <v>2.263308073364456</v>
       </c>
       <c r="C307" t="n">
-        <v>1.379522247330645</v>
+        <v>1.376053537912836</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.588324881520376</v>
+        <v>-2.588221375408051</v>
       </c>
       <c r="E307" t="n">
-        <v>3.153178007076129</v>
+        <v>3.152982617120537</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13631,10 +13631,10 @@
         <v>0.6483</v>
       </c>
       <c r="J307" t="n">
-        <v>3.49668</v>
+        <v>3.49684</v>
       </c>
       <c r="K307" t="n">
-        <v>1.91928</v>
+        <v>1.93427</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.830615945459568</v>
+        <v>1.835131546966284</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2851671950238721</v>
+        <v>0.2880956412844249</v>
       </c>
       <c r="D308" t="n">
-        <v>1.612480907223701</v>
+        <v>1.612008020339983</v>
       </c>
       <c r="E308" t="n">
-        <v>4.80336002580104</v>
+        <v>4.803318719029948</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13674,10 +13674,10 @@
         <v>0.6483</v>
       </c>
       <c r="J308" t="n">
-        <v>3.03736</v>
+        <v>3.03728</v>
       </c>
       <c r="K308" t="n">
-        <v>2.42354</v>
+        <v>2.44687</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.163793221279509</v>
+        <v>3.168215865682056</v>
       </c>
       <c r="C309" t="n">
-        <v>2.248010079461205</v>
+        <v>2.251790495689776</v>
       </c>
       <c r="D309" t="n">
-        <v>0.5875121379698145</v>
+        <v>0.586940520951984</v>
       </c>
       <c r="E309" t="n">
-        <v>5.404773513839389</v>
+        <v>5.404863706237295</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13717,10 +13717,10 @@
         <v>0.81037</v>
       </c>
       <c r="J309" t="n">
-        <v>3.08114</v>
+        <v>3.08092</v>
       </c>
       <c r="K309" t="n">
-        <v>2.23728</v>
+        <v>2.26059</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.778502572715194</v>
+        <v>5.780221674576436</v>
       </c>
       <c r="C310" t="n">
-        <v>6.633033839257263</v>
+        <v>6.622012287782453</v>
       </c>
       <c r="D310" t="n">
-        <v>2.743171430225533</v>
+        <v>2.743105667602252</v>
       </c>
       <c r="E310" t="n">
-        <v>8.382920747428813</v>
+        <v>8.383353747286293</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13760,10 +13760,10 @@
         <v>0.81037</v>
       </c>
       <c r="J310" t="n">
-        <v>2.59002</v>
+        <v>2.5895</v>
       </c>
       <c r="K310" t="n">
-        <v>2.67523</v>
+        <v>2.69789</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.917898014555465</v>
+        <v>3.921919468633384</v>
       </c>
       <c r="C311" t="n">
-        <v>3.190084038594021</v>
+        <v>3.191353432719057</v>
       </c>
       <c r="D311" t="n">
-        <v>0.7052874641698903</v>
+        <v>0.7052093710286034</v>
       </c>
       <c r="E311" t="n">
-        <v>4.87112112122301</v>
+        <v>4.871102970455121</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13803,10 +13803,10 @@
         <v>0.97245</v>
       </c>
       <c r="J311" t="n">
-        <v>2.98498</v>
+        <v>2.98467</v>
       </c>
       <c r="K311" t="n">
-        <v>2.26848</v>
+        <v>2.2917</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.075274309834476</v>
+        <v>4.073800338278488</v>
       </c>
       <c r="C312" t="n">
-        <v>2.339946785490055</v>
+        <v>2.34060975616468</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.123267288937646</v>
+        <v>-1.123065172965643</v>
       </c>
       <c r="E312" t="n">
-        <v>5.809050085041045</v>
+        <v>5.809135502387042</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13846,10 +13846,10 @@
         <v>0.80906</v>
       </c>
       <c r="J312" t="n">
-        <v>2.70086</v>
+        <v>2.70092</v>
       </c>
       <c r="K312" t="n">
-        <v>2.64724</v>
+        <v>2.66075</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.234035863275486</v>
+        <v>3.234216254195266</v>
       </c>
       <c r="C313" t="n">
-        <v>2.415985732258408</v>
+        <v>2.424857333889596</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.1015609323090083</v>
+        <v>-0.1015658938355424</v>
       </c>
       <c r="E313" t="n">
-        <v>6.313366575249901</v>
+        <v>6.313669382269627</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13889,10 +13889,10 @@
         <v>0.6462</v>
       </c>
       <c r="J313" t="n">
-        <v>2.38551</v>
+        <v>2.38525</v>
       </c>
       <c r="K313" t="n">
-        <v>2.38896</v>
+        <v>2.40283</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.318939710710934</v>
+        <v>4.318755926026419</v>
       </c>
       <c r="C314" t="n">
-        <v>3.881011253760147</v>
+        <v>3.888326954389987</v>
       </c>
       <c r="D314" t="n">
-        <v>1.514739272232046</v>
+        <v>1.514887032397216</v>
       </c>
       <c r="E314" t="n">
-        <v>8.600283189987667</v>
+        <v>8.601976775023147</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13932,10 +13932,10 @@
         <v>0.6462</v>
       </c>
       <c r="J314" t="n">
-        <v>1.95374</v>
+        <v>1.95375</v>
       </c>
       <c r="K314" t="n">
-        <v>2.49425</v>
+        <v>2.50795</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.531356988285171</v>
+        <v>1.531349703014473</v>
       </c>
       <c r="C315" t="n">
-        <v>2.651393664763146</v>
+        <v>2.652641728433913</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9818295322432391</v>
+        <v>0.9818383776636352</v>
       </c>
       <c r="E315" t="n">
-        <v>3.988303128512838</v>
+        <v>3.988677374502902</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13975,10 +13975,10 @@
         <v>0.6462</v>
       </c>
       <c r="J315" t="n">
-        <v>2.41639</v>
+        <v>2.41687</v>
       </c>
       <c r="K315" t="n">
-        <v>3.03701</v>
+        <v>3.0587</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.57291672334794</v>
+        <v>2.571373894281503</v>
       </c>
       <c r="C316" t="n">
-        <v>2.855112694085871</v>
+        <v>2.859057121712283</v>
       </c>
       <c r="D316" t="n">
-        <v>0.4478529928877872</v>
+        <v>0.447822766725503</v>
       </c>
       <c r="E316" t="n">
-        <v>3.687829825460831</v>
+        <v>3.688239318164954</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14018,10 +14018,10 @@
         <v>0.64516</v>
       </c>
       <c r="J316" t="n">
-        <v>2.62109</v>
+        <v>2.6214</v>
       </c>
       <c r="K316" t="n">
-        <v>2.56004</v>
+        <v>2.58235</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.853975743740294</v>
+        <v>8.845153499067537</v>
       </c>
       <c r="C317" t="n">
-        <v>9.099896955742249</v>
+        <v>9.077094057722036</v>
       </c>
       <c r="D317" t="n">
-        <v>0.3699341890839314</v>
+        <v>0.370839422229885</v>
       </c>
       <c r="E317" t="n">
-        <v>7.340422878178221</v>
+        <v>7.34137866576301</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14061,10 +14061,10 @@
         <v>0.48387</v>
       </c>
       <c r="J317" t="n">
-        <v>3.43081</v>
+        <v>3.43104</v>
       </c>
       <c r="K317" t="n">
-        <v>3.12059</v>
+        <v>3.15085</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.286533705495699</v>
+        <v>4.281887213205282</v>
       </c>
       <c r="C318" t="n">
-        <v>5.387217405210443</v>
+        <v>5.376363195751921</v>
       </c>
       <c r="D318" t="n">
-        <v>2.149357277960084</v>
+        <v>2.150063379575573</v>
       </c>
       <c r="E318" t="n">
-        <v>5.22940205726985</v>
+        <v>5.229895256243933</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14104,10 +14104,10 @@
         <v>0.48387</v>
       </c>
       <c r="J318" t="n">
-        <v>3.37023</v>
+        <v>3.37079</v>
       </c>
       <c r="K318" t="n">
-        <v>3.09233</v>
+        <v>3.11349</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.296663471631179</v>
+        <v>4.291761767070135</v>
       </c>
       <c r="C319" t="n">
-        <v>3.356582985496015</v>
+        <v>3.348302203734099</v>
       </c>
       <c r="D319" t="n">
-        <v>2.745783639258059</v>
+        <v>2.745901376022619</v>
       </c>
       <c r="E319" t="n">
-        <v>3.749641223224098</v>
+        <v>3.749081962700918</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14147,10 +14147,10 @@
         <v>0.16103</v>
       </c>
       <c r="J319" t="n">
-        <v>3.17678</v>
+        <v>3.1774</v>
       </c>
       <c r="K319" t="n">
-        <v>3.56389</v>
+        <v>3.58429</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.865771681193733</v>
+        <v>6.87308328348506</v>
       </c>
       <c r="C320" t="n">
-        <v>6.805365042091016</v>
+        <v>6.805716043459298</v>
       </c>
       <c r="D320" t="n">
-        <v>2.211753755758727</v>
+        <v>2.211136492519938</v>
       </c>
       <c r="E320" t="n">
-        <v>3.084407178100901</v>
+        <v>3.083592415679748</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14190,10 +14190,10 @@
         <v>0</v>
       </c>
       <c r="J320" t="n">
-        <v>3.18014</v>
+        <v>3.17951</v>
       </c>
       <c r="K320" t="n">
-        <v>2.87261</v>
+        <v>2.894</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.976298358665866</v>
+        <v>5.980549567771964</v>
       </c>
       <c r="C321" t="n">
-        <v>4.678767476239076</v>
+        <v>4.683907431055978</v>
       </c>
       <c r="D321" t="n">
-        <v>1.487421342062833</v>
+        <v>1.486636311603995</v>
       </c>
       <c r="E321" t="n">
-        <v>2.67836380981521</v>
+        <v>2.677252259304019</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14233,10 +14233,10 @@
         <v>-0.48232</v>
       </c>
       <c r="J321" t="n">
-        <v>3.2291</v>
+        <v>3.22862</v>
       </c>
       <c r="K321" t="n">
-        <v>2.65039</v>
+        <v>2.66319</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.53189295269696</v>
+        <v>5.537391484197318</v>
       </c>
       <c r="C322" t="n">
-        <v>3.502701795371999</v>
+        <v>3.509075011334151</v>
       </c>
       <c r="D322" t="n">
-        <v>0.04236611876988761</v>
+        <v>0.04203033256953148</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5030957669849623</v>
+        <v>-0.5050157107830411</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14276,10 +14276,10 @@
         <v>-0.6430900000000001</v>
       </c>
       <c r="J322" t="n">
-        <v>3.72732</v>
+        <v>3.72666</v>
       </c>
       <c r="K322" t="n">
-        <v>2.90082</v>
+        <v>2.9218</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.317404544697379</v>
+        <v>4.324960409445811</v>
       </c>
       <c r="C323" t="n">
-        <v>5.186712206351585</v>
+        <v>5.202595198028148</v>
       </c>
       <c r="D323" t="n">
-        <v>0.9817337660311232</v>
+        <v>0.9811335909164054</v>
       </c>
       <c r="E323" t="n">
-        <v>4.158535075658976</v>
+        <v>4.157828904970806</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14319,10 +14319,10 @@
         <v>-0.96308</v>
       </c>
       <c r="J323" t="n">
-        <v>3.89826</v>
+        <v>3.8978</v>
       </c>
       <c r="K323" t="n">
-        <v>3.14892</v>
+        <v>3.1695</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -14338,16 +14338,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.601375338670935</v>
+        <v>7.601535031899465</v>
       </c>
       <c r="C324" t="n">
-        <v>6.94959260400454</v>
+        <v>6.946833138806707</v>
       </c>
       <c r="D324" t="n">
-        <v>3.735997084280696</v>
+        <v>3.736058703830381</v>
       </c>
       <c r="E324" t="n">
-        <v>2.172825569091774</v>
+        <v>2.171560405124451</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14362,10 +14362,10 @@
         <v>-1.1236</v>
       </c>
       <c r="J324" t="n">
-        <v>3.61719</v>
+        <v>3.61713</v>
       </c>
       <c r="K324" t="n">
-        <v>2.50108</v>
+        <v>2.51404</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14381,16 +14381,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.027396776134175</v>
+        <v>6.030408283739597</v>
       </c>
       <c r="C325" t="n">
-        <v>5.625954404869726</v>
+        <v>5.641248687015832</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.04828051615300977</v>
+        <v>-0.04887942527218581</v>
       </c>
       <c r="E325" t="n">
-        <v>2.851348774724149</v>
+        <v>2.851039325122429</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14405,10 +14405,10 @@
         <v>-1.1236</v>
       </c>
       <c r="J325" t="n">
-        <v>3.29445</v>
+        <v>3.29407</v>
       </c>
       <c r="K325" t="n">
-        <v>2.5579</v>
+        <v>2.57937</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -14424,16 +14424,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.887833120955821</v>
+        <v>5.888313493686725</v>
       </c>
       <c r="C326" t="n">
-        <v>4.919834302975312</v>
+        <v>4.930756435854877</v>
       </c>
       <c r="D326" t="n">
-        <v>0.8608719858816727</v>
+        <v>0.8608738499763291</v>
       </c>
       <c r="E326" t="n">
-        <v>4.399784236987903</v>
+        <v>4.40099921367243</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14451,7 +14451,7 @@
         <v>2.88702</v>
       </c>
       <c r="K326" t="n">
-        <v>2.20055</v>
+        <v>2.22261</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -14467,16 +14467,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.753550124340205</v>
+        <v>9.750534054063277</v>
       </c>
       <c r="C327" t="n">
-        <v>9.279420354173439</v>
+        <v>9.275019880701873</v>
       </c>
       <c r="D327" t="n">
-        <v>2.748848700001028</v>
+        <v>2.749214313709358</v>
       </c>
       <c r="E327" t="n">
-        <v>7.705345078675041</v>
+        <v>7.706543476929983</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14491,10 +14491,10 @@
         <v>-0.96308</v>
       </c>
       <c r="J327" t="n">
-        <v>2.09096</v>
+        <v>2.09182</v>
       </c>
       <c r="K327" t="n">
-        <v>1.93349</v>
+        <v>1.94716</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14510,16 +14510,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.34496128227267</v>
+        <v>10.33708214301878</v>
       </c>
       <c r="C328" t="n">
-        <v>9.046098184537609</v>
+        <v>9.034992168942612</v>
       </c>
       <c r="D328" t="n">
-        <v>3.164292067201901</v>
+        <v>3.165058764866635</v>
       </c>
       <c r="E328" t="n">
-        <v>7.463163781014459</v>
+        <v>7.464206179796173</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14534,10 +14534,10 @@
         <v>-0.96154</v>
       </c>
       <c r="J328" t="n">
-        <v>1.82669</v>
+        <v>1.82708</v>
       </c>
       <c r="K328" t="n">
-        <v>1.75845</v>
+        <v>1.77241</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -14553,16 +14553,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.023348955246742</v>
+        <v>4.011368005730809</v>
       </c>
       <c r="C329" t="n">
-        <v>3.054616176433567</v>
+        <v>3.039351588181161</v>
       </c>
       <c r="D329" t="n">
-        <v>2.829315490028517</v>
+        <v>2.830625095924999</v>
       </c>
       <c r="E329" t="n">
-        <v>3.680809004068131</v>
+        <v>3.681647150085432</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14577,10 +14577,10 @@
         <v>-0.80257</v>
       </c>
       <c r="J329" t="n">
-        <v>1.16186</v>
+        <v>1.1622</v>
       </c>
       <c r="K329" t="n">
-        <v>1.43614</v>
+        <v>1.45051</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14596,16 +14596,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.136010053808438</v>
+        <v>6.127061659058874</v>
       </c>
       <c r="C330" t="n">
-        <v>5.557778482063069</v>
+        <v>5.542668921136018</v>
       </c>
       <c r="D330" t="n">
-        <v>1.307818747155887</v>
+        <v>1.309057827164595</v>
       </c>
       <c r="E330" t="n">
-        <v>5.681989535734377</v>
+        <v>5.682663473980876</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14620,10 +14620,10 @@
         <v>-0.80257</v>
       </c>
       <c r="J330" t="n">
-        <v>1.15736</v>
+        <v>1.15817</v>
       </c>
       <c r="K330" t="n">
-        <v>1.0311</v>
+        <v>1.03768</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -14639,16 +14639,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>6.168034415700485</v>
+        <v>6.16089307526031</v>
       </c>
       <c r="C331" t="n">
-        <v>7.47273561968782</v>
+        <v>7.446560287254811</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.061831449358475</v>
+        <v>-1.061333774228712</v>
       </c>
       <c r="E331" t="n">
-        <v>5.030823276603202</v>
+        <v>5.030855078963992</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14663,10 +14663,10 @@
         <v>-0.80386</v>
       </c>
       <c r="J331" t="n">
-        <v>0.74465</v>
+        <v>0.74575</v>
       </c>
       <c r="K331" t="n">
-        <v>0.6287700000000001</v>
+        <v>0.64456</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -14682,16 +14682,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.39573551606427</v>
+        <v>4.407141425642958</v>
       </c>
       <c r="C332" t="n">
-        <v>4.048734963809575</v>
+        <v>4.050931793994428</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.628981009416597</v>
+        <v>-1.630145809996852</v>
       </c>
       <c r="E332" t="n">
-        <v>4.529792928229548</v>
+        <v>4.52989784133857</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14706,10 +14706,10 @@
         <v>-0.80515</v>
       </c>
       <c r="J332" t="n">
-        <v>1.19649</v>
+        <v>1.19516</v>
       </c>
       <c r="K332" t="n">
-        <v>0.679</v>
+        <v>0.69468</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14725,16 +14725,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.879803483760713</v>
+        <v>3.883806565979508</v>
       </c>
       <c r="C333" t="n">
-        <v>3.801713447340838</v>
+        <v>3.794529498075749</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.150040554329281</v>
+        <v>-3.150802485073589</v>
       </c>
       <c r="E333" t="n">
-        <v>4.427796817365204</v>
+        <v>4.428046639778427</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14749,10 +14749,10 @@
         <v>-0.6462</v>
       </c>
       <c r="J333" t="n">
-        <v>1.24114</v>
+        <v>1.24054</v>
       </c>
       <c r="K333" t="n">
-        <v>0.71344</v>
+        <v>0.72906</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14768,16 +14768,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.878477540442703</v>
+        <v>2.887693960533499</v>
       </c>
       <c r="C334" t="n">
-        <v>4.894604211419407</v>
+        <v>4.905320160687743</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.64446414999142</v>
+        <v>-1.644961712763238</v>
       </c>
       <c r="E334" t="n">
-        <v>5.085768682290803</v>
+        <v>5.085274334090983</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14792,10 +14792,10 @@
         <v>-0.80906</v>
       </c>
       <c r="J334" t="n">
-        <v>0.99819</v>
+        <v>0.99754</v>
       </c>
       <c r="K334" t="n">
-        <v>0.01688</v>
+        <v>0.0337</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -14811,16 +14811,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.71043149430248</v>
+        <v>3.719066606340293</v>
       </c>
       <c r="C335" t="n">
-        <v>1.757213194230256</v>
+        <v>1.774133737275996</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.361916447280643</v>
+        <v>-2.362823612249698</v>
       </c>
       <c r="E335" t="n">
-        <v>3.779165531335282</v>
+        <v>3.779214426871569</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14835,10 +14835,10 @@
         <v>-0.81037</v>
       </c>
       <c r="J335" t="n">
-        <v>1.67324</v>
+        <v>1.6726</v>
       </c>
       <c r="K335" t="n">
-        <v>0.0506</v>
+        <v>0.06733</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -14854,16 +14854,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.79783018303439</v>
+        <v>3.801856423181538</v>
       </c>
       <c r="C336" t="n">
-        <v>3.786392687033402</v>
+        <v>3.791294759957053</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.452861674527052</v>
+        <v>-3.453044397688798</v>
       </c>
       <c r="E336" t="n">
-        <v>3.414574658260316</v>
+        <v>3.414296398438776</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14878,10 +14878,10 @@
         <v>-0.81169</v>
       </c>
       <c r="J336" t="n">
-        <v>-2.54524</v>
+        <v>-2.54535</v>
       </c>
       <c r="K336" t="n">
-        <v>0.25329</v>
+        <v>0.27811</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14897,16 +14897,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.927769363591625</v>
+        <v>1.93198144635085</v>
       </c>
       <c r="C337" t="n">
-        <v>1.441961373137923</v>
+        <v>1.456669783602083</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.512019487789719</v>
+        <v>-3.512454369140605</v>
       </c>
       <c r="E337" t="n">
-        <v>3.514116876051165</v>
+        <v>3.514591186708826</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14921,10 +14921,10 @@
         <v>-0.81169</v>
       </c>
       <c r="J337" t="n">
-        <v>2.74052</v>
+        <v>2.74022</v>
       </c>
       <c r="K337" t="n">
-        <v>0.08426</v>
+        <v>0.10092</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -14940,16 +14940,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.34541494082472</v>
+        <v>3.347295794305927</v>
       </c>
       <c r="C338" t="n">
-        <v>2.102549999364411</v>
+        <v>2.118566679196232</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.236891453560919</v>
+        <v>-2.237170558088264</v>
       </c>
       <c r="E338" t="n">
-        <v>1.739945847408131</v>
+        <v>1.739751222768704</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14964,10 +14964,10 @@
         <v>-0.97403</v>
       </c>
       <c r="J338" t="n">
-        <v>-0.47303</v>
+        <v>-0.47291</v>
       </c>
       <c r="K338" t="n">
-        <v>0.20265</v>
+        <v>0.21911</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -14983,16 +14983,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.3726522674528887</v>
+        <v>0.3695349825207028</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.182003850782088</v>
+        <v>-2.16424363052109</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.010018383888179</v>
+        <v>-2.010063017998975</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.7775638740992852</v>
+        <v>-0.7780700293527842</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15007,10 +15007,10 @@
         <v>-1.2966</v>
       </c>
       <c r="J339" t="n">
-        <v>-0.05052</v>
+        <v>-0.04974</v>
       </c>
       <c r="K339" t="n">
-        <v>0.26977</v>
+        <v>0.29449</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -15026,16 +15026,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.431254241499548</v>
+        <v>3.423452281782269</v>
       </c>
       <c r="C340" t="n">
-        <v>0.4274517850618942</v>
+        <v>0.4314934904457779</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.662683287441658</v>
+        <v>-2.661745897783174</v>
       </c>
       <c r="E340" t="n">
-        <v>-0.8714694044759774</v>
+        <v>-0.8721370336156498</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15050,10 +15050,10 @@
         <v>-1.45631</v>
       </c>
       <c r="J340" t="n">
-        <v>-0.5256</v>
+        <v>-0.5249</v>
       </c>
       <c r="K340" t="n">
-        <v>0.61536</v>
+        <v>0.63941</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -15069,16 +15069,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.852520015137229</v>
+        <v>4.836448709823493</v>
       </c>
       <c r="C341" t="n">
-        <v>1.40151272053497</v>
+        <v>1.376573411518978</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.002734453079681</v>
+        <v>-3.001287246167561</v>
       </c>
       <c r="E341" t="n">
-        <v>1.94252130353354</v>
+        <v>1.942213532946213</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15093,10 +15093,10 @@
         <v>-1.45631</v>
       </c>
       <c r="J341" t="n">
-        <v>-1.20653</v>
+        <v>-1.20612</v>
       </c>
       <c r="K341" t="n">
-        <v>0.68262</v>
+        <v>0.69807</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15112,16 +15112,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.49426965876012</v>
+        <v>5.480961590506506</v>
       </c>
       <c r="C342" t="n">
-        <v>2.759715120617412</v>
+        <v>2.742386238615535</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.6847114627089868</v>
+        <v>-0.6833374815226723</v>
       </c>
       <c r="E342" t="n">
-        <v>0.02123194736516343</v>
+        <v>0.02095156842485402</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15136,10 +15136,10 @@
         <v>-1.45631</v>
       </c>
       <c r="J342" t="n">
-        <v>-1.42789</v>
+        <v>-1.42733</v>
       </c>
       <c r="K342" t="n">
-        <v>1.13023</v>
+        <v>1.1533</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -15155,16 +15155,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>6.086095737412744</v>
+        <v>6.077263913137498</v>
       </c>
       <c r="C343" t="n">
-        <v>1.577177428878684</v>
+        <v>1.548524866852574</v>
       </c>
       <c r="D343" t="n">
-        <v>2.408400883766837</v>
+        <v>2.408985477005587</v>
       </c>
       <c r="E343" t="n">
-        <v>0.804161695364769</v>
+        <v>0.8039616888592116</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15179,10 +15179,10 @@
         <v>-1.2966</v>
       </c>
       <c r="J343" t="n">
-        <v>-1.09554</v>
+        <v>-1.0947</v>
       </c>
       <c r="K343" t="n">
-        <v>1.2919</v>
+        <v>1.31457</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -15198,16 +15198,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>6.190421430147452</v>
+        <v>6.208345536205595</v>
       </c>
       <c r="C344" t="n">
-        <v>3.952591529908611</v>
+        <v>3.963278651186242</v>
       </c>
       <c r="D344" t="n">
-        <v>0.873671347040017</v>
+        <v>0.8717260224757606</v>
       </c>
       <c r="E344" t="n">
-        <v>2.763234340664722</v>
+        <v>2.763080800598305</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15222,10 +15222,10 @@
         <v>-0.97403</v>
       </c>
       <c r="J344" t="n">
-        <v>-0.70835</v>
+        <v>-0.70978</v>
       </c>
       <c r="K344" t="n">
-        <v>1.36571</v>
+        <v>1.38819</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15241,16 +15241,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.39143494881343</v>
+        <v>10.39814363827012</v>
       </c>
       <c r="C345" t="n">
-        <v>7.604847435337803</v>
+        <v>7.593636712614216</v>
       </c>
       <c r="D345" t="n">
-        <v>7.735967331913041</v>
+        <v>7.734608516039865</v>
       </c>
       <c r="E345" t="n">
-        <v>2.738176580169416</v>
+        <v>2.738625909540104</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15265,10 +15265,10 @@
         <v>-0.65041</v>
       </c>
       <c r="J345" t="n">
-        <v>-0.65917</v>
+        <v>-0.65966</v>
       </c>
       <c r="K345" t="n">
-        <v>1.58543</v>
+        <v>1.60747</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15284,16 +15284,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.122363200038402</v>
+        <v>2.130944042086291</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4370929464681983</v>
+        <v>-0.4244147939783449</v>
       </c>
       <c r="D346" t="n">
-        <v>1.530905004712846</v>
+        <v>1.53081609036223</v>
       </c>
       <c r="E346" t="n">
-        <v>2.172050285950222</v>
+        <v>2.172330441933079</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15308,10 +15308,10 @@
         <v>-0.16313</v>
       </c>
       <c r="J346" t="n">
-        <v>-0.20649</v>
+        <v>-0.20679</v>
       </c>
       <c r="K346" t="n">
-        <v>2.17722</v>
+        <v>2.18947</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -15327,16 +15327,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.142196937426879</v>
+        <v>5.150718684250921</v>
       </c>
       <c r="C347" t="n">
-        <v>3.083331411103885</v>
+        <v>3.099789808332321</v>
       </c>
       <c r="D347" t="n">
-        <v>4.419871688047694</v>
+        <v>4.418600882713619</v>
       </c>
       <c r="E347" t="n">
-        <v>2.011522559850598</v>
+        <v>2.010897719631077</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15351,10 +15351,10 @@
         <v>0.1634</v>
       </c>
       <c r="J347" t="n">
-        <v>-1.1033</v>
+        <v>-1.10351</v>
       </c>
       <c r="K347" t="n">
-        <v>2.05664</v>
+        <v>2.07755</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -15370,16 +15370,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.662284547243488</v>
+        <v>3.669455018694001</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.7809457716627</v>
+        <v>-0.7705868454765064</v>
       </c>
       <c r="D348" t="n">
-        <v>4.029154647735189</v>
+        <v>4.028988290433344</v>
       </c>
       <c r="E348" t="n">
-        <v>2.91852395703569</v>
+        <v>2.919030516966004</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15394,10 +15394,10 @@
         <v>0.491</v>
       </c>
       <c r="J348" t="n">
-        <v>2.90993</v>
+        <v>2.90988</v>
       </c>
       <c r="K348" t="n">
-        <v>2.25703</v>
+        <v>2.2775</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15413,16 +15413,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.6369393018332</v>
+        <v>6.639636487359457</v>
       </c>
       <c r="C349" t="n">
-        <v>6.209409224829021</v>
+        <v>6.228140102779212</v>
       </c>
       <c r="D349" t="n">
-        <v>5.531175057549698</v>
+        <v>5.531643161905508</v>
       </c>
       <c r="E349" t="n">
-        <v>5.746605854816678</v>
+        <v>5.74683609721871</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15437,10 +15437,10 @@
         <v>0.65466</v>
       </c>
       <c r="J349" t="n">
-        <v>-1.38851</v>
+        <v>-1.38874</v>
       </c>
       <c r="K349" t="n">
-        <v>2.64354</v>
+        <v>2.66319</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -15456,16 +15456,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.488607162865455</v>
+        <v>5.48936843521699</v>
       </c>
       <c r="C350" t="n">
-        <v>3.03579451078495</v>
+        <v>3.04155058657567</v>
       </c>
       <c r="D350" t="n">
-        <v>6.412575337142634</v>
+        <v>6.412059482975918</v>
       </c>
       <c r="E350" t="n">
-        <v>6.382824484495031</v>
+        <v>6.381909251652074</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15480,10 +15480,10 @@
         <v>0.65574</v>
       </c>
       <c r="J350" t="n">
-        <v>2.59521</v>
+        <v>2.59519</v>
       </c>
       <c r="K350" t="n">
-        <v>2.90722</v>
+        <v>2.92634</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -15499,16 +15499,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>5.618719040246822</v>
+        <v>5.609709552780329</v>
       </c>
       <c r="C351" t="n">
-        <v>4.328169893797362</v>
+        <v>4.329956299863591</v>
       </c>
       <c r="D351" t="n">
-        <v>1.894619433005484</v>
+        <v>1.894868061009869</v>
       </c>
       <c r="E351" t="n">
-        <v>7.674742271191759</v>
+        <v>7.674843405490361</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15523,10 +15523,10 @@
         <v>0.65681</v>
       </c>
       <c r="J351" t="n">
-        <v>1.84989</v>
+        <v>1.85033</v>
       </c>
       <c r="K351" t="n">
-        <v>2.82495</v>
+        <v>2.84396</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.36741199449857</v>
+        <v>-53.3716435373044</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.31711559263698</v>
+        <v>-49.31920514238725</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.27683635487107</v>
+        <v>-44.27591077834889</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.405775824330557</v>
+        <v>-1.405925434582578</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15566,10 +15566,10 @@
         <v>0.65681</v>
       </c>
       <c r="J352" t="n">
-        <v>1.60025</v>
+        <v>1.60067</v>
       </c>
       <c r="K352" t="n">
-        <v>2.13639</v>
+        <v>2.15683</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -15585,16 +15585,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40185017409358</v>
+        <v>-99.40197272406446</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11550479573198</v>
+        <v>-98.11647222565402</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.68443834357957</v>
+        <v>-88.68415804327566</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.30460504824605</v>
+        <v>-52.30464190037026</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15609,10 +15609,10 @@
         <v>-5.41872</v>
       </c>
       <c r="J353" t="n">
-        <v>-49.24236</v>
+        <v>-49.24183</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.85494</v>
+        <v>-38.84574</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15628,16 +15628,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80712833373208</v>
+        <v>-98.80731135801039</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98419090681753</v>
+        <v>-95.98502100512947</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.1453776203125</v>
+        <v>-82.14500373297355</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.55070820223051</v>
+        <v>-50.55055230538783</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15652,10 +15652,10 @@
         <v>-2.95567</v>
       </c>
       <c r="J354" t="n">
-        <v>-69.47646</v>
+        <v>-69.47422</v>
       </c>
       <c r="K354" t="n">
-        <v>-39.01585</v>
+        <v>-39.00632</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -15671,16 +15671,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.1269809584258</v>
+        <v>-98.12711795317868</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.34608902969472</v>
+        <v>-94.34788363377858</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.39329286095894</v>
+        <v>-81.39316012125946</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.85633810554106</v>
+        <v>-42.85597081332219</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15695,10 +15695,10 @@
         <v>-2.95567</v>
       </c>
       <c r="J355" t="n">
-        <v>-70.02321000000001</v>
+        <v>-70.02136</v>
       </c>
       <c r="K355" t="n">
-        <v>-24.51651</v>
+        <v>-24.50304</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -15714,16 +15714,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.73671435022069</v>
+        <v>-97.73615115307662</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62347679820724</v>
+        <v>-93.62099507027733</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64763884316153</v>
+        <v>-75.64849539092089</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.03868485068302</v>
+        <v>-43.03906157327621</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15738,10 +15738,10 @@
         <v>-1.63934</v>
       </c>
       <c r="J356" t="n">
-        <v>-74.59457</v>
+        <v>-74.59829999999999</v>
       </c>
       <c r="K356" t="n">
-        <v>-27.55323</v>
+        <v>-27.54128</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15757,16 +15757,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.45921504568894</v>
+        <v>-97.45884275128206</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.98588361314098</v>
+        <v>-90.98320037184409</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18191082662628</v>
+        <v>-74.18255412484274</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.64657665609019</v>
+        <v>-45.64627806366808</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15781,10 +15781,10 @@
         <v>-2.12766</v>
       </c>
       <c r="J357" t="n">
-        <v>-74.77885000000001</v>
+        <v>-74.78028</v>
       </c>
       <c r="K357" t="n">
-        <v>-16.61132</v>
+        <v>-16.59902</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15800,16 +15800,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.42885721981662</v>
+        <v>-97.42868309174636</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90554750764259</v>
+        <v>-89.90495084520556</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.99410560968153</v>
+        <v>-74.99413450649175</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.21810569958774</v>
+        <v>-40.2174490257181</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15824,10 +15824,10 @@
         <v>-9.64052</v>
       </c>
       <c r="J358" t="n">
-        <v>-76.74901</v>
+        <v>-76.75029000000001</v>
       </c>
       <c r="K358" t="n">
-        <v>-23.47208</v>
+        <v>-23.45282</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -15843,16 +15843,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07274790613695</v>
+        <v>-90.07187062394723</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.38441170416712</v>
+        <v>-81.38361918138027</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.91155241684993</v>
+        <v>-74.91196833340568</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.44853577781845</v>
+        <v>-31.44827455099354</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15867,10 +15867,10 @@
         <v>-6.68842</v>
       </c>
       <c r="J359" t="n">
-        <v>-66.86611000000001</v>
+        <v>-66.86682</v>
       </c>
       <c r="K359" t="n">
-        <v>-15.0892</v>
+        <v>-15.0791</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -15886,16 +15886,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.74785497363096</v>
+        <v>-76.74601786482054</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.62417809972287</v>
+        <v>-65.62294109055904</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.91123313182375</v>
+        <v>-71.91139211277874</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.81637659576998</v>
+        <v>-12.81470031746895</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15910,10 +15910,10 @@
         <v>-5.21173</v>
       </c>
       <c r="J360" t="n">
-        <v>-57.11084</v>
+        <v>-57.11076</v>
       </c>
       <c r="K360" t="n">
-        <v>-16.13408</v>
+        <v>-16.12161</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -15929,16 +15929,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.83058441160314</v>
+        <v>-74.8297237797896</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.32674836912005</v>
+        <v>-66.31688966844619</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.34952132192772</v>
+        <v>-70.34940691178299</v>
       </c>
       <c r="E361" t="n">
-        <v>-17.07700177428316</v>
+        <v>-17.07747703267301</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>
@@ -15953,10 +15953,10 @@
         <v>-3.90244</v>
       </c>
       <c r="J361" t="n">
-        <v>-53.24821</v>
+        <v>-53.24911</v>
       </c>
       <c r="K361" t="n">
-        <v>-13.31201</v>
+        <v>-13.29787</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>

--- a/Paper1/Paper/Data/HawaiiData.xlsx
+++ b/Paper1/Paper/Data/HawaiiData.xlsx
@@ -519,7 +519,7 @@
         <v>6.81613</v>
       </c>
       <c r="K2" t="n">
-        <v>2.87895</v>
+        <v>2.87126</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -562,7 +562,7 @@
         <v>4.1021</v>
       </c>
       <c r="K3" t="n">
-        <v>2.59393</v>
+        <v>2.57368</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         <v>7.64422</v>
       </c>
       <c r="K4" t="n">
-        <v>2.06887</v>
+        <v>2.05005</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         <v>0.78852</v>
       </c>
       <c r="K5" t="n">
-        <v>1.84914</v>
+        <v>1.84424</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>1.84658</v>
       </c>
       <c r="K6" t="n">
-        <v>1.71065</v>
+        <v>1.70612</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         <v>2.08449</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64195</v>
+        <v>1.62441</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>4.63764</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4766</v>
+        <v>1.45957</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>6.97377</v>
       </c>
       <c r="K9" t="n">
-        <v>1.50158</v>
+        <v>1.49783</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>7.98008</v>
       </c>
       <c r="K10" t="n">
-        <v>1.02416</v>
+        <v>0.99529</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>5.8278</v>
       </c>
       <c r="K11" t="n">
-        <v>0.78565</v>
+        <v>0.77054</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
         <v>2.9503</v>
       </c>
       <c r="K12" t="n">
-        <v>0.41797</v>
+        <v>0.39083</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>3.51153</v>
       </c>
       <c r="K13" t="n">
-        <v>0.54895</v>
+        <v>0.52144</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>1.94713</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.23428</v>
+        <v>-0.25964</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
         <v>3.15431</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.16943</v>
+        <v>-0.18201</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>4.82046</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02615</v>
+        <v>0.01304</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>5.38341</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.40491</v>
+        <v>-0.42991</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>4.36429</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.62581</v>
+        <v>-0.6502</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>3.86553</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.93799</v>
+        <v>-0.94867</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>0.97692</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.11732</v>
+        <v>-1.12753</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>-1.18745</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.21983</v>
+        <v>-1.24272</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>-2.91305</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.11775</v>
+        <v>-1.11515</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>-2.6775</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.20826</v>
+        <v>-1.23121</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>-2.96163</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.97555</v>
+        <v>-0.98624</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>-3.79345</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.87092</v>
+        <v>-0.88186</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>-6.73928</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.56099</v>
+        <v>-0.57269</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>-7.32479</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03916</v>
+        <v>-0.0521</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>-7.1254</v>
       </c>
       <c r="K28" t="n">
-        <v>0.26147</v>
+        <v>0.24782</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-8.415520000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.95738</v>
+        <v>0.94204</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>-7.85285</v>
       </c>
       <c r="K30" t="n">
-        <v>1.16767</v>
+        <v>1.15183</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>-7.16309</v>
       </c>
       <c r="K31" t="n">
-        <v>1.2888</v>
+        <v>1.27263</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>-7.55994</v>
       </c>
       <c r="K32" t="n">
-        <v>1.32703</v>
+        <v>1.31079</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>-8.48602</v>
       </c>
       <c r="K33" t="n">
-        <v>1.1298</v>
+        <v>1.12728</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>-7.68216</v>
       </c>
       <c r="K34" t="n">
-        <v>1.27497</v>
+        <v>1.25885</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>-5.99345</v>
       </c>
       <c r="K35" t="n">
-        <v>1.35455</v>
+        <v>1.33841</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         <v>-7.30623</v>
       </c>
       <c r="K36" t="n">
-        <v>1.0771</v>
+        <v>1.0616</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>-7.4327</v>
       </c>
       <c r="K37" t="n">
-        <v>0.56386</v>
+        <v>0.54952</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>-3.37108</v>
       </c>
       <c r="K38" t="n">
-        <v>0.61664</v>
+        <v>0.60217</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>-2.19051</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.03918</v>
+        <v>-0.05212</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>-1.43983</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.11736</v>
+        <v>-0.13011</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>-0.49028</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.5456</v>
+        <v>-0.55736</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>-0.87717</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.95967</v>
+        <v>-0.9705</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>-0.88079</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.67515</v>
+        <v>-0.68662</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>1.3325</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.63537</v>
+        <v>-0.64691</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>0.55998</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.57158</v>
+        <v>-0.59624</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>1.28628</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.33744</v>
+        <v>-0.3626</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>0.98446</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.28545</v>
+        <v>-0.29781</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>2.6052</v>
       </c>
       <c r="K48" t="n">
-        <v>0.46784</v>
+        <v>0.46687</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>2.47558</v>
       </c>
       <c r="K49" t="n">
-        <v>0.92581</v>
+        <v>0.91087</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>1.36814</v>
       </c>
       <c r="K50" t="n">
-        <v>1.01708</v>
+        <v>1.00195</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>0.16895</v>
       </c>
       <c r="K51" t="n">
-        <v>1.14973</v>
+        <v>1.13429</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
         <v>-0.72939</v>
       </c>
       <c r="K52" t="n">
-        <v>0.93995</v>
+        <v>0.92496</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>-0.54606</v>
       </c>
       <c r="K53" t="n">
-        <v>0.77064</v>
+        <v>0.756</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>-0.36021</v>
       </c>
       <c r="K54" t="n">
-        <v>1.00825</v>
+        <v>0.98001</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>-1.19128</v>
       </c>
       <c r="K55" t="n">
-        <v>0.77124</v>
+        <v>0.74354</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>-2.05836</v>
       </c>
       <c r="K56" t="n">
-        <v>0.58724</v>
+        <v>0.55997</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>-0.18493</v>
       </c>
       <c r="K57" t="n">
-        <v>0.44421</v>
+        <v>0.4303</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>-1.03702</v>
       </c>
       <c r="K58" t="n">
-        <v>0.23441</v>
+        <v>0.22095</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>-2.17944</v>
       </c>
       <c r="K59" t="n">
-        <v>0.09109</v>
+        <v>0.07792</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>-1.12347</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.38805</v>
+        <v>-0.41306</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>-1.00905</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.41344</v>
+        <v>-0.42553</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>-0.75413</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.64541</v>
+        <v>-0.65705</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>1.25597</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.14208</v>
+        <v>-0.1547</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>2.01067</v>
       </c>
       <c r="K64" t="n">
-        <v>0.10347</v>
+        <v>0.07745</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>0.76272</v>
       </c>
       <c r="K65" t="n">
-        <v>0.24627</v>
+        <v>0.23286</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>1.11254</v>
       </c>
       <c r="K66" t="n">
-        <v>0.44076</v>
+        <v>0.42702</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>2.19418</v>
       </c>
       <c r="K67" t="n">
-        <v>0.70048</v>
+        <v>0.69921</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>2.4185</v>
       </c>
       <c r="K68" t="n">
-        <v>1.1287</v>
+        <v>1.1137</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>2.18369</v>
       </c>
       <c r="K69" t="n">
-        <v>1.53486</v>
+        <v>1.51909</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>2.97358</v>
       </c>
       <c r="K70" t="n">
-        <v>1.26023</v>
+        <v>1.24497</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>3.16051</v>
       </c>
       <c r="K71" t="n">
-        <v>1.43006</v>
+        <v>1.41448</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>2.0643</v>
       </c>
       <c r="K72" t="n">
-        <v>1.10375</v>
+        <v>1.08879</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>3.76248</v>
       </c>
       <c r="K73" t="n">
-        <v>1.37519</v>
+        <v>1.3468</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>3.28817</v>
       </c>
       <c r="K74" t="n">
-        <v>1.42913</v>
+        <v>1.41357</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>1.56007</v>
       </c>
       <c r="K75" t="n">
-        <v>1.16414</v>
+        <v>1.14913</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>1.23793</v>
       </c>
       <c r="K76" t="n">
-        <v>1.18863</v>
+        <v>1.18664</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>1.25015</v>
       </c>
       <c r="K77" t="n">
-        <v>1.29299</v>
+        <v>1.26484</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>-0.04673</v>
       </c>
       <c r="K78" t="n">
-        <v>1.381</v>
+        <v>1.3658</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>-1.37348</v>
       </c>
       <c r="K79" t="n">
-        <v>1.22375</v>
+        <v>1.20869</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>-1.29686</v>
       </c>
       <c r="K80" t="n">
-        <v>0.87235</v>
+        <v>0.85809</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>-1.46387</v>
       </c>
       <c r="K81" t="n">
-        <v>1.21701</v>
+        <v>1.2022</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>-1.77293</v>
       </c>
       <c r="K82" t="n">
-        <v>1.47549</v>
+        <v>1.47304</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>-1.09116</v>
       </c>
       <c r="K83" t="n">
-        <v>1.51243</v>
+        <v>1.49712</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>-1.2865</v>
       </c>
       <c r="K84" t="n">
-        <v>2.11919</v>
+        <v>2.10283</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         <v>-1.96697</v>
       </c>
       <c r="K85" t="n">
-        <v>1.77886</v>
+        <v>1.77613</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>-1.70266</v>
       </c>
       <c r="K86" t="n">
-        <v>1.97259</v>
+        <v>1.95652</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>-1.2652</v>
       </c>
       <c r="K87" t="n">
-        <v>1.86677</v>
+        <v>1.85091</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>-0.99316</v>
       </c>
       <c r="K88" t="n">
-        <v>1.77477</v>
+        <v>1.75908</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>-0.57684</v>
       </c>
       <c r="K89" t="n">
-        <v>1.95303</v>
+        <v>1.95004</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>0.14623</v>
       </c>
       <c r="K90" t="n">
-        <v>1.6168</v>
+        <v>1.60163</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         <v>0.38673</v>
       </c>
       <c r="K91" t="n">
-        <v>1.59074</v>
+        <v>1.5754</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>-0.28095</v>
       </c>
       <c r="K92" t="n">
-        <v>1.55157</v>
+        <v>1.53651</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>-1.01727</v>
       </c>
       <c r="K93" t="n">
-        <v>1.31629</v>
+        <v>1.30166</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>-1.34253</v>
       </c>
       <c r="K94" t="n">
-        <v>1.28967</v>
+        <v>1.26231</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>-1.92064</v>
       </c>
       <c r="K95" t="n">
-        <v>1.16162</v>
+        <v>1.14725</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>-1.2639</v>
       </c>
       <c r="K96" t="n">
-        <v>1.19482</v>
+        <v>1.18046</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>-1.95129</v>
       </c>
       <c r="K97" t="n">
-        <v>1.52144</v>
+        <v>1.49404</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>-1.93974</v>
       </c>
       <c r="K98" t="n">
-        <v>1.55759</v>
+        <v>1.54271</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>-2.02241</v>
       </c>
       <c r="K99" t="n">
-        <v>1.88277</v>
+        <v>1.8674</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>-2.25761</v>
       </c>
       <c r="K100" t="n">
-        <v>2.28328</v>
+        <v>2.25479</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>-1.59827</v>
       </c>
       <c r="K101" t="n">
-        <v>2.22862</v>
+        <v>2.20028</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>-1.14518</v>
       </c>
       <c r="K102" t="n">
-        <v>2.60586</v>
+        <v>2.60228</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>-0.72556</v>
       </c>
       <c r="K103" t="n">
-        <v>2.95628</v>
+        <v>2.92683</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>-1.65101</v>
       </c>
       <c r="K104" t="n">
-        <v>3.18096</v>
+        <v>3.16408</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>-1.33991</v>
       </c>
       <c r="K105" t="n">
-        <v>3.37289</v>
+        <v>3.35579</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>-1.70892</v>
       </c>
       <c r="K106" t="n">
-        <v>3.74485</v>
+        <v>3.72725</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5034,7 +5034,7 @@
         <v>0.68667</v>
       </c>
       <c r="K107" t="n">
-        <v>3.99401</v>
+        <v>3.97607</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>1.65402</v>
       </c>
       <c r="K108" t="n">
-        <v>4.01442</v>
+        <v>3.99652</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>2.32127</v>
       </c>
       <c r="K109" t="n">
-        <v>4.05004</v>
+        <v>4.03266</v>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0.66956</v>
       </c>
       <c r="K110" t="n">
-        <v>4.30427</v>
+        <v>4.28607</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>0.87769</v>
       </c>
       <c r="K111" t="n">
-        <v>3.80683</v>
+        <v>3.78937</v>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>1.75034</v>
       </c>
       <c r="K112" t="n">
-        <v>3.96173</v>
+        <v>3.95688</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>2.71015</v>
       </c>
       <c r="K113" t="n">
-        <v>3.99265</v>
+        <v>3.97554</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>2.88092</v>
       </c>
       <c r="K114" t="n">
-        <v>4.07814</v>
+        <v>4.06048</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>3.29156</v>
       </c>
       <c r="K115" t="n">
-        <v>3.97859</v>
+        <v>3.97375</v>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>3.94634</v>
       </c>
       <c r="K116" t="n">
-        <v>4.07816</v>
+        <v>4.0611</v>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>3.91093</v>
       </c>
       <c r="K117" t="n">
-        <v>3.80665</v>
+        <v>3.78998</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>5.24193</v>
       </c>
       <c r="K118" t="n">
-        <v>3.6939</v>
+        <v>3.67744</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>3.6318</v>
       </c>
       <c r="K119" t="n">
-        <v>3.68459</v>
+        <v>3.68017</v>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>1.87632</v>
       </c>
       <c r="K120" t="n">
-        <v>3.34568</v>
+        <v>3.32975</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>1.44759</v>
       </c>
       <c r="K121" t="n">
-        <v>3.11868</v>
+        <v>3.11534</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>3.30476</v>
       </c>
       <c r="K122" t="n">
-        <v>2.33606</v>
+        <v>2.32145</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>3.27766</v>
       </c>
       <c r="K123" t="n">
-        <v>2.69404</v>
+        <v>2.66714</v>
       </c>
       <c r="L123" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>2.21597</v>
       </c>
       <c r="K124" t="n">
-        <v>2.28882</v>
+        <v>2.27433</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>0.87878</v>
       </c>
       <c r="K125" t="n">
-        <v>1.91968</v>
+        <v>1.90588</v>
       </c>
       <c r="L125" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>0.29782</v>
       </c>
       <c r="K126" t="n">
-        <v>1.63069</v>
+        <v>1.60534</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>-0.37752</v>
       </c>
       <c r="K127" t="n">
-        <v>1.47437</v>
+        <v>1.46096</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>-0.12895</v>
       </c>
       <c r="K128" t="n">
-        <v>1.48105</v>
+        <v>1.46785</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>0.65218</v>
       </c>
       <c r="K129" t="n">
-        <v>1.00116</v>
+        <v>1.00012</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>0.34643</v>
       </c>
       <c r="K130" t="n">
-        <v>0.76584</v>
+        <v>0.75345</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>-6.46206</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.15048</v>
+        <v>-0.17343</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>-7.12501</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.43936</v>
+        <v>-0.45045</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>-7.87357</v>
       </c>
       <c r="K133" t="n">
-        <v>-0.48482</v>
+        <v>-0.5073800000000001</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>-7.89682</v>
       </c>
       <c r="K134" t="n">
-        <v>0.50985</v>
+        <v>0.48617</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>-7.86886</v>
       </c>
       <c r="K135" t="n">
-        <v>0.50849</v>
+        <v>0.50802</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>-7.13322</v>
       </c>
       <c r="K136" t="n">
-        <v>0.76125</v>
+        <v>0.74893</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>-6.80835</v>
       </c>
       <c r="K137" t="n">
-        <v>1.23642</v>
+        <v>1.23528</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         <v>-6.60221</v>
       </c>
       <c r="K138" t="n">
-        <v>1.56989</v>
+        <v>1.55691</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>-5.48672</v>
       </c>
       <c r="K139" t="n">
-        <v>2.46771</v>
+        <v>2.45363</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>-5.03357</v>
       </c>
       <c r="K140" t="n">
-        <v>1.79269</v>
+        <v>1.77956</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>-5.26749</v>
       </c>
       <c r="K141" t="n">
-        <v>2.25911</v>
+        <v>2.23374</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -6539,7 +6539,7 @@
         <v>-5.50654</v>
       </c>
       <c r="K142" t="n">
-        <v>2.51036</v>
+        <v>2.49655</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>-0.61918</v>
       </c>
       <c r="K143" t="n">
-        <v>3.45467</v>
+        <v>3.43989</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>1.44287</v>
       </c>
       <c r="K144" t="n">
-        <v>3.78586</v>
+        <v>3.77074</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>2.52602</v>
       </c>
       <c r="K145" t="n">
-        <v>4.07145</v>
+        <v>4.05656</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>3.65909</v>
       </c>
       <c r="K146" t="n">
-        <v>3.80447</v>
+        <v>3.80141</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>3.11967</v>
       </c>
       <c r="K147" t="n">
-        <v>3.43797</v>
+        <v>3.41183</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>2.80844</v>
       </c>
       <c r="K148" t="n">
-        <v>2.99908</v>
+        <v>2.9849</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         <v>2.05342</v>
       </c>
       <c r="K149" t="n">
-        <v>2.30567</v>
+        <v>2.28076</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>1.73332</v>
       </c>
       <c r="K150" t="n">
-        <v>2.12524</v>
+        <v>2.1122</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>0.23826</v>
       </c>
       <c r="K151" t="n">
-        <v>1.31668</v>
+        <v>1.29301</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>0.67216</v>
       </c>
       <c r="K152" t="n">
-        <v>1.70467</v>
+        <v>1.68077</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>1.02751</v>
       </c>
       <c r="K153" t="n">
-        <v>1.63436</v>
+        <v>1.61054</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>1.08997</v>
       </c>
       <c r="K154" t="n">
-        <v>1.75242</v>
+        <v>1.72859</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>2.46883</v>
       </c>
       <c r="K155" t="n">
-        <v>1.93859</v>
+        <v>1.91468</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>1.92559</v>
       </c>
       <c r="K156" t="n">
-        <v>1.92458</v>
+        <v>1.90072</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>2.43304</v>
       </c>
       <c r="K157" t="n">
-        <v>1.87249</v>
+        <v>1.8601</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>1.33274</v>
       </c>
       <c r="K158" t="n">
-        <v>2.07685</v>
+        <v>2.05305</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>1.63252</v>
       </c>
       <c r="K159" t="n">
-        <v>2.40107</v>
+        <v>2.37725</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -7313,7 +7313,7 @@
         <v>1.61073</v>
       </c>
       <c r="K160" t="n">
-        <v>2.7784</v>
+        <v>2.75403</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>2.49768</v>
       </c>
       <c r="K161" t="n">
-        <v>3.46982</v>
+        <v>3.45635</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>3.27015</v>
       </c>
       <c r="K162" t="n">
-        <v>3.71689</v>
+        <v>3.69217</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>4.0691</v>
       </c>
       <c r="K163" t="n">
-        <v>3.73209</v>
+        <v>3.7185</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>3.70529</v>
       </c>
       <c r="K164" t="n">
-        <v>4.0737</v>
+        <v>4.06035</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>2.92964</v>
       </c>
       <c r="K165" t="n">
-        <v>4.00355</v>
+        <v>3.99025</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>2.53471</v>
       </c>
       <c r="K166" t="n">
-        <v>3.83087</v>
+        <v>3.80669</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>3.55969</v>
       </c>
       <c r="K167" t="n">
-        <v>3.67154</v>
+        <v>3.65854</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>3.47448</v>
       </c>
       <c r="K168" t="n">
-        <v>4.06192</v>
+        <v>4.03774</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>2.88883</v>
       </c>
       <c r="K169" t="n">
-        <v>3.73085</v>
+        <v>3.70694</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>2.85888</v>
       </c>
       <c r="K170" t="n">
-        <v>3.2423</v>
+        <v>3.21879</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>2.90654</v>
       </c>
       <c r="K171" t="n">
-        <v>3.38689</v>
+        <v>3.37457</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>3.18469</v>
       </c>
       <c r="K172" t="n">
-        <v>3.26557</v>
+        <v>3.253</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>2.86077</v>
       </c>
       <c r="K173" t="n">
-        <v>3.53677</v>
+        <v>3.52409</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>2.58488</v>
       </c>
       <c r="K174" t="n">
-        <v>3.16524</v>
+        <v>3.16388</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>2.85953</v>
       </c>
       <c r="K175" t="n">
-        <v>3.19092</v>
+        <v>3.16781</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>2.55971</v>
       </c>
       <c r="K176" t="n">
-        <v>3.00768</v>
+        <v>2.99574</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
         <v>2.90968</v>
       </c>
       <c r="K177" t="n">
-        <v>3.32694</v>
+        <v>3.3042</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>3.8469</v>
       </c>
       <c r="K178" t="n">
-        <v>2.99841</v>
+        <v>2.99745</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>2.44219</v>
       </c>
       <c r="K179" t="n">
-        <v>2.83109</v>
+        <v>2.80869</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>1.78547</v>
       </c>
       <c r="K180" t="n">
-        <v>2.25762</v>
+        <v>2.25691</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>1.81739</v>
       </c>
       <c r="K181" t="n">
-        <v>2.85835</v>
+        <v>2.8469</v>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>1.45179</v>
       </c>
       <c r="K182" t="n">
-        <v>2.9824</v>
+        <v>2.97092</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>1.73389</v>
       </c>
       <c r="K183" t="n">
-        <v>2.63545</v>
+        <v>2.62412</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>1.25114</v>
       </c>
       <c r="K184" t="n">
-        <v>2.79581</v>
+        <v>2.77371</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>1.47674</v>
       </c>
       <c r="K185" t="n">
-        <v>1.99958</v>
+        <v>1.96752</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>1.51615</v>
       </c>
       <c r="K186" t="n">
-        <v>2.20489</v>
+        <v>2.17278</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>1.01809</v>
       </c>
       <c r="K187" t="n">
-        <v>2.33475</v>
+        <v>2.32365</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>1.01258</v>
       </c>
       <c r="K188" t="n">
-        <v>2.47463</v>
+        <v>2.45316</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>1.06063</v>
       </c>
       <c r="K189" t="n">
-        <v>2.42518</v>
+        <v>2.41436</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>0.3828</v>
       </c>
       <c r="K190" t="n">
-        <v>2.90079</v>
+        <v>2.87926</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>0.87203</v>
       </c>
       <c r="K191" t="n">
-        <v>2.78408</v>
+        <v>2.7732</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>1.49477</v>
       </c>
       <c r="K192" t="n">
-        <v>3.10533</v>
+        <v>3.08375</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>1.2914</v>
       </c>
       <c r="K193" t="n">
-        <v>2.6251</v>
+        <v>2.61431</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>1.42623</v>
       </c>
       <c r="K194" t="n">
-        <v>2.32296</v>
+        <v>2.31226</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -8818,7 +8818,7 @@
         <v>0.91826</v>
       </c>
       <c r="K195" t="n">
-        <v>2.14834</v>
+        <v>2.12744</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>1.27211</v>
       </c>
       <c r="K196" t="n">
-        <v>1.89467</v>
+        <v>1.87392</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>0.67276</v>
       </c>
       <c r="K197" t="n">
-        <v>1.75618</v>
+        <v>1.756</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>0.25473</v>
       </c>
       <c r="K198" t="n">
-        <v>1.92327</v>
+        <v>1.9129</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>1.03418</v>
       </c>
       <c r="K199" t="n">
-        <v>1.65281</v>
+        <v>1.6322</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>-0.23441</v>
       </c>
       <c r="K200" t="n">
-        <v>1.17207</v>
+        <v>1.15175</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>-0.20364</v>
       </c>
       <c r="K201" t="n">
-        <v>0.79597</v>
+        <v>0.78582</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -9119,7 +9119,7 @@
         <v>-0.67849</v>
       </c>
       <c r="K202" t="n">
-        <v>0.32103</v>
+        <v>0.31096</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>-0.9078000000000001</v>
       </c>
       <c r="K203" t="n">
-        <v>0.33106</v>
+        <v>0.321</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>-1.06044</v>
       </c>
       <c r="K204" t="n">
-        <v>-0.21013</v>
+        <v>-0.23012</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>-0.9976699999999999</v>
       </c>
       <c r="K205" t="n">
-        <v>0.07994</v>
+        <v>0.05995</v>
       </c>
       <c r="L205" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>-0.33445</v>
       </c>
       <c r="K206" t="n">
-        <v>0.24002</v>
+        <v>0.22</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0.17909</v>
       </c>
       <c r="K207" t="n">
-        <v>0.39059</v>
+        <v>0.38057</v>
       </c>
       <c r="L207" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>-1.01099</v>
       </c>
       <c r="K208" t="n">
-        <v>0.06998</v>
+        <v>0.04999</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>-0.79054</v>
       </c>
       <c r="K209" t="n">
-        <v>0.23078</v>
+        <v>0.2107</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>-0.95639</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.52915</v>
+        <v>-0.53914</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>-3.18665</v>
       </c>
       <c r="K211" t="n">
-        <v>-1.26683</v>
+        <v>-1.28678</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>-3.2485</v>
       </c>
       <c r="K212" t="n">
-        <v>-1.54799</v>
+        <v>-1.55813</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>-4.50734</v>
       </c>
       <c r="K213" t="n">
-        <v>-1.61935</v>
+        <v>-1.62935</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>-5.04426</v>
       </c>
       <c r="K214" t="n">
-        <v>-2.37</v>
+        <v>-2.39</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>-6.30201</v>
       </c>
       <c r="K215" t="n">
-        <v>-3.09969</v>
+        <v>-3.10969</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>-7.64505</v>
       </c>
       <c r="K216" t="n">
-        <v>-2.93793</v>
+        <v>-2.94826</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>-7.87262</v>
       </c>
       <c r="K217" t="n">
-        <v>-4.08347</v>
+        <v>-4.09386</v>
       </c>
       <c r="L217" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>-8.357839999999999</v>
       </c>
       <c r="K218" t="n">
-        <v>-4.72912</v>
+        <v>-4.74955</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>-9.30087</v>
       </c>
       <c r="K219" t="n">
-        <v>-5.11772</v>
+        <v>-5.12821</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>-9.0524</v>
       </c>
       <c r="K220" t="n">
-        <v>-5.41459</v>
+        <v>-5.42566</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>-10.13408</v>
       </c>
       <c r="K221" t="n">
-        <v>-5.24577</v>
+        <v>-5.26632</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>-10.12126</v>
       </c>
       <c r="K222" t="n">
-        <v>-5.17916</v>
+        <v>-5.19976</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>-8.6998</v>
       </c>
       <c r="K223" t="n">
-        <v>-4.43524</v>
+        <v>-4.44624</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>-7.54172</v>
       </c>
       <c r="K224" t="n">
-        <v>-4.08805</v>
+        <v>-4.09903</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>-7.08652</v>
       </c>
       <c r="K225" t="n">
-        <v>-4.06421</v>
+        <v>-4.08495</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>-6.15609</v>
       </c>
       <c r="K226" t="n">
-        <v>-3.32889</v>
+        <v>-3.32958</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>-5.44009</v>
       </c>
       <c r="K227" t="n">
-        <v>-2.45589</v>
+        <v>-2.47678</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v>-4.18288</v>
       </c>
       <c r="K228" t="n">
-        <v>-2.43802</v>
+        <v>-2.44885</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>-4.20568</v>
       </c>
       <c r="K229" t="n">
-        <v>-1.61341</v>
+        <v>-1.62415</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>-4.39814</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.55503</v>
+        <v>-0.56568</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>-3.84336</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.15771</v>
+        <v>-0.17878</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>-3.5376</v>
       </c>
       <c r="K232" t="n">
-        <v>0.38023</v>
+        <v>0.36978</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>-1.63789</v>
       </c>
       <c r="K233" t="n">
-        <v>0.86635</v>
+        <v>0.85606</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>-1.38235</v>
       </c>
       <c r="K234" t="n">
-        <v>1.24907</v>
+        <v>1.23888</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>-1.35605</v>
       </c>
       <c r="K235" t="n">
-        <v>1.35321</v>
+        <v>1.34306</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>-1.42166</v>
       </c>
       <c r="K236" t="n">
-        <v>1.59704</v>
+        <v>1.58697</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>-0.25822</v>
       </c>
       <c r="K237" t="n">
-        <v>1.81106</v>
+        <v>1.79044</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>0.24162</v>
       </c>
       <c r="K238" t="n">
-        <v>1.66349</v>
+        <v>1.63205</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>1.3296</v>
       </c>
       <c r="K239" t="n">
-        <v>1.86184</v>
+        <v>1.84127</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>1.6742</v>
       </c>
       <c r="K240" t="n">
-        <v>2.31893</v>
+        <v>2.30908</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>2.18738</v>
       </c>
       <c r="K241" t="n">
-        <v>2.11595</v>
+        <v>2.10604</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -10812,16 +10812,16 @@
         <v>40544</v>
       </c>
       <c r="B242" t="n">
-        <v>11.68090719932215</v>
+        <v>11.6793304557671</v>
       </c>
       <c r="C242" t="n">
-        <v>11.3318132331983</v>
+        <v>11.32569126226912</v>
       </c>
       <c r="D242" t="n">
-        <v>10.10328109363019</v>
+        <v>10.13329264896041</v>
       </c>
       <c r="E242" t="n">
-        <v>7.275771662400277</v>
+        <v>7.275795221643611</v>
       </c>
       <c r="F242" t="n">
         <v>20.28409601772081</v>
@@ -10839,7 +10839,7 @@
         <v>2.30584</v>
       </c>
       <c r="K242" t="n">
-        <v>1.885</v>
+        <v>1.87526</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -10855,16 +10855,16 @@
         <v>40575</v>
       </c>
       <c r="B243" t="n">
-        <v>12.21073280281228</v>
+        <v>12.26165048404681</v>
       </c>
       <c r="C243" t="n">
-        <v>12.40926470388992</v>
+        <v>12.40417173088109</v>
       </c>
       <c r="D243" t="n">
-        <v>7.717293596312369</v>
+        <v>7.787910322302216</v>
       </c>
       <c r="E243" t="n">
-        <v>9.006520143250118</v>
+        <v>9.006549547437203</v>
       </c>
       <c r="F243" t="n">
         <v>18.53821730100375</v>
@@ -10882,7 +10882,7 @@
         <v>2.64201</v>
       </c>
       <c r="K243" t="n">
-        <v>2.28517</v>
+        <v>2.2756</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -10898,16 +10898,16 @@
         <v>40603</v>
       </c>
       <c r="B244" t="n">
-        <v>3.873680974224403</v>
+        <v>3.975695750797037</v>
       </c>
       <c r="C244" t="n">
-        <v>7.187927437076924</v>
+        <v>7.180252727548586</v>
       </c>
       <c r="D244" t="n">
-        <v>6.067304321369793</v>
+        <v>6.058175442718139</v>
       </c>
       <c r="E244" t="n">
-        <v>8.726219241082966</v>
+        <v>8.726242679350204</v>
       </c>
       <c r="F244" t="n">
         <v>16.2326661382471</v>
@@ -10925,7 +10925,7 @@
         <v>3.88705</v>
       </c>
       <c r="K244" t="n">
-        <v>2.18855</v>
+        <v>2.17895</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -10941,16 +10941,16 @@
         <v>40634</v>
       </c>
       <c r="B245" t="n">
-        <v>3.88591955118085</v>
+        <v>3.844155477577149</v>
       </c>
       <c r="C245" t="n">
-        <v>7.411427942976867</v>
+        <v>7.421258183334789</v>
       </c>
       <c r="D245" t="n">
-        <v>4.895240332822581</v>
+        <v>4.836147584872141</v>
       </c>
       <c r="E245" t="n">
-        <v>8.559979368649362</v>
+        <v>8.560088693633183</v>
       </c>
       <c r="F245" t="n">
         <v>13.94462886009298</v>
@@ -10968,7 +10968,7 @@
         <v>2.90178</v>
       </c>
       <c r="K245" t="n">
-        <v>1.87493</v>
+        <v>1.86524</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -10984,16 +10984,16 @@
         <v>40664</v>
       </c>
       <c r="B246" t="n">
-        <v>0.1532861826856857</v>
+        <v>0.1697900216704795</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.6828919657593135</v>
+        <v>-0.6729385710876001</v>
       </c>
       <c r="D246" t="n">
-        <v>1.935148213773696</v>
+        <v>1.851305410399751</v>
       </c>
       <c r="E246" t="n">
-        <v>9.481564238556327</v>
+        <v>9.481628000233243</v>
       </c>
       <c r="F246" t="n">
         <v>11.82500420932786</v>
@@ -11011,7 +11011,7 @@
         <v>3.10555</v>
       </c>
       <c r="K246" t="n">
-        <v>1.49503</v>
+        <v>1.4852</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -11027,16 +11027,16 @@
         <v>40695</v>
       </c>
       <c r="B247" t="n">
-        <v>-0.3638146660678077</v>
+        <v>-0.3546964780125506</v>
       </c>
       <c r="C247" t="n">
-        <v>2.316925798545744</v>
+        <v>2.305476933697892</v>
       </c>
       <c r="D247" t="n">
-        <v>-1.485945253225873</v>
+        <v>-1.579735325264364</v>
       </c>
       <c r="E247" t="n">
-        <v>9.120111413047404</v>
+        <v>9.120117191732447</v>
       </c>
       <c r="F247" t="n">
         <v>8.047097541414283</v>
@@ -11054,7 +11054,7 @@
         <v>3.46134</v>
       </c>
       <c r="K247" t="n">
-        <v>1.16825</v>
+        <v>1.14787</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -11070,13 +11070,13 @@
         <v>40725</v>
       </c>
       <c r="B248" t="n">
-        <v>-1.541412985089996</v>
+        <v>-1.549515289062697</v>
       </c>
       <c r="C248" t="n">
-        <v>-2.302675731629356</v>
+        <v>-2.306802295305721</v>
       </c>
       <c r="D248" t="n">
-        <v>-3.072449067066763</v>
+        <v>-3.087475353941871</v>
       </c>
       <c r="E248" t="n">
         <v>8.16528181146432</v>
@@ -11097,7 +11097,7 @@
         <v>3.43695</v>
       </c>
       <c r="K248" t="n">
-        <v>1.37414</v>
+        <v>1.35388</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -11113,16 +11113,16 @@
         <v>40756</v>
       </c>
       <c r="B249" t="n">
-        <v>1.480266607016767</v>
+        <v>1.452211493375666</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.2312479805749779</v>
+        <v>-0.2296752196580654</v>
       </c>
       <c r="D249" t="n">
-        <v>2.478020887554067</v>
+        <v>2.491523997364786</v>
       </c>
       <c r="E249" t="n">
-        <v>7.167525944489195</v>
+        <v>7.167514602883895</v>
       </c>
       <c r="F249" t="n">
         <v>9.392992139372435</v>
@@ -11140,7 +11140,7 @@
         <v>4.28892</v>
       </c>
       <c r="K249" t="n">
-        <v>1.24831</v>
+        <v>1.23855</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -11156,16 +11156,16 @@
         <v>40787</v>
       </c>
       <c r="B250" t="n">
-        <v>4.857599815151104</v>
+        <v>4.829002123152293</v>
       </c>
       <c r="C250" t="n">
-        <v>4.6681628923539</v>
+        <v>4.653255281707902</v>
       </c>
       <c r="D250" t="n">
-        <v>6.277401962654205</v>
+        <v>6.318342875837546</v>
       </c>
       <c r="E250" t="n">
-        <v>8.2983422144417</v>
+        <v>8.298359157014401</v>
       </c>
       <c r="F250" t="n">
         <v>13.49262661830506</v>
@@ -11183,7 +11183,7 @@
         <v>5.36402</v>
       </c>
       <c r="K250" t="n">
-        <v>1.62585</v>
+        <v>1.60584</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11199,16 +11199,16 @@
         <v>40817</v>
       </c>
       <c r="B251" t="n">
-        <v>0.8642423709991576</v>
+        <v>0.8294686810882412</v>
       </c>
       <c r="C251" t="n">
-        <v>1.468253206631021</v>
+        <v>1.464878999721919</v>
       </c>
       <c r="D251" t="n">
-        <v>2.687932896377343</v>
+        <v>2.673370747984105</v>
       </c>
       <c r="E251" t="n">
-        <v>8.444116149118287</v>
+        <v>8.444138624836661</v>
       </c>
       <c r="F251" t="n">
         <v>9.688543425286866</v>
@@ -11226,7 +11226,7 @@
         <v>4.69098</v>
       </c>
       <c r="K251" t="n">
-        <v>1.81743</v>
+        <v>1.80798</v>
       </c>
       <c r="L251" t="inlineStr">
         <is>
@@ -11242,16 +11242,16 @@
         <v>40848</v>
       </c>
       <c r="B252" t="n">
-        <v>3.683160341395753</v>
+        <v>3.652717279772566</v>
       </c>
       <c r="C252" t="n">
-        <v>2.957114169548247</v>
+        <v>2.97273474311055</v>
       </c>
       <c r="D252" t="n">
-        <v>3.967268399521484</v>
+        <v>3.945298792562668</v>
       </c>
       <c r="E252" t="n">
-        <v>10.18943805476773</v>
+        <v>10.1895377770854</v>
       </c>
       <c r="F252" t="n">
         <v>14.40103706322551</v>
@@ -11269,7 +11269,7 @@
         <v>4.78305</v>
       </c>
       <c r="K252" t="n">
-        <v>1.62475</v>
+        <v>1.59437</v>
       </c>
       <c r="L252" t="inlineStr">
         <is>
@@ -11285,16 +11285,16 @@
         <v>40878</v>
       </c>
       <c r="B253" t="n">
-        <v>7.06945301752957</v>
+        <v>7.118185942725153</v>
       </c>
       <c r="C253" t="n">
-        <v>8.425329120105829</v>
+        <v>8.41134710600242</v>
       </c>
       <c r="D253" t="n">
-        <v>3.54998841021732</v>
+        <v>3.581973696821561</v>
       </c>
       <c r="E253" t="n">
-        <v>7.955371951717582</v>
+        <v>7.955360935927924</v>
       </c>
       <c r="F253" t="n">
         <v>11.98334471005023</v>
@@ -11312,7 +11312,7 @@
         <v>4.9474</v>
       </c>
       <c r="K253" t="n">
-        <v>2.49689</v>
+        <v>2.4772</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -11328,16 +11328,16 @@
         <v>40909</v>
       </c>
       <c r="B254" t="n">
-        <v>7.407366300488616</v>
+        <v>7.372916249347194</v>
       </c>
       <c r="C254" t="n">
-        <v>7.305454473556572</v>
+        <v>7.31638306267679</v>
       </c>
       <c r="D254" t="n">
-        <v>5.650093057627426</v>
+        <v>5.721046427826804</v>
       </c>
       <c r="E254" t="n">
-        <v>8.186649137090573</v>
+        <v>8.186674790912573</v>
       </c>
       <c r="F254" t="n">
         <v>16.05208829938633</v>
@@ -11355,7 +11355,7 @@
         <v>5.61764</v>
       </c>
       <c r="K254" t="n">
-        <v>1.94315</v>
+        <v>1.92347</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -11371,16 +11371,16 @@
         <v>40940</v>
       </c>
       <c r="B255" t="n">
-        <v>5.439755980259942</v>
+        <v>5.447147907603922</v>
       </c>
       <c r="C255" t="n">
-        <v>5.86674323561196</v>
+        <v>5.903693977556745</v>
       </c>
       <c r="D255" t="n">
-        <v>2.553078418150934</v>
+        <v>2.551846860443585</v>
       </c>
       <c r="E255" t="n">
-        <v>6.395400402807883</v>
+        <v>6.395425652365527</v>
       </c>
       <c r="F255" t="n">
         <v>9.442758474681657</v>
@@ -11398,7 +11398,7 @@
         <v>5.94719</v>
       </c>
       <c r="K255" t="n">
-        <v>2.38855</v>
+        <v>2.36918</v>
       </c>
       <c r="L255" t="inlineStr">
         <is>
@@ -11414,16 +11414,16 @@
         <v>40969</v>
       </c>
       <c r="B256" t="n">
-        <v>11.73978426487428</v>
+        <v>11.70623573351168</v>
       </c>
       <c r="C256" t="n">
-        <v>9.824114200518252</v>
+        <v>9.846524186991456</v>
       </c>
       <c r="D256" t="n">
-        <v>5.631449123740828</v>
+        <v>5.657183762856399</v>
       </c>
       <c r="E256" t="n">
-        <v>7.153732721814654</v>
+        <v>7.153774293952497</v>
       </c>
       <c r="F256" t="n">
         <v>13.80193464833384</v>
@@ -11441,7 +11441,7 @@
         <v>5.6654</v>
       </c>
       <c r="K256" t="n">
-        <v>2.84185</v>
+        <v>2.82271</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -11457,16 +11457,16 @@
         <v>41000</v>
       </c>
       <c r="B257" t="n">
-        <v>8.754365966609857</v>
+        <v>8.775548113920273</v>
       </c>
       <c r="C257" t="n">
-        <v>8.53559925646965</v>
+        <v>8.535284009520282</v>
       </c>
       <c r="D257" t="n">
-        <v>5.086253479206793</v>
+        <v>5.100009691201479</v>
       </c>
       <c r="E257" t="n">
-        <v>7.466457257460601</v>
+        <v>7.466423237190134</v>
       </c>
       <c r="F257" t="n">
         <v>12.20632970664188</v>
@@ -11484,7 +11484,7 @@
         <v>6.14174</v>
       </c>
       <c r="K257" t="n">
-        <v>2.90973</v>
+        <v>2.89065</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -11500,16 +11500,16 @@
         <v>41030</v>
       </c>
       <c r="B258" t="n">
-        <v>11.90156908493525</v>
+        <v>11.91738360216326</v>
       </c>
       <c r="C258" t="n">
-        <v>11.74851831464241</v>
+        <v>11.74069477279978</v>
       </c>
       <c r="D258" t="n">
-        <v>8.754092251403932</v>
+        <v>8.778888600920908</v>
       </c>
       <c r="E258" t="n">
-        <v>7.926013622677064</v>
+        <v>7.926019595618006</v>
       </c>
       <c r="F258" t="n">
         <v>17.68569205895112</v>
@@ -11527,7 +11527,7 @@
         <v>6.59556</v>
       </c>
       <c r="K258" t="n">
-        <v>3.84219</v>
+        <v>3.81325</v>
       </c>
       <c r="L258" t="inlineStr">
         <is>
@@ -11543,16 +11543,16 @@
         <v>41061</v>
       </c>
       <c r="B259" t="n">
-        <v>11.47480686580518</v>
+        <v>11.45513457286691</v>
       </c>
       <c r="C259" t="n">
-        <v>9.094922207882083</v>
+        <v>9.107047029853167</v>
       </c>
       <c r="D259" t="n">
-        <v>7.807816342267415</v>
+        <v>7.828146284276905</v>
       </c>
       <c r="E259" t="n">
-        <v>8.253994766143569</v>
+        <v>8.254026103296329</v>
       </c>
       <c r="F259" t="n">
         <v>17.49773369594201</v>
@@ -11570,7 +11570,7 @@
         <v>6.63022</v>
       </c>
       <c r="K259" t="n">
-        <v>3.97979</v>
+        <v>3.96162</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -11586,16 +11586,16 @@
         <v>41091</v>
       </c>
       <c r="B260" t="n">
-        <v>8.844225206517887</v>
+        <v>8.847578160509029</v>
       </c>
       <c r="C260" t="n">
-        <v>9.295815823383791</v>
+        <v>9.298099931962135</v>
       </c>
       <c r="D260" t="n">
-        <v>8.123120495041869</v>
+        <v>8.090050773747359</v>
       </c>
       <c r="E260" t="n">
-        <v>8.656392302274263</v>
+        <v>8.656429217674088</v>
       </c>
       <c r="F260" t="n">
         <v>17.72885720549804</v>
@@ -11613,7 +11613,7 @@
         <v>6.9076</v>
       </c>
       <c r="K260" t="n">
-        <v>4.34381</v>
+        <v>4.32594</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>41122</v>
       </c>
       <c r="B261" t="n">
-        <v>12.53996053805857</v>
+        <v>12.52789333058086</v>
       </c>
       <c r="C261" t="n">
-        <v>10.30734806766995</v>
+        <v>10.2897228809645</v>
       </c>
       <c r="D261" t="n">
-        <v>5.616713620101832</v>
+        <v>5.62080953460331</v>
       </c>
       <c r="E261" t="n">
-        <v>10.39434974573929</v>
+        <v>10.39439846956214</v>
       </c>
       <c r="F261" t="n">
         <v>16.47965838208145</v>
@@ -11656,7 +11656,7 @@
         <v>5.46906</v>
       </c>
       <c r="K261" t="n">
-        <v>5.08579</v>
+        <v>5.06837</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -11672,16 +11672,16 @@
         <v>41153</v>
       </c>
       <c r="B262" t="n">
-        <v>6.772424333664695</v>
+        <v>6.794819372919569</v>
       </c>
       <c r="C262" t="n">
-        <v>6.466904613596713</v>
+        <v>6.499091993038908</v>
       </c>
       <c r="D262" t="n">
-        <v>-0.7646328559841487</v>
+        <v>-0.808066316874001</v>
       </c>
       <c r="E262" t="n">
-        <v>8.715874651411282</v>
+        <v>8.715868073086641</v>
       </c>
       <c r="F262" t="n">
         <v>7.270312491495079</v>
@@ -11699,7 +11699,7 @@
         <v>4.06079</v>
       </c>
       <c r="K262" t="n">
-        <v>5.31228</v>
+        <v>5.30583</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -11715,16 +11715,16 @@
         <v>41183</v>
       </c>
       <c r="B263" t="n">
-        <v>9.086825540356624</v>
+        <v>9.091524606122858</v>
       </c>
       <c r="C263" t="n">
-        <v>7.429461707157436</v>
+        <v>7.444808353748456</v>
       </c>
       <c r="D263" t="n">
-        <v>3.204845943068424</v>
+        <v>3.171597996391995</v>
       </c>
       <c r="E263" t="n">
-        <v>8.725891307995104</v>
+        <v>8.72585841107254</v>
       </c>
       <c r="F263" t="n">
         <v>11.03570222020211</v>
@@ -11742,7 +11742,7 @@
         <v>3.97938</v>
       </c>
       <c r="K263" t="n">
-        <v>4.77356</v>
+        <v>4.74587</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -11758,16 +11758,16 @@
         <v>41214</v>
       </c>
       <c r="B264" t="n">
-        <v>13.48609143894739</v>
+        <v>13.42001798397252</v>
       </c>
       <c r="C264" t="n">
-        <v>11.25205955323327</v>
+        <v>11.20178098345921</v>
       </c>
       <c r="D264" t="n">
-        <v>4.643646638323262</v>
+        <v>4.648802027950349</v>
       </c>
       <c r="E264" t="n">
-        <v>6.332360751454247</v>
+        <v>6.332274575544106</v>
       </c>
       <c r="F264" t="n">
         <v>9.952348806129585</v>
@@ -11785,7 +11785,7 @@
         <v>3.80671</v>
       </c>
       <c r="K264" t="n">
-        <v>5.34623</v>
+        <v>5.32966</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -11801,16 +11801,16 @@
         <v>41244</v>
       </c>
       <c r="B265" t="n">
-        <v>8.076507004215493</v>
+        <v>8.053405443130179</v>
       </c>
       <c r="C265" t="n">
-        <v>5.793623313710539</v>
+        <v>5.780543360517076</v>
       </c>
       <c r="D265" t="n">
-        <v>2.715930781201892</v>
+        <v>2.702085773095564</v>
       </c>
       <c r="E265" t="n">
-        <v>7.363186389467602</v>
+        <v>7.363131018683422</v>
       </c>
       <c r="F265" t="n">
         <v>10.55252329897978</v>
@@ -11828,7 +11828,7 @@
         <v>3.70125</v>
       </c>
       <c r="K265" t="n">
-        <v>4.5891</v>
+        <v>4.56155</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -11844,16 +11844,16 @@
         <v>41275</v>
       </c>
       <c r="B266" t="n">
-        <v>2.556256505892263</v>
+        <v>2.579921922610406</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.2139824722959038</v>
+        <v>-0.1720113442837068</v>
       </c>
       <c r="D266" t="n">
-        <v>2.17198178175162</v>
+        <v>2.191005721831707</v>
       </c>
       <c r="E266" t="n">
-        <v>12.01074068525536</v>
+        <v>12.01076564876233</v>
       </c>
       <c r="F266" t="n">
         <v>15.53028477810436</v>
@@ -11871,7 +11871,7 @@
         <v>2.88285</v>
       </c>
       <c r="K266" t="n">
-        <v>4.72473</v>
+        <v>4.70779</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -11887,16 +11887,16 @@
         <v>41306</v>
       </c>
       <c r="B267" t="n">
-        <v>5.068583232782187</v>
+        <v>5.096032670163475</v>
       </c>
       <c r="C267" t="n">
-        <v>1.67405104307814</v>
+        <v>1.684288244585841</v>
       </c>
       <c r="D267" t="n">
-        <v>3.455574794517191</v>
+        <v>3.459306320390088</v>
       </c>
       <c r="E267" t="n">
-        <v>13.52823197301927</v>
+        <v>13.52825553722572</v>
       </c>
       <c r="F267" t="n">
         <v>17.82535593890307</v>
@@ -11914,7 +11914,7 @@
         <v>2.68754</v>
       </c>
       <c r="K267" t="n">
-        <v>4.55505</v>
+        <v>4.53814</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -11930,16 +11930,16 @@
         <v>41334</v>
       </c>
       <c r="B268" t="n">
-        <v>5.845067646233892</v>
+        <v>5.830496752971093</v>
       </c>
       <c r="C268" t="n">
-        <v>3.418202156246997</v>
+        <v>3.399161156080011</v>
       </c>
       <c r="D268" t="n">
-        <v>0.8997297575554342</v>
+        <v>0.9113234590413022</v>
       </c>
       <c r="E268" t="n">
-        <v>15.10205865561842</v>
+        <v>15.10208977683916</v>
       </c>
       <c r="F268" t="n">
         <v>16.5171747870255</v>
@@ -11957,7 +11957,7 @@
         <v>2.18414</v>
       </c>
       <c r="K268" t="n">
-        <v>4.77573</v>
+        <v>4.75904</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -11973,16 +11973,16 @@
         <v>41365</v>
       </c>
       <c r="B269" t="n">
-        <v>2.33927506308429</v>
+        <v>2.376766202200109</v>
       </c>
       <c r="C269" t="n">
-        <v>0.7288508665144633</v>
+        <v>0.7325226388983808</v>
       </c>
       <c r="D269" t="n">
-        <v>2.934988295179086</v>
+        <v>2.94822346501713</v>
       </c>
       <c r="E269" t="n">
-        <v>10.14349311026617</v>
+        <v>10.14345158240917</v>
       </c>
       <c r="F269" t="n">
         <v>12.42473303809164</v>
@@ -12000,7 +12000,7 @@
         <v>2.61229</v>
       </c>
       <c r="K269" t="n">
-        <v>4.46598</v>
+        <v>4.44911</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -12016,16 +12016,16 @@
         <v>41395</v>
       </c>
       <c r="B270" t="n">
-        <v>2.66094177937819</v>
+        <v>2.696355900977077</v>
       </c>
       <c r="C270" t="n">
-        <v>0.3396648971739413</v>
+        <v>0.3545096258865899</v>
       </c>
       <c r="D270" t="n">
-        <v>-1.542067343565623</v>
+        <v>-1.523749087716697</v>
       </c>
       <c r="E270" t="n">
-        <v>11.78201516927002</v>
+        <v>11.78199293836488</v>
       </c>
       <c r="F270" t="n">
         <v>10.03053325047622</v>
@@ -12043,7 +12043,7 @@
         <v>2.24574</v>
       </c>
       <c r="K270" t="n">
-        <v>4.23569</v>
+        <v>4.22913</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -12059,16 +12059,16 @@
         <v>41426</v>
       </c>
       <c r="B271" t="n">
-        <v>4.161722738120677</v>
+        <v>4.119065691867108</v>
       </c>
       <c r="C271" t="n">
-        <v>3.262635211183862</v>
+        <v>3.25651038223469</v>
       </c>
       <c r="D271" t="n">
-        <v>-1.201865723001461</v>
+        <v>-1.179907134286184</v>
       </c>
       <c r="E271" t="n">
-        <v>12.72401434568446</v>
+        <v>12.72401977239421</v>
       </c>
       <c r="F271" t="n">
         <v>12.23517566241541</v>
@@ -12086,7 +12086,7 @@
         <v>2.03146</v>
       </c>
       <c r="K271" t="n">
-        <v>4.30342</v>
+        <v>4.28699</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12102,16 +12102,16 @@
         <v>41456</v>
       </c>
       <c r="B272" t="n">
-        <v>3.855793088559722</v>
+        <v>3.814978438828942</v>
       </c>
       <c r="C272" t="n">
-        <v>2.830105124392079</v>
+        <v>2.815925892008875</v>
       </c>
       <c r="D272" t="n">
-        <v>-2.903159161760305</v>
+        <v>-2.919732808547348</v>
       </c>
       <c r="E272" t="n">
-        <v>12.48945518346805</v>
+        <v>12.48948976816433</v>
       </c>
       <c r="F272" t="n">
         <v>9.671828508600445</v>
@@ -12129,7 +12129,7 @@
         <v>2.06698</v>
       </c>
       <c r="K272" t="n">
-        <v>3.8382</v>
+        <v>3.82153</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -12145,16 +12145,16 @@
         <v>41487</v>
       </c>
       <c r="B273" t="n">
-        <v>2.056384974819991</v>
+        <v>2.047042641535346</v>
       </c>
       <c r="C273" t="n">
-        <v>2.697177512147775</v>
+        <v>2.692054600863947</v>
       </c>
       <c r="D273" t="n">
-        <v>-0.1046646738985912</v>
+        <v>-0.1081748410978634</v>
       </c>
       <c r="E273" t="n">
-        <v>12.15007242674164</v>
+        <v>12.15013066287893</v>
       </c>
       <c r="F273" t="n">
         <v>11.84107940076478</v>
@@ -12172,7 +12172,7 @@
         <v>2.86969</v>
       </c>
       <c r="K273" t="n">
-        <v>3.01134</v>
+        <v>2.99413</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -12188,16 +12188,16 @@
         <v>41518</v>
       </c>
       <c r="B274" t="n">
-        <v>-0.1484509202047457</v>
+        <v>-0.1452191961638039</v>
       </c>
       <c r="C274" t="n">
-        <v>0.2330599416900725</v>
+        <v>0.2274607554510366</v>
       </c>
       <c r="D274" t="n">
-        <v>0.04539309655713364</v>
+        <v>0.03636525037198357</v>
       </c>
       <c r="E274" t="n">
-        <v>11.91688033205118</v>
+        <v>11.91692715589603</v>
       </c>
       <c r="F274" t="n">
         <v>12.17544609466823</v>
@@ -12215,7 +12215,7 @@
         <v>2.13082</v>
       </c>
       <c r="K274" t="n">
-        <v>2.6877</v>
+        <v>2.66056</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -12231,16 +12231,16 @@
         <v>41548</v>
       </c>
       <c r="B275" t="n">
-        <v>-0.3286722752122051</v>
+        <v>-0.3226011117121175</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.4541003154710066</v>
+        <v>-0.4743053684571175</v>
       </c>
       <c r="D275" t="n">
-        <v>-2.032879633674178</v>
+        <v>-2.016582468235495</v>
       </c>
       <c r="E275" t="n">
-        <v>10.8937726424023</v>
+        <v>10.89383086751729</v>
       </c>
       <c r="F275" t="n">
         <v>8.914445192139819</v>
@@ -12258,7 +12258,7 @@
         <v>2.58216</v>
       </c>
       <c r="K275" t="n">
-        <v>2.77453</v>
+        <v>2.76722</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -12274,16 +12274,16 @@
         <v>41579</v>
       </c>
       <c r="B276" t="n">
-        <v>-4.032698912550414</v>
+        <v>-3.992049910730244</v>
       </c>
       <c r="C276" t="n">
-        <v>-4.146537689144647</v>
+        <v>-4.139637718789269</v>
       </c>
       <c r="D276" t="n">
-        <v>-3.712249861182071</v>
+        <v>-3.723145496269586</v>
       </c>
       <c r="E276" t="n">
-        <v>8.913984306999655</v>
+        <v>8.913969278815603</v>
       </c>
       <c r="F276" t="n">
         <v>4.409863943221204</v>
@@ -12301,7 +12301,7 @@
         <v>2.63791</v>
       </c>
       <c r="K276" t="n">
-        <v>2.23296</v>
+        <v>2.21556</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -12317,16 +12317,16 @@
         <v>41609</v>
       </c>
       <c r="B277" t="n">
-        <v>-3.382154795313663</v>
+        <v>-3.362498133450831</v>
       </c>
       <c r="C277" t="n">
-        <v>-3.711510848265176</v>
+        <v>-3.708749383972754</v>
       </c>
       <c r="D277" t="n">
-        <v>-3.394101114323578</v>
+        <v>-3.413410715055731</v>
       </c>
       <c r="E277" t="n">
-        <v>10.77595309634778</v>
+        <v>10.77602628295615</v>
       </c>
       <c r="F277" t="n">
         <v>8.827771897887482</v>
@@ -12344,7 +12344,7 @@
         <v>2.55237</v>
       </c>
       <c r="K277" t="n">
-        <v>2.58046</v>
+        <v>2.56336</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -12360,16 +12360,16 @@
         <v>41640</v>
       </c>
       <c r="B278" t="n">
-        <v>3.318093219278317</v>
+        <v>3.265641300383892</v>
       </c>
       <c r="C278" t="n">
-        <v>3.628312236657072</v>
+        <v>3.580882252244377</v>
       </c>
       <c r="D278" t="n">
-        <v>-1.565652807992701</v>
+        <v>-1.601373848191012</v>
       </c>
       <c r="E278" t="n">
-        <v>6.127342609782849</v>
+        <v>6.127333914894995</v>
       </c>
       <c r="F278" t="n">
         <v>4.402028610889386</v>
@@ -12387,7 +12387,7 @@
         <v>3.58306</v>
       </c>
       <c r="K278" t="n">
-        <v>2.96253</v>
+        <v>2.94574</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12403,16 +12403,16 @@
         <v>41671</v>
       </c>
       <c r="B279" t="n">
-        <v>-0.1599778575878674</v>
+        <v>-0.1306070992246777</v>
       </c>
       <c r="C279" t="n">
-        <v>0.4683003423314736</v>
+        <v>0.4864095844934191</v>
       </c>
       <c r="D279" t="n">
-        <v>-0.2971120966861363</v>
+        <v>-0.3172282600339416</v>
       </c>
       <c r="E279" t="n">
-        <v>4.003005903496204</v>
+        <v>4.002994109996605</v>
       </c>
       <c r="F279" t="n">
         <v>2.954617429174844</v>
@@ -12430,7 +12430,7 @@
         <v>3.1055</v>
       </c>
       <c r="K279" t="n">
-        <v>2.34661</v>
+        <v>2.32939</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -12446,16 +12446,16 @@
         <v>41699</v>
       </c>
       <c r="B280" t="n">
-        <v>-1.885369579831797</v>
+        <v>-1.843929334876815</v>
       </c>
       <c r="C280" t="n">
-        <v>-2.179190984307933</v>
+        <v>-2.135207692009111</v>
       </c>
       <c r="D280" t="n">
-        <v>-0.7808962728500957</v>
+        <v>-0.7898702056708728</v>
       </c>
       <c r="E280" t="n">
-        <v>0.4846270127703445</v>
+        <v>0.4845741541953164</v>
       </c>
       <c r="F280" t="n">
         <v>-1.198779532100924</v>
@@ -12473,7 +12473,7 @@
         <v>3.13292</v>
       </c>
       <c r="K280" t="n">
-        <v>2.32203</v>
+        <v>2.3049</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -12489,16 +12489,16 @@
         <v>41730</v>
       </c>
       <c r="B281" t="n">
-        <v>2.164460956483194</v>
+        <v>2.171158758178149</v>
       </c>
       <c r="C281" t="n">
-        <v>1.86417755022954</v>
+        <v>1.84813795261134</v>
       </c>
       <c r="D281" t="n">
-        <v>-3.077612448370992</v>
+        <v>-3.085024072358644</v>
       </c>
       <c r="E281" t="n">
-        <v>4.006861595270306</v>
+        <v>4.006806605803592</v>
       </c>
       <c r="F281" t="n">
         <v>-0.1172855387057581</v>
@@ -12516,7 +12516,7 @@
         <v>2.52866</v>
       </c>
       <c r="K281" t="n">
-        <v>2.23795</v>
+        <v>2.22073</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -12532,16 +12532,16 @@
         <v>41760</v>
       </c>
       <c r="B282" t="n">
-        <v>1.180664877006898</v>
+        <v>1.197298916011347</v>
       </c>
       <c r="C282" t="n">
-        <v>1.617144724619091</v>
+        <v>1.610500337961418</v>
       </c>
       <c r="D282" t="n">
-        <v>0.2542126345234541</v>
+        <v>0.2793240961300736</v>
       </c>
       <c r="E282" t="n">
-        <v>1.010027733445407</v>
+        <v>1.009974626765597</v>
       </c>
       <c r="F282" t="n">
         <v>1.16762326719495</v>
@@ -12559,7 +12559,7 @@
         <v>2.46732</v>
       </c>
       <c r="K282" t="n">
-        <v>2.43624</v>
+        <v>2.40975</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -12575,16 +12575,16 @@
         <v>41791</v>
       </c>
       <c r="B283" t="n">
-        <v>1.172419941780611</v>
+        <v>1.134989060973268</v>
       </c>
       <c r="C283" t="n">
-        <v>0.556347529099166</v>
+        <v>0.561996342347526</v>
       </c>
       <c r="D283" t="n">
-        <v>0.09277845684152464</v>
+        <v>0.1375745545996176</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.1206534886659782</v>
+        <v>-0.1206838197190696</v>
       </c>
       <c r="F283" t="n">
         <v>0.6583366471794694</v>
@@ -12602,7 +12602,7 @@
         <v>1.71547</v>
       </c>
       <c r="K283" t="n">
-        <v>2.29109</v>
+        <v>2.27424</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -12618,16 +12618,16 @@
         <v>41821</v>
       </c>
       <c r="B284" t="n">
-        <v>2.579690171681204</v>
+        <v>2.550549641465572</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.04544101648337184</v>
+        <v>-0.05114059188370268</v>
       </c>
       <c r="D284" t="n">
-        <v>2.835910383148899</v>
+        <v>2.833515296899369</v>
       </c>
       <c r="E284" t="n">
-        <v>0.7864773630498867</v>
+        <v>0.7864509663510377</v>
       </c>
       <c r="F284" t="n">
         <v>3.647207409992936</v>
@@ -12645,7 +12645,7 @@
         <v>1.26785</v>
       </c>
       <c r="K284" t="n">
-        <v>2.46422</v>
+        <v>2.4381</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -12661,16 +12661,16 @@
         <v>41852</v>
       </c>
       <c r="B285" t="n">
-        <v>0.4466689080444786</v>
+        <v>0.4642319479377877</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.7733935407845172</v>
+        <v>-0.7702412881767651</v>
       </c>
       <c r="D285" t="n">
-        <v>-1.462483705154205</v>
+        <v>-1.480735895665997</v>
       </c>
       <c r="E285" t="n">
-        <v>0.2818449199872175</v>
+        <v>0.281810487063372</v>
       </c>
       <c r="F285" t="n">
         <v>-2.393965286651845</v>
@@ -12688,7 +12688,7 @@
         <v>0.55138</v>
       </c>
       <c r="K285" t="n">
-        <v>2.99924</v>
+        <v>2.98309</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -12704,16 +12704,16 @@
         <v>41883</v>
       </c>
       <c r="B286" t="n">
-        <v>4.668690803169739</v>
+        <v>4.656051443824438</v>
       </c>
       <c r="C286" t="n">
-        <v>1.855249216741117</v>
+        <v>1.848461977898563</v>
       </c>
       <c r="D286" t="n">
-        <v>2.917763949720853</v>
+        <v>2.939898054843559</v>
       </c>
       <c r="E286" t="n">
-        <v>1.268321605814093</v>
+        <v>1.268320953497915</v>
       </c>
       <c r="F286" t="n">
         <v>4.181582055819955</v>
@@ -12731,7 +12731,7 @@
         <v>1.35613</v>
       </c>
       <c r="K286" t="n">
-        <v>3.02513</v>
+        <v>3.0093</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -12747,16 +12747,16 @@
         <v>41913</v>
       </c>
       <c r="B287" t="n">
-        <v>5.844541756931765</v>
+        <v>5.816829185367567</v>
       </c>
       <c r="C287" t="n">
-        <v>3.935159839686242</v>
+        <v>3.92591317371529</v>
       </c>
       <c r="D287" t="n">
-        <v>4.804874820454774</v>
+        <v>4.867021028146512</v>
       </c>
       <c r="E287" t="n">
-        <v>2.669709925236141</v>
+        <v>2.669730265025017</v>
       </c>
       <c r="F287" t="n">
         <v>8.062522233907398</v>
@@ -12774,7 +12774,7 @@
         <v>1.26572</v>
       </c>
       <c r="K287" t="n">
-        <v>3.27745</v>
+        <v>3.25211</v>
       </c>
       <c r="L287" t="inlineStr">
         <is>
@@ -12790,16 +12790,16 @@
         <v>41944</v>
       </c>
       <c r="B288" t="n">
-        <v>3.499862306200563</v>
+        <v>3.48002469918931</v>
       </c>
       <c r="C288" t="n">
-        <v>2.943995754343964</v>
+        <v>2.918237682360569</v>
       </c>
       <c r="D288" t="n">
-        <v>2.074469503879439</v>
+        <v>2.087979816225194</v>
       </c>
       <c r="E288" t="n">
-        <v>3.353930139421779</v>
+        <v>3.35396067489997</v>
       </c>
       <c r="F288" t="n">
         <v>5.833923359984761</v>
@@ -12817,7 +12817,7 @@
         <v>0.52284</v>
       </c>
       <c r="K288" t="n">
-        <v>3.71596</v>
+        <v>3.69143</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -12833,16 +12833,16 @@
         <v>41974</v>
       </c>
       <c r="B289" t="n">
-        <v>6.861132552923221</v>
+        <v>6.846427578741032</v>
       </c>
       <c r="C289" t="n">
-        <v>6.017091638230632</v>
+        <v>5.974516893043691</v>
       </c>
       <c r="D289" t="n">
-        <v>2.156106685775772</v>
+        <v>2.170741939744758</v>
       </c>
       <c r="E289" t="n">
-        <v>3.800715758812645</v>
+        <v>3.800784233110255</v>
       </c>
       <c r="F289" t="n">
         <v>8.274234768504174</v>
@@ -12860,7 +12860,7 @@
         <v>-0.27212</v>
       </c>
       <c r="K289" t="n">
-        <v>3.01489</v>
+        <v>2.99915</v>
       </c>
       <c r="L289" t="inlineStr">
         <is>
@@ -12876,16 +12876,16 @@
         <v>42005</v>
       </c>
       <c r="B290" t="n">
-        <v>0.8608783441057311</v>
+        <v>0.8703219683678931</v>
       </c>
       <c r="C290" t="n">
-        <v>1.156307902309517</v>
+        <v>1.18739072392462</v>
       </c>
       <c r="D290" t="n">
-        <v>-2.121339799956545</v>
+        <v>-2.178993379242478</v>
       </c>
       <c r="E290" t="n">
-        <v>2.41012281723274</v>
+        <v>2.410091492885913</v>
       </c>
       <c r="F290" t="n">
         <v>-0.5598222880354942</v>
@@ -12903,7 +12903,7 @@
         <v>-0.03102</v>
       </c>
       <c r="K290" t="n">
-        <v>3.40386</v>
+        <v>3.38855</v>
       </c>
       <c r="L290" t="inlineStr">
         <is>
@@ -12919,16 +12919,16 @@
         <v>42036</v>
       </c>
       <c r="B291" t="n">
-        <v>3.210190005372993</v>
+        <v>3.281328130865213</v>
       </c>
       <c r="C291" t="n">
-        <v>3.30600599970563</v>
+        <v>3.358217291846421</v>
       </c>
       <c r="D291" t="n">
-        <v>-1.156377772779105</v>
+        <v>-1.218236114123461</v>
       </c>
       <c r="E291" t="n">
-        <v>3.624570274770345</v>
+        <v>3.624568095563885</v>
       </c>
       <c r="F291" t="n">
         <v>1.206347769112126</v>
@@ -12946,7 +12946,7 @@
         <v>-0.23569</v>
       </c>
       <c r="K291" t="n">
-        <v>3.76809</v>
+        <v>3.75317</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -12962,16 +12962,16 @@
         <v>42064</v>
       </c>
       <c r="B292" t="n">
-        <v>6.277806644191841</v>
+        <v>6.312752113995512</v>
       </c>
       <c r="C292" t="n">
-        <v>5.589130105142059</v>
+        <v>5.59111915120567</v>
       </c>
       <c r="D292" t="n">
-        <v>2.238158368864673</v>
+        <v>2.202432851617164</v>
       </c>
       <c r="E292" t="n">
-        <v>4.889303273598622</v>
+        <v>4.889292875670015</v>
       </c>
       <c r="F292" t="n">
         <v>6.466415316239305</v>
@@ -12989,7 +12989,7 @@
         <v>-0.73882</v>
       </c>
       <c r="K292" t="n">
-        <v>3.10982</v>
+        <v>3.08498</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -13005,16 +13005,16 @@
         <v>42095</v>
       </c>
       <c r="B293" t="n">
-        <v>3.527654180890272</v>
+        <v>3.54028262678816</v>
       </c>
       <c r="C293" t="n">
-        <v>2.383290190843024</v>
+        <v>2.405172207760242</v>
       </c>
       <c r="D293" t="n">
-        <v>2.540214623218628</v>
+        <v>2.540707995062874</v>
       </c>
       <c r="E293" t="n">
-        <v>4.245931878705367</v>
+        <v>4.245941403283382</v>
       </c>
       <c r="F293" t="n">
         <v>6.821875781081577</v>
@@ -13032,7 +13032,7 @@
         <v>-0.52376</v>
       </c>
       <c r="K293" t="n">
-        <v>3.74181</v>
+        <v>3.71758</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -13048,16 +13048,16 @@
         <v>42125</v>
       </c>
       <c r="B294" t="n">
-        <v>8.354093925716732</v>
+        <v>8.364430753678388</v>
       </c>
       <c r="C294" t="n">
-        <v>5.900804410734906</v>
+        <v>5.917596111283618</v>
       </c>
       <c r="D294" t="n">
-        <v>4.171452749961602</v>
+        <v>4.19879801967884</v>
       </c>
       <c r="E294" t="n">
-        <v>6.248583344198799</v>
+        <v>6.248609955591999</v>
       </c>
       <c r="F294" t="n">
         <v>11.54880351145597</v>
@@ -13075,7 +13075,7 @@
         <v>-0.8229300000000001</v>
       </c>
       <c r="K294" t="n">
-        <v>3.37235</v>
+        <v>3.34821</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -13091,16 +13091,16 @@
         <v>42156</v>
       </c>
       <c r="B295" t="n">
-        <v>6.68404994040348</v>
+        <v>6.603563518507816</v>
       </c>
       <c r="C295" t="n">
-        <v>5.378685150165019</v>
+        <v>5.380382504055237</v>
       </c>
       <c r="D295" t="n">
-        <v>6.0606056224495</v>
+        <v>6.103420103214785</v>
       </c>
       <c r="E295" t="n">
-        <v>6.940381522591776</v>
+        <v>6.940420024324956</v>
       </c>
       <c r="F295" t="n">
         <v>15.08537326920969</v>
@@ -13118,7 +13118,7 @@
         <v>-0.04685</v>
       </c>
       <c r="K295" t="n">
-        <v>3.78253</v>
+        <v>3.75884</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -13134,16 +13134,16 @@
         <v>42186</v>
       </c>
       <c r="B296" t="n">
-        <v>5.198063790070306</v>
+        <v>5.146088052746856</v>
       </c>
       <c r="C296" t="n">
-        <v>5.712291099233924</v>
+        <v>5.694769758473828</v>
       </c>
       <c r="D296" t="n">
-        <v>0.1312825219072389</v>
+        <v>0.1233559846064436</v>
       </c>
       <c r="E296" t="n">
-        <v>4.677126454987945</v>
+        <v>4.677146057702308</v>
       </c>
       <c r="F296" t="n">
         <v>5.257264220796709</v>
@@ -13161,7 +13161,7 @@
         <v>0.28549</v>
       </c>
       <c r="K296" t="n">
-        <v>3.57969</v>
+        <v>3.57474</v>
       </c>
       <c r="L296" t="inlineStr">
         <is>
@@ -13177,16 +13177,16 @@
         <v>42217</v>
       </c>
       <c r="B297" t="n">
-        <v>3.8610460343939</v>
+        <v>3.867392647400081</v>
       </c>
       <c r="C297" t="n">
-        <v>4.013056291227746</v>
+        <v>3.992438161147338</v>
       </c>
       <c r="D297" t="n">
-        <v>2.992286037782366</v>
+        <v>2.967825400918223</v>
       </c>
       <c r="E297" t="n">
-        <v>4.089138194572528</v>
+        <v>4.089127579249552</v>
       </c>
       <c r="F297" t="n">
         <v>5.919019585052454</v>
@@ -13204,7 +13204,7 @@
         <v>0.32236</v>
       </c>
       <c r="K297" t="n">
-        <v>3.53852</v>
+        <v>3.52399</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -13220,16 +13220,16 @@
         <v>42248</v>
       </c>
       <c r="B298" t="n">
-        <v>2.429169381656648</v>
+        <v>2.44976264031016</v>
       </c>
       <c r="C298" t="n">
-        <v>1.072207497751942</v>
+        <v>1.098872092463354</v>
       </c>
       <c r="D298" t="n">
-        <v>0.418796172969027</v>
+        <v>0.4230466452775472</v>
       </c>
       <c r="E298" t="n">
-        <v>3.046329766948364</v>
+        <v>3.046340916625323</v>
       </c>
       <c r="F298" t="n">
         <v>3.245793136343056</v>
@@ -13247,7 +13247,7 @@
         <v>0.36145</v>
       </c>
       <c r="K298" t="n">
-        <v>3.37813</v>
+        <v>3.36375</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -13263,16 +13263,16 @@
         <v>42278</v>
       </c>
       <c r="B299" t="n">
-        <v>3.286348374986403</v>
+        <v>3.291224232475498</v>
       </c>
       <c r="C299" t="n">
-        <v>2.78786568076459</v>
+        <v>2.773498564567589</v>
       </c>
       <c r="D299" t="n">
-        <v>1.81275192177297</v>
+        <v>1.846907775731199</v>
       </c>
       <c r="E299" t="n">
-        <v>2.815479282391764</v>
+        <v>2.815456586348564</v>
       </c>
       <c r="F299" t="n">
         <v>4.355258956633312</v>
@@ -13290,7 +13290,7 @@
         <v>-0.01045</v>
       </c>
       <c r="K299" t="n">
-        <v>3.25598</v>
+        <v>3.24151</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13306,16 +13306,16 @@
         <v>42309</v>
       </c>
       <c r="B300" t="n">
-        <v>4.538876253491964</v>
+        <v>4.510347072369325</v>
       </c>
       <c r="C300" t="n">
-        <v>3.698847247969517</v>
+        <v>3.645309449790268</v>
       </c>
       <c r="D300" t="n">
-        <v>3.839018112116044</v>
+        <v>3.86502516124001</v>
       </c>
       <c r="E300" t="n">
-        <v>3.740187148604912</v>
+        <v>3.740198807537864</v>
       </c>
       <c r="F300" t="n">
         <v>8.065503164147758</v>
@@ -13333,7 +13333,7 @@
         <v>0.9801800000000001</v>
       </c>
       <c r="K300" t="n">
-        <v>2.78968</v>
+        <v>2.77499</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         <v>42339</v>
       </c>
       <c r="B301" t="n">
-        <v>4.784019757239144</v>
+        <v>4.777435048200185</v>
       </c>
       <c r="C301" t="n">
-        <v>3.185370017392564</v>
+        <v>3.143618793725067</v>
       </c>
       <c r="D301" t="n">
-        <v>5.177808868506628</v>
+        <v>5.222869169428401</v>
       </c>
       <c r="E301" t="n">
-        <v>1.878186331831588</v>
+        <v>1.878180879520053</v>
       </c>
       <c r="F301" t="n">
         <v>8.795937664020936</v>
@@ -13376,7 +13376,7 @@
         <v>1.95792</v>
       </c>
       <c r="K301" t="n">
-        <v>3.53027</v>
+        <v>3.51616</v>
       </c>
       <c r="L301" t="inlineStr">
         <is>
@@ -13392,16 +13392,16 @@
         <v>42370</v>
       </c>
       <c r="B302" t="n">
-        <v>5.386305370842148</v>
+        <v>5.334916214677055</v>
       </c>
       <c r="C302" t="n">
-        <v>3.361635797076379</v>
+        <v>3.369178373155801</v>
       </c>
       <c r="D302" t="n">
-        <v>4.134328882951133</v>
+        <v>4.127986508570469</v>
       </c>
       <c r="E302" t="n">
-        <v>1.198764076513203</v>
+        <v>1.198734546114855</v>
       </c>
       <c r="F302" t="n">
         <v>4.938556867702859</v>
@@ -13419,7 +13419,7 @@
         <v>1.47842</v>
       </c>
       <c r="K302" t="n">
-        <v>2.97354</v>
+        <v>2.94975</v>
       </c>
       <c r="L302" t="inlineStr">
         <is>
@@ -13435,16 +13435,16 @@
         <v>42401</v>
       </c>
       <c r="B303" t="n">
-        <v>5.156612191450072</v>
+        <v>5.217049398442186</v>
       </c>
       <c r="C303" t="n">
-        <v>3.154459614347771</v>
+        <v>3.225920229203338</v>
       </c>
       <c r="D303" t="n">
-        <v>1.698277029242101</v>
+        <v>1.658983589003249</v>
       </c>
       <c r="E303" t="n">
-        <v>3.115006146620658</v>
+        <v>3.11497118489612</v>
       </c>
       <c r="F303" t="n">
         <v>3.542414888719758</v>
@@ -13462,7 +13462,7 @@
         <v>1.99517</v>
       </c>
       <c r="K303" t="n">
-        <v>2.43593</v>
+        <v>2.4116</v>
       </c>
       <c r="L303" t="inlineStr">
         <is>
@@ -13478,16 +13478,16 @@
         <v>42430</v>
       </c>
       <c r="B304" t="n">
-        <v>0.9887337248025263</v>
+        <v>1.064900087467269</v>
       </c>
       <c r="C304" t="n">
-        <v>0.5057348458960664</v>
+        <v>0.5369294959363113</v>
       </c>
       <c r="D304" t="n">
-        <v>-0.5989351588020497</v>
+        <v>-0.6417798445928935</v>
       </c>
       <c r="E304" t="n">
-        <v>3.856288611796366</v>
+        <v>3.856279360919346</v>
       </c>
       <c r="F304" t="n">
         <v>2.510222301201392</v>
@@ -13505,7 +13505,7 @@
         <v>2.7326</v>
       </c>
       <c r="K304" t="n">
-        <v>3.11566</v>
+        <v>3.10148</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -13521,16 +13521,16 @@
         <v>42461</v>
       </c>
       <c r="B305" t="n">
-        <v>1.050068259259773</v>
+        <v>1.074812274395387</v>
       </c>
       <c r="C305" t="n">
-        <v>0.1629277491386416</v>
+        <v>0.1763518858134416</v>
       </c>
       <c r="D305" t="n">
-        <v>2.192272630448699</v>
+        <v>2.205044542074619</v>
       </c>
       <c r="E305" t="n">
-        <v>1.984210598915692</v>
+        <v>1.984202584885142</v>
       </c>
       <c r="F305" t="n">
         <v>4.427161707563054</v>
@@ -13548,7 +13548,7 @@
         <v>2.49373</v>
       </c>
       <c r="K305" t="n">
-        <v>2.45266</v>
+        <v>2.44673</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -13564,16 +13564,16 @@
         <v>42491</v>
       </c>
       <c r="B306" t="n">
-        <v>0.5559850166789504</v>
+        <v>0.6236330027708847</v>
       </c>
       <c r="C306" t="n">
-        <v>0.033161118844105</v>
+        <v>0.04428507219937927</v>
       </c>
       <c r="D306" t="n">
-        <v>-1.252204127951362</v>
+        <v>-1.253748814056821</v>
       </c>
       <c r="E306" t="n">
-        <v>2.334943899394748</v>
+        <v>2.334939428252891</v>
       </c>
       <c r="F306" t="n">
         <v>1.373212451989558</v>
@@ -13591,7 +13591,7 @@
         <v>2.96893</v>
       </c>
       <c r="K306" t="n">
-        <v>2.47147</v>
+        <v>2.4658</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -13607,16 +13607,16 @@
         <v>42522</v>
       </c>
       <c r="B307" t="n">
-        <v>2.263308073364456</v>
+        <v>2.200933428864094</v>
       </c>
       <c r="C307" t="n">
-        <v>1.376053537912836</v>
+        <v>1.367130445516751</v>
       </c>
       <c r="D307" t="n">
-        <v>-2.588221375408051</v>
+        <v>-2.59161108671434</v>
       </c>
       <c r="E307" t="n">
-        <v>3.152982617120537</v>
+        <v>3.152981207959948</v>
       </c>
       <c r="F307" t="n">
         <v>1.070719660349995</v>
@@ -13634,7 +13634,7 @@
         <v>3.49684</v>
       </c>
       <c r="K307" t="n">
-        <v>1.93427</v>
+        <v>1.92791</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -13650,16 +13650,16 @@
         <v>42552</v>
       </c>
       <c r="B308" t="n">
-        <v>1.835131546966284</v>
+        <v>1.774197429446311</v>
       </c>
       <c r="C308" t="n">
-        <v>0.2880956412844249</v>
+        <v>0.2808907157103135</v>
       </c>
       <c r="D308" t="n">
-        <v>1.612008020339983</v>
+        <v>1.612010216460158</v>
       </c>
       <c r="E308" t="n">
-        <v>4.803318719029948</v>
+        <v>4.803315968872379</v>
       </c>
       <c r="F308" t="n">
         <v>6.886726952055944</v>
@@ -13677,7 +13677,7 @@
         <v>3.03728</v>
       </c>
       <c r="K308" t="n">
-        <v>2.44687</v>
+        <v>2.43205</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -13693,16 +13693,16 @@
         <v>42583</v>
       </c>
       <c r="B309" t="n">
-        <v>3.168215865682056</v>
+        <v>3.147540873631294</v>
       </c>
       <c r="C309" t="n">
-        <v>2.251790495689776</v>
+        <v>2.225613956158567</v>
       </c>
       <c r="D309" t="n">
-        <v>0.586940520951984</v>
+        <v>0.5762624787437831</v>
       </c>
       <c r="E309" t="n">
-        <v>5.404863706237295</v>
+        <v>5.404853304068702</v>
       </c>
       <c r="F309" t="n">
         <v>5.003015904149954</v>
@@ -13720,7 +13720,7 @@
         <v>3.08092</v>
       </c>
       <c r="K309" t="n">
-        <v>2.26059</v>
+        <v>2.23668</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -13736,16 +13736,16 @@
         <v>42614</v>
       </c>
       <c r="B310" t="n">
-        <v>5.780221674576436</v>
+        <v>5.757389756774134</v>
       </c>
       <c r="C310" t="n">
-        <v>6.622012287782453</v>
+        <v>6.607126973953248</v>
       </c>
       <c r="D310" t="n">
-        <v>2.743105667602252</v>
+        <v>2.747690208009756</v>
       </c>
       <c r="E310" t="n">
-        <v>8.383353747286293</v>
+        <v>8.383365011152378</v>
       </c>
       <c r="F310" t="n">
         <v>11.03031283644527</v>
@@ -13763,7 +13763,7 @@
         <v>2.5895</v>
       </c>
       <c r="K310" t="n">
-        <v>2.69789</v>
+        <v>2.68367</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -13779,16 +13779,16 @@
         <v>42644</v>
       </c>
       <c r="B311" t="n">
-        <v>3.921919468633384</v>
+        <v>3.907931638859452</v>
       </c>
       <c r="C311" t="n">
-        <v>3.191353432719057</v>
+        <v>3.16202408118631</v>
       </c>
       <c r="D311" t="n">
-        <v>0.7052093710286034</v>
+        <v>0.7045170989433691</v>
       </c>
       <c r="E311" t="n">
-        <v>4.871102970455121</v>
+        <v>4.871105058454783</v>
       </c>
       <c r="F311" t="n">
         <v>4.953581576758759</v>
@@ -13806,7 +13806,7 @@
         <v>2.98467</v>
       </c>
       <c r="K311" t="n">
-        <v>2.2917</v>
+        <v>2.27697</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -13822,16 +13822,16 @@
         <v>42675</v>
       </c>
       <c r="B312" t="n">
-        <v>4.073800338278488</v>
+        <v>4.036471076096304</v>
       </c>
       <c r="C312" t="n">
-        <v>2.34060975616468</v>
+        <v>2.284930230760063</v>
       </c>
       <c r="D312" t="n">
-        <v>-1.123065172965643</v>
+        <v>-1.112144745049248</v>
       </c>
       <c r="E312" t="n">
-        <v>5.809135502387042</v>
+        <v>5.809145532683901</v>
       </c>
       <c r="F312" t="n">
         <v>4.706509656613789</v>
@@ -13849,7 +13849,7 @@
         <v>2.70092</v>
       </c>
       <c r="K312" t="n">
-        <v>2.66075</v>
+        <v>2.64677</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -13865,16 +13865,16 @@
         <v>42705</v>
       </c>
       <c r="B313" t="n">
-        <v>3.234216254195266</v>
+        <v>3.252240759904246</v>
       </c>
       <c r="C313" t="n">
-        <v>2.424857333889596</v>
+        <v>2.336637474824821</v>
       </c>
       <c r="D313" t="n">
-        <v>-0.1015658938355424</v>
+        <v>-0.1051253005134645</v>
       </c>
       <c r="E313" t="n">
-        <v>6.313669382269627</v>
+        <v>6.313677454079047</v>
       </c>
       <c r="F313" t="n">
         <v>7.349908592472909</v>
@@ -13892,7 +13892,7 @@
         <v>2.38525</v>
       </c>
       <c r="K313" t="n">
-        <v>2.40283</v>
+        <v>2.38832</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -13908,16 +13908,16 @@
         <v>42736</v>
       </c>
       <c r="B314" t="n">
-        <v>4.318755926026419</v>
+        <v>4.281073329832852</v>
       </c>
       <c r="C314" t="n">
-        <v>3.888326954389987</v>
+        <v>3.893724445158475</v>
       </c>
       <c r="D314" t="n">
-        <v>1.514887032397216</v>
+        <v>1.520798092473785</v>
       </c>
       <c r="E314" t="n">
-        <v>8.601976775023147</v>
+        <v>8.602050922005366</v>
       </c>
       <c r="F314" t="n">
         <v>10.89601368010873</v>
@@ -13935,7 +13935,7 @@
         <v>1.95375</v>
       </c>
       <c r="K314" t="n">
-        <v>2.50795</v>
+        <v>2.50265</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -13951,16 +13951,16 @@
         <v>42767</v>
       </c>
       <c r="B315" t="n">
-        <v>1.531349703014473</v>
+        <v>1.669438610553486</v>
       </c>
       <c r="C315" t="n">
-        <v>2.652641728433913</v>
+        <v>2.81072052836504</v>
       </c>
       <c r="D315" t="n">
-        <v>0.9818383776636352</v>
+        <v>0.9737279669016274</v>
       </c>
       <c r="E315" t="n">
-        <v>3.988677374502902</v>
+        <v>3.988704546383515</v>
       </c>
       <c r="F315" t="n">
         <v>4.392910871620126</v>
@@ -13978,7 +13978,7 @@
         <v>2.41687</v>
       </c>
       <c r="K315" t="n">
-        <v>3.0587</v>
+        <v>3.04533</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -13994,16 +13994,16 @@
         <v>42795</v>
       </c>
       <c r="B316" t="n">
-        <v>2.571373894281503</v>
+        <v>2.668264017554067</v>
       </c>
       <c r="C316" t="n">
-        <v>2.859057121712283</v>
+        <v>2.933216006481598</v>
       </c>
       <c r="D316" t="n">
-        <v>0.447822766725503</v>
+        <v>0.432773884029114</v>
       </c>
       <c r="E316" t="n">
-        <v>3.688239318164954</v>
+        <v>3.688266672383023</v>
       </c>
       <c r="F316" t="n">
         <v>4.020509334308242</v>
@@ -14021,7 +14021,7 @@
         <v>2.6214</v>
       </c>
       <c r="K316" t="n">
-        <v>2.58235</v>
+        <v>2.56839</v>
       </c>
       <c r="L316" t="inlineStr">
         <is>
@@ -14037,16 +14037,16 @@
         <v>42826</v>
       </c>
       <c r="B317" t="n">
-        <v>8.845153499067537</v>
+        <v>8.79628537299746</v>
       </c>
       <c r="C317" t="n">
-        <v>9.077094057722036</v>
+        <v>9.061932165046827</v>
       </c>
       <c r="D317" t="n">
-        <v>0.370839422229885</v>
+        <v>0.3964833310055482</v>
       </c>
       <c r="E317" t="n">
-        <v>7.34137866576301</v>
+        <v>7.34141659848857</v>
       </c>
       <c r="F317" t="n">
         <v>8.937423402856105</v>
@@ -14064,7 +14064,7 @@
         <v>3.43104</v>
       </c>
       <c r="K317" t="n">
-        <v>3.15085</v>
+        <v>3.11977</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -14080,16 +14080,16 @@
         <v>42856</v>
       </c>
       <c r="B318" t="n">
-        <v>4.281887213205282</v>
+        <v>4.363446205873811</v>
       </c>
       <c r="C318" t="n">
-        <v>5.376363195751921</v>
+        <v>5.413832205587354</v>
       </c>
       <c r="D318" t="n">
-        <v>2.150063379575573</v>
+        <v>2.167039725531961</v>
       </c>
       <c r="E318" t="n">
-        <v>5.229895256243933</v>
+        <v>5.22991061296072</v>
       </c>
       <c r="F318" t="n">
         <v>8.451364972978915</v>
@@ -14107,7 +14107,7 @@
         <v>3.37079</v>
       </c>
       <c r="K318" t="n">
-        <v>3.11349</v>
+        <v>3.09152</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -14123,16 +14123,16 @@
         <v>42887</v>
       </c>
       <c r="B319" t="n">
-        <v>4.291761767070135</v>
+        <v>4.210033897817511</v>
       </c>
       <c r="C319" t="n">
-        <v>3.348302203734099</v>
+        <v>3.383636097917608</v>
       </c>
       <c r="D319" t="n">
-        <v>2.745901376022619</v>
+        <v>2.746801153535383</v>
       </c>
       <c r="E319" t="n">
-        <v>3.749081962700918</v>
+        <v>3.74905276670896</v>
       </c>
       <c r="F319" t="n">
         <v>7.056169430981973</v>
@@ -14150,7 +14150,7 @@
         <v>3.1774</v>
       </c>
       <c r="K319" t="n">
-        <v>3.58429</v>
+        <v>3.56295</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -14166,16 +14166,16 @@
         <v>42917</v>
       </c>
       <c r="B320" t="n">
-        <v>6.87308328348506</v>
+        <v>6.75419632580303</v>
       </c>
       <c r="C320" t="n">
-        <v>6.805716043459298</v>
+        <v>6.743081805589135</v>
       </c>
       <c r="D320" t="n">
-        <v>2.211136492519938</v>
+        <v>2.227121313199465</v>
       </c>
       <c r="E320" t="n">
-        <v>3.083592415679748</v>
+        <v>3.083559513216816</v>
       </c>
       <c r="F320" t="n">
         <v>5.673570033464137</v>
@@ -14193,7 +14193,7 @@
         <v>3.17951</v>
       </c>
       <c r="K320" t="n">
-        <v>2.894</v>
+        <v>2.86313</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -14209,16 +14209,16 @@
         <v>42948</v>
       </c>
       <c r="B321" t="n">
-        <v>5.980549567771964</v>
+        <v>5.938496685790251</v>
       </c>
       <c r="C321" t="n">
-        <v>4.683907431055978</v>
+        <v>4.628173761947396</v>
       </c>
       <c r="D321" t="n">
-        <v>1.486636311603995</v>
+        <v>1.47497356086399</v>
       </c>
       <c r="E321" t="n">
-        <v>2.677252259304019</v>
+        <v>2.677193158285451</v>
       </c>
       <c r="F321" t="n">
         <v>2.812140782604367</v>
@@ -14236,7 +14236,7 @@
         <v>3.22862</v>
       </c>
       <c r="K321" t="n">
-        <v>2.66319</v>
+        <v>2.6497</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -14252,16 +14252,16 @@
         <v>42979</v>
       </c>
       <c r="B322" t="n">
-        <v>5.537391484197318</v>
+        <v>5.554860416572538</v>
       </c>
       <c r="C322" t="n">
-        <v>3.509075011334151</v>
+        <v>3.552114324241407</v>
       </c>
       <c r="D322" t="n">
-        <v>0.04203033256953148</v>
+        <v>0.02752814724780173</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.5050157107830411</v>
+        <v>-0.5051025050266333</v>
       </c>
       <c r="F322" t="n">
         <v>-1.925600768888869</v>
@@ -14279,7 +14279,7 @@
         <v>3.72666</v>
       </c>
       <c r="K322" t="n">
-        <v>2.9218</v>
+        <v>2.90874</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -14295,16 +14295,16 @@
         <v>43009</v>
       </c>
       <c r="B323" t="n">
-        <v>4.324960409445811</v>
+        <v>4.333060793169774</v>
       </c>
       <c r="C323" t="n">
-        <v>5.202595198028148</v>
+        <v>5.146112600437203</v>
       </c>
       <c r="D323" t="n">
-        <v>0.9811335909164054</v>
+        <v>0.9521520753456469</v>
       </c>
       <c r="E323" t="n">
-        <v>4.157828904970806</v>
+        <v>4.15779219191148</v>
       </c>
       <c r="F323" t="n">
         <v>3.912201306772523</v>
@@ -14322,7 +14322,7 @@
         <v>3.8978</v>
       </c>
       <c r="K323" t="n">
-        <v>3.1695</v>
+        <v>3.1568</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -14338,16 +14338,16 @@
         <v>43040</v>
       </c>
       <c r="B324" t="n">
-        <v>7.601535031899465</v>
+        <v>7.536310049198081</v>
       </c>
       <c r="C324" t="n">
-        <v>6.946833138806707</v>
+        <v>6.795156858656815</v>
       </c>
       <c r="D324" t="n">
-        <v>3.736058703830381</v>
+        <v>3.745723727222749</v>
       </c>
       <c r="E324" t="n">
-        <v>2.171560405124451</v>
+        <v>2.171502006227266</v>
       </c>
       <c r="F324" t="n">
         <v>5.540582686539519</v>
@@ -14365,7 +14365,7 @@
         <v>3.61713</v>
       </c>
       <c r="K324" t="n">
-        <v>2.51404</v>
+        <v>2.5093</v>
       </c>
       <c r="L324" t="inlineStr">
         <is>
@@ -14381,16 +14381,16 @@
         <v>43070</v>
       </c>
       <c r="B325" t="n">
-        <v>6.030408283739597</v>
+        <v>6.076167666363141</v>
       </c>
       <c r="C325" t="n">
-        <v>5.641248687015832</v>
+        <v>5.494677306087548</v>
       </c>
       <c r="D325" t="n">
-        <v>-0.04887942527218581</v>
+        <v>-0.08633812908726002</v>
       </c>
       <c r="E325" t="n">
-        <v>2.851039325122429</v>
+        <v>2.85102962687247</v>
       </c>
       <c r="F325" t="n">
         <v>3.072298813570273</v>
@@ -14408,7 +14408,7 @@
         <v>3.29407</v>
       </c>
       <c r="K325" t="n">
-        <v>2.57937</v>
+        <v>2.56587</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -14424,16 +14424,16 @@
         <v>43101</v>
       </c>
       <c r="B326" t="n">
-        <v>5.888313493686725</v>
+        <v>5.848648017321745</v>
       </c>
       <c r="C326" t="n">
-        <v>4.930756435854877</v>
+        <v>4.997820374782336</v>
       </c>
       <c r="D326" t="n">
-        <v>0.8608738499763291</v>
+        <v>0.8545292773355584</v>
       </c>
       <c r="E326" t="n">
-        <v>4.40099921367243</v>
+        <v>4.401060689949143</v>
       </c>
       <c r="F326" t="n">
         <v>5.417273833488068</v>
@@ -14451,7 +14451,7 @@
         <v>2.88702</v>
       </c>
       <c r="K326" t="n">
-        <v>2.22261</v>
+        <v>2.20861</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -14467,16 +14467,16 @@
         <v>43132</v>
       </c>
       <c r="B327" t="n">
-        <v>9.750534054063277</v>
+        <v>9.88296606028667</v>
       </c>
       <c r="C327" t="n">
-        <v>9.275019880701873</v>
+        <v>9.511736544372496</v>
       </c>
       <c r="D327" t="n">
-        <v>2.749214313709358</v>
+        <v>2.757615787903633</v>
       </c>
       <c r="E327" t="n">
-        <v>7.706543476929983</v>
+        <v>7.706589849103684</v>
       </c>
       <c r="F327" t="n">
         <v>10.5375030535565</v>
@@ -14494,7 +14494,7 @@
         <v>2.09182</v>
       </c>
       <c r="K327" t="n">
-        <v>1.94716</v>
+        <v>1.94158</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14510,16 +14510,16 @@
         <v>43160</v>
       </c>
       <c r="B328" t="n">
-        <v>10.33708214301878</v>
+        <v>10.43183477917289</v>
       </c>
       <c r="C328" t="n">
-        <v>9.034992168942612</v>
+        <v>9.12346774489723</v>
       </c>
       <c r="D328" t="n">
-        <v>3.165058764866635</v>
+        <v>3.193048532686849</v>
       </c>
       <c r="E328" t="n">
-        <v>7.464206179796173</v>
+        <v>7.464256917161616</v>
       </c>
       <c r="F328" t="n">
         <v>11.46591975377156</v>
@@ -14537,7 +14537,7 @@
         <v>1.82708</v>
       </c>
       <c r="K328" t="n">
-        <v>1.77241</v>
+        <v>1.76657</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -14553,16 +14553,16 @@
         <v>43191</v>
       </c>
       <c r="B329" t="n">
-        <v>4.011368005730809</v>
+        <v>4.010865376630668</v>
       </c>
       <c r="C329" t="n">
-        <v>3.039351588181161</v>
+        <v>3.115229091483429</v>
       </c>
       <c r="D329" t="n">
-        <v>2.830625095924999</v>
+        <v>2.865407225048022</v>
       </c>
       <c r="E329" t="n">
-        <v>3.681647150085432</v>
+        <v>3.681691865941783</v>
       </c>
       <c r="F329" t="n">
         <v>7.943240685540509</v>
@@ -14580,7 +14580,7 @@
         <v>1.1622</v>
       </c>
       <c r="K329" t="n">
-        <v>1.45051</v>
+        <v>1.44432</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -14596,16 +14596,16 @@
         <v>43221</v>
       </c>
       <c r="B330" t="n">
-        <v>6.127061659058874</v>
+        <v>6.253589990724095</v>
       </c>
       <c r="C330" t="n">
-        <v>5.542668921136018</v>
+        <v>5.608005952311323</v>
       </c>
       <c r="D330" t="n">
-        <v>1.309057827164595</v>
+        <v>1.336954533354762</v>
       </c>
       <c r="E330" t="n">
-        <v>5.682663473980876</v>
+        <v>5.682699936653113</v>
       </c>
       <c r="F330" t="n">
         <v>8.137113847614108</v>
@@ -14623,7 +14623,7 @@
         <v>1.15817</v>
       </c>
       <c r="K330" t="n">
-        <v>1.03768</v>
+        <v>1.03084</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -14639,16 +14639,16 @@
         <v>43252</v>
       </c>
       <c r="B331" t="n">
-        <v>6.16089307526031</v>
+        <v>6.001884240045841</v>
       </c>
       <c r="C331" t="n">
-        <v>7.446560287254811</v>
+        <v>7.433128272286194</v>
       </c>
       <c r="D331" t="n">
-        <v>-1.061333774228712</v>
+        <v>-1.051664465888413</v>
       </c>
       <c r="E331" t="n">
-        <v>5.030855078963992</v>
+        <v>5.030861907929607</v>
       </c>
       <c r="F331" t="n">
         <v>4.666813243096546</v>
@@ -14666,7 +14666,7 @@
         <v>0.74575</v>
       </c>
       <c r="K331" t="n">
-        <v>0.64456</v>
+        <v>0.6371</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -14682,16 +14682,16 @@
         <v>43282</v>
       </c>
       <c r="B332" t="n">
-        <v>4.407141425642958</v>
+        <v>4.255155346043948</v>
       </c>
       <c r="C332" t="n">
-        <v>4.050931793994428</v>
+        <v>3.99632950748241</v>
       </c>
       <c r="D332" t="n">
-        <v>-1.630145809996852</v>
+        <v>-1.616568432804166</v>
       </c>
       <c r="E332" t="n">
-        <v>4.52989784133857</v>
+        <v>4.52991195447765</v>
       </c>
       <c r="F332" t="n">
         <v>3.624230474045764</v>
@@ -14709,7 +14709,7 @@
         <v>1.19516</v>
       </c>
       <c r="K332" t="n">
-        <v>0.69468</v>
+        <v>0.69586</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -14725,16 +14725,16 @@
         <v>43313</v>
       </c>
       <c r="B333" t="n">
-        <v>3.883806565979508</v>
+        <v>3.839962058678825</v>
       </c>
       <c r="C333" t="n">
-        <v>3.794529498075749</v>
+        <v>3.714211668684886</v>
       </c>
       <c r="D333" t="n">
-        <v>-3.150802485073589</v>
+        <v>-3.139629631365337</v>
       </c>
       <c r="E333" t="n">
-        <v>4.428046639778427</v>
+        <v>4.428021329266718</v>
       </c>
       <c r="F333" t="n">
         <v>0.7179325744210985</v>
@@ -14752,7 +14752,7 @@
         <v>1.24054</v>
       </c>
       <c r="K333" t="n">
-        <v>0.72906</v>
+        <v>0.72175</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -14768,16 +14768,16 @@
         <v>43344</v>
       </c>
       <c r="B334" t="n">
-        <v>2.887693960533499</v>
+        <v>2.90932754285893</v>
       </c>
       <c r="C334" t="n">
-        <v>4.905320160687743</v>
+        <v>4.934352028870959</v>
       </c>
       <c r="D334" t="n">
-        <v>-1.644961712763238</v>
+        <v>-1.660568089501779</v>
       </c>
       <c r="E334" t="n">
-        <v>5.085274334090983</v>
+        <v>5.085240830435844</v>
       </c>
       <c r="F334" t="n">
         <v>2.59634611094044</v>
@@ -14795,7 +14795,7 @@
         <v>0.99754</v>
       </c>
       <c r="K334" t="n">
-        <v>0.0337</v>
+        <v>0.01687</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -14811,16 +14811,16 @@
         <v>43374</v>
       </c>
       <c r="B335" t="n">
-        <v>3.719066606340293</v>
+        <v>3.702917631925473</v>
       </c>
       <c r="C335" t="n">
-        <v>1.774133737275996</v>
+        <v>1.689837460616594</v>
       </c>
       <c r="D335" t="n">
-        <v>-2.362823612249698</v>
+        <v>-2.405538120822825</v>
       </c>
       <c r="E335" t="n">
-        <v>3.779214426871569</v>
+        <v>3.779202964183659</v>
       </c>
       <c r="F335" t="n">
         <v>0.2888895836095751</v>
@@ -14838,7 +14838,7 @@
         <v>1.6726</v>
       </c>
       <c r="K335" t="n">
-        <v>0.06733</v>
+        <v>0.05058</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -14854,16 +14854,16 @@
         <v>43405</v>
       </c>
       <c r="B336" t="n">
-        <v>3.801856423181538</v>
+        <v>3.723123941776674</v>
       </c>
       <c r="C336" t="n">
-        <v>3.791294759957053</v>
+        <v>3.561056495082204</v>
       </c>
       <c r="D336" t="n">
-        <v>-3.453044397688798</v>
+        <v>-3.458743600875724</v>
       </c>
       <c r="E336" t="n">
-        <v>3.414296398438776</v>
+        <v>3.414278054847175</v>
       </c>
       <c r="F336" t="n">
         <v>-0.1589170253252226</v>
@@ -14881,7 +14881,7 @@
         <v>-2.54535</v>
       </c>
       <c r="K336" t="n">
-        <v>0.27811</v>
+        <v>0.26167</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -14897,16 +14897,16 @@
         <v>43435</v>
       </c>
       <c r="B337" t="n">
-        <v>1.93198144635085</v>
+        <v>1.991550934273101</v>
       </c>
       <c r="C337" t="n">
-        <v>1.456669783602083</v>
+        <v>1.181723752648134</v>
       </c>
       <c r="D337" t="n">
-        <v>-3.512454369140605</v>
+        <v>-3.542810670613061</v>
       </c>
       <c r="E337" t="n">
-        <v>3.514591186708826</v>
+        <v>3.51461493934313</v>
       </c>
       <c r="F337" t="n">
         <v>0.2555358508475214</v>
@@ -14924,7 +14924,7 @@
         <v>2.74022</v>
       </c>
       <c r="K337" t="n">
-        <v>0.10092</v>
+        <v>0.08423</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -14940,16 +14940,16 @@
         <v>43466</v>
       </c>
       <c r="B338" t="n">
-        <v>3.347295794305927</v>
+        <v>3.283398495660461</v>
       </c>
       <c r="C338" t="n">
-        <v>2.118566679196232</v>
+        <v>2.176574919431085</v>
       </c>
       <c r="D338" t="n">
-        <v>-2.237170558088264</v>
+        <v>-2.259859190026958</v>
       </c>
       <c r="E338" t="n">
-        <v>1.739751222768704</v>
+        <v>1.73974901052365</v>
       </c>
       <c r="F338" t="n">
         <v>-1.524383408925667</v>
@@ -14967,7 +14967,7 @@
         <v>-0.47291</v>
       </c>
       <c r="K338" t="n">
-        <v>0.21911</v>
+        <v>0.20258</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -14983,16 +14983,16 @@
         <v>43497</v>
       </c>
       <c r="B339" t="n">
-        <v>0.3695349825207028</v>
+        <v>0.6221431043657466</v>
       </c>
       <c r="C339" t="n">
-        <v>-2.16424363052109</v>
+        <v>-1.749752030973362</v>
       </c>
       <c r="D339" t="n">
-        <v>-2.010063017998975</v>
+        <v>-2.035445172094508</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.7780700293527842</v>
+        <v>-0.7780693034257657</v>
       </c>
       <c r="F339" t="n">
         <v>-3.903675752103297</v>
@@ -15010,7 +15010,7 @@
         <v>-0.04974</v>
       </c>
       <c r="K339" t="n">
-        <v>0.29449</v>
+        <v>0.27811</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -15026,16 +15026,16 @@
         <v>43525</v>
       </c>
       <c r="B340" t="n">
-        <v>3.423452281782269</v>
+        <v>3.6167823360993</v>
       </c>
       <c r="C340" t="n">
-        <v>0.4314934904457779</v>
+        <v>0.6053443014032878</v>
       </c>
       <c r="D340" t="n">
-        <v>-2.661745897783174</v>
+        <v>-2.646129996304225</v>
       </c>
       <c r="E340" t="n">
-        <v>-0.8721370336156498</v>
+        <v>-0.8721469999455111</v>
       </c>
       <c r="F340" t="n">
         <v>-3.769366909050764</v>
@@ -15053,7 +15053,7 @@
         <v>-0.5249</v>
       </c>
       <c r="K340" t="n">
-        <v>0.63941</v>
+        <v>0.62358</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -15069,16 +15069,16 @@
         <v>43556</v>
       </c>
       <c r="B341" t="n">
-        <v>4.836448709823493</v>
+        <v>4.801557955358216</v>
       </c>
       <c r="C341" t="n">
-        <v>1.376573411518978</v>
+        <v>1.418856857819484</v>
       </c>
       <c r="D341" t="n">
-        <v>-3.001287246167561</v>
+        <v>-2.999400545070996</v>
       </c>
       <c r="E341" t="n">
-        <v>1.942213532946213</v>
+        <v>1.942205124907947</v>
       </c>
       <c r="F341" t="n">
         <v>-0.6405689934359637</v>
@@ -15096,7 +15096,7 @@
         <v>-1.20612</v>
       </c>
       <c r="K341" t="n">
-        <v>0.69807</v>
+        <v>0.6823900000000001</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15112,16 +15112,16 @@
         <v>43586</v>
       </c>
       <c r="B342" t="n">
-        <v>5.480961590506506</v>
+        <v>5.645536353008418</v>
       </c>
       <c r="C342" t="n">
-        <v>2.742386238615535</v>
+        <v>2.832031940393476</v>
       </c>
       <c r="D342" t="n">
-        <v>-0.6833374815226723</v>
+        <v>-0.684781124113476</v>
       </c>
       <c r="E342" t="n">
-        <v>0.02095156842485402</v>
+        <v>0.02095514875946058</v>
       </c>
       <c r="F342" t="n">
         <v>-0.401706957670056</v>
@@ -15139,7 +15139,7 @@
         <v>-1.42733</v>
       </c>
       <c r="K342" t="n">
-        <v>1.1533</v>
+        <v>1.13838</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -15155,16 +15155,16 @@
         <v>43617</v>
       </c>
       <c r="B343" t="n">
-        <v>6.077263913137498</v>
+        <v>5.865082167621094</v>
       </c>
       <c r="C343" t="n">
-        <v>1.548524866852574</v>
+        <v>1.59489162159181</v>
       </c>
       <c r="D343" t="n">
-        <v>2.408985477005587</v>
+        <v>2.411385680448186</v>
       </c>
       <c r="E343" t="n">
-        <v>0.8039616888592116</v>
+        <v>0.8039687437500831</v>
       </c>
       <c r="F343" t="n">
         <v>3.872779605436594</v>
@@ -15182,7 +15182,7 @@
         <v>-1.0947</v>
       </c>
       <c r="K343" t="n">
-        <v>1.31457</v>
+        <v>1.29147</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -15198,16 +15198,16 @@
         <v>43647</v>
       </c>
       <c r="B344" t="n">
-        <v>6.208345536205595</v>
+        <v>5.957485532053575</v>
       </c>
       <c r="C344" t="n">
-        <v>3.963278651186242</v>
+        <v>3.822901222274533</v>
       </c>
       <c r="D344" t="n">
-        <v>0.8717260224757606</v>
+        <v>0.9142489852025593</v>
       </c>
       <c r="E344" t="n">
-        <v>2.763080800598305</v>
+        <v>2.763090664326628</v>
       </c>
       <c r="F344" t="n">
         <v>4.801890871215964</v>
@@ -15225,7 +15225,7 @@
         <v>-0.70978</v>
       </c>
       <c r="K344" t="n">
-        <v>1.38819</v>
+        <v>1.36525</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -15241,16 +15241,16 @@
         <v>43678</v>
       </c>
       <c r="B345" t="n">
-        <v>10.39814363827012</v>
+        <v>10.28693100950546</v>
       </c>
       <c r="C345" t="n">
-        <v>7.593636712614216</v>
+        <v>7.412335097435552</v>
       </c>
       <c r="D345" t="n">
-        <v>7.734608516039865</v>
+        <v>7.775236341205316</v>
       </c>
       <c r="E345" t="n">
-        <v>2.738625909540104</v>
+        <v>2.738551217855045</v>
       </c>
       <c r="F345" t="n">
         <v>10.8000098203086</v>
@@ -15268,7 +15268,7 @@
         <v>-0.65966</v>
       </c>
       <c r="K345" t="n">
-        <v>1.60747</v>
+        <v>1.58489</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -15284,16 +15284,16 @@
         <v>43709</v>
       </c>
       <c r="B346" t="n">
-        <v>2.130944042086291</v>
+        <v>2.153749809911143</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.4244147939783449</v>
+        <v>-0.3465722690834117</v>
       </c>
       <c r="D346" t="n">
-        <v>1.53081609036223</v>
+        <v>1.550269111837821</v>
       </c>
       <c r="E346" t="n">
-        <v>2.172330441933079</v>
+        <v>2.172327841074084</v>
       </c>
       <c r="F346" t="n">
         <v>3.919007356003235</v>
@@ -15311,7 +15311,7 @@
         <v>-0.20679</v>
       </c>
       <c r="K346" t="n">
-        <v>2.18947</v>
+        <v>2.24397</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -15327,16 +15327,16 @@
         <v>43739</v>
       </c>
       <c r="B347" t="n">
-        <v>5.150718684250921</v>
+        <v>5.147521663794308</v>
       </c>
       <c r="C347" t="n">
-        <v>3.099789808332321</v>
+        <v>2.96290443798346</v>
       </c>
       <c r="D347" t="n">
-        <v>4.418600882713619</v>
+        <v>4.364316255282907</v>
       </c>
       <c r="E347" t="n">
-        <v>2.010897719631077</v>
+        <v>2.010847514016212</v>
       </c>
       <c r="F347" t="n">
         <v>5.28584931917373</v>
@@ -15354,7 +15354,7 @@
         <v>-1.10351</v>
       </c>
       <c r="K347" t="n">
-        <v>2.07755</v>
+        <v>2.09808</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -15370,16 +15370,16 @@
         <v>43770</v>
       </c>
       <c r="B348" t="n">
-        <v>3.669455018694001</v>
+        <v>3.564490679337839</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.7705868454765064</v>
+        <v>-1.14509528785498</v>
       </c>
       <c r="D348" t="n">
-        <v>4.028988290433344</v>
+        <v>4.033407581419235</v>
       </c>
       <c r="E348" t="n">
-        <v>2.919030516966004</v>
+        <v>2.919056715256341</v>
       </c>
       <c r="F348" t="n">
         <v>7.716941507266006</v>
@@ -15397,7 +15397,7 @@
         <v>2.90988</v>
       </c>
       <c r="K348" t="n">
-        <v>2.2775</v>
+        <v>2.2226</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15413,16 +15413,16 @@
         <v>43800</v>
       </c>
       <c r="B349" t="n">
-        <v>6.639636487359457</v>
+        <v>6.712488785252058</v>
       </c>
       <c r="C349" t="n">
-        <v>6.228140102779212</v>
+        <v>5.744260282874958</v>
       </c>
       <c r="D349" t="n">
-        <v>5.531643161905508</v>
+        <v>5.554722445900118</v>
       </c>
       <c r="E349" t="n">
-        <v>5.74683609721871</v>
+        <v>5.746856241612042</v>
       </c>
       <c r="F349" t="n">
         <v>12.07670357925119</v>
@@ -15440,7 +15440,7 @@
         <v>-1.38874</v>
       </c>
       <c r="K349" t="n">
-        <v>2.66319</v>
+        <v>2.67632</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -15456,16 +15456,16 @@
         <v>43831</v>
       </c>
       <c r="B350" t="n">
-        <v>5.48936843521699</v>
+        <v>5.360933204679563</v>
       </c>
       <c r="C350" t="n">
-        <v>3.04155058657567</v>
+        <v>3.152724802218798</v>
       </c>
       <c r="D350" t="n">
-        <v>6.412059482975918</v>
+        <v>6.374697577123767</v>
       </c>
       <c r="E350" t="n">
-        <v>6.381909251652074</v>
+        <v>6.381883420370027</v>
       </c>
       <c r="F350" t="n">
         <v>11.24422410330805</v>
@@ -15483,7 +15483,7 @@
         <v>2.59519</v>
       </c>
       <c r="K350" t="n">
-        <v>2.92634</v>
+        <v>2.88097</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -15499,16 +15499,16 @@
         <v>43862</v>
       </c>
       <c r="B351" t="n">
-        <v>5.609709552780329</v>
+        <v>5.960662227801494</v>
       </c>
       <c r="C351" t="n">
-        <v>4.329956299863591</v>
+        <v>5.101032407647899</v>
       </c>
       <c r="D351" t="n">
-        <v>1.894868061009869</v>
+        <v>1.866295496443326</v>
       </c>
       <c r="E351" t="n">
-        <v>7.674843405490361</v>
+        <v>7.674879587309413</v>
       </c>
       <c r="F351" t="n">
         <v>8.589389707578277</v>
@@ -15526,7 +15526,7 @@
         <v>1.85033</v>
       </c>
       <c r="K351" t="n">
-        <v>2.84396</v>
+        <v>2.84898</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -15542,16 +15542,16 @@
         <v>43891</v>
       </c>
       <c r="B352" t="n">
-        <v>-53.3716435373044</v>
+        <v>-53.24994387036035</v>
       </c>
       <c r="C352" t="n">
-        <v>-49.31920514238725</v>
+        <v>-49.15999660564631</v>
       </c>
       <c r="D352" t="n">
-        <v>-44.27591077834889</v>
+        <v>-44.25592982290078</v>
       </c>
       <c r="E352" t="n">
-        <v>-1.405925434582578</v>
+        <v>-1.405899018781764</v>
       </c>
       <c r="F352" t="n">
         <v>-45.03550973431809</v>
@@ -15569,7 +15569,7 @@
         <v>1.60067</v>
       </c>
       <c r="K352" t="n">
-        <v>2.15683</v>
+        <v>2.102</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -15585,16 +15585,16 @@
         <v>43922</v>
       </c>
       <c r="B353" t="n">
-        <v>-99.40197272406446</v>
+        <v>-99.40218678976916</v>
       </c>
       <c r="C353" t="n">
-        <v>-98.11647222565402</v>
+        <v>-98.11469172934576</v>
       </c>
       <c r="D353" t="n">
-        <v>-88.68415804327566</v>
+        <v>-88.68168525921284</v>
       </c>
       <c r="E353" t="n">
-        <v>-52.30464190037026</v>
+        <v>-52.30463004073071</v>
       </c>
       <c r="F353" t="n">
         <v>-94.56918472470967</v>
@@ -15612,7 +15612,7 @@
         <v>-49.24183</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.84574</v>
+        <v>-38.84194</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -15628,16 +15628,16 @@
         <v>43952</v>
       </c>
       <c r="B354" t="n">
-        <v>-98.80731135801039</v>
+        <v>-98.80463840197949</v>
       </c>
       <c r="C354" t="n">
-        <v>-95.98502100512947</v>
+        <v>-95.97842394605077</v>
       </c>
       <c r="D354" t="n">
-        <v>-82.14500373297355</v>
+        <v>-82.14613249485076</v>
       </c>
       <c r="E354" t="n">
-        <v>-50.55055230538783</v>
+        <v>-50.55052680272709</v>
       </c>
       <c r="F354" t="n">
         <v>-91.14556568617806</v>
@@ -15655,7 +15655,7 @@
         <v>-69.47422</v>
       </c>
       <c r="K354" t="n">
-        <v>-39.00632</v>
+        <v>-39.01951</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -15671,16 +15671,16 @@
         <v>43983</v>
       </c>
       <c r="B355" t="n">
-        <v>-98.12711795317868</v>
+        <v>-98.13193635734406</v>
       </c>
       <c r="C355" t="n">
-        <v>-94.34788363377858</v>
+        <v>-94.3462610705611</v>
       </c>
       <c r="D355" t="n">
-        <v>-81.39316012125946</v>
+        <v>-81.39755439598432</v>
       </c>
       <c r="E355" t="n">
-        <v>-42.85597081332219</v>
+        <v>-42.85592624731962</v>
       </c>
       <c r="F355" t="n">
         <v>-89.28591385793068</v>
@@ -15698,7 +15698,7 @@
         <v>-70.02136</v>
       </c>
       <c r="K355" t="n">
-        <v>-24.50304</v>
+        <v>-24.5</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -15714,16 +15714,16 @@
         <v>44013</v>
       </c>
       <c r="B356" t="n">
-        <v>-97.73615115307662</v>
+        <v>-97.74165944702972</v>
       </c>
       <c r="C356" t="n">
-        <v>-93.62099507027733</v>
+        <v>-93.63180121972722</v>
       </c>
       <c r="D356" t="n">
-        <v>-75.64849539092089</v>
+        <v>-75.63671194834342</v>
       </c>
       <c r="E356" t="n">
-        <v>-43.03906157327621</v>
+        <v>-43.03904890392778</v>
       </c>
       <c r="F356" t="n">
         <v>-85.97972877447285</v>
@@ -15741,7 +15741,7 @@
         <v>-74.59829999999999</v>
       </c>
       <c r="K356" t="n">
-        <v>-27.54128</v>
+        <v>-27.56069</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -15757,16 +15757,16 @@
         <v>44044</v>
       </c>
       <c r="B357" t="n">
-        <v>-97.45884275128206</v>
+        <v>-97.46075776989619</v>
       </c>
       <c r="C357" t="n">
-        <v>-90.98320037184409</v>
+        <v>-91.0009641372634</v>
       </c>
       <c r="D357" t="n">
-        <v>-74.18255412484274</v>
+        <v>-74.177774172602</v>
       </c>
       <c r="E357" t="n">
-        <v>-45.64627806366808</v>
+        <v>-45.64635203248899</v>
       </c>
       <c r="F357" t="n">
         <v>-85.95954311968738</v>
@@ -15784,7 +15784,7 @@
         <v>-74.78028</v>
       </c>
       <c r="K357" t="n">
-        <v>-16.59902</v>
+        <v>-16.59751</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -15800,16 +15800,16 @@
         <v>44075</v>
       </c>
       <c r="B358" t="n">
-        <v>-97.42868309174636</v>
+        <v>-97.43045306200882</v>
       </c>
       <c r="C358" t="n">
-        <v>-89.90495084520556</v>
+        <v>-89.90231085286977</v>
       </c>
       <c r="D358" t="n">
-        <v>-74.99413450649175</v>
+        <v>-74.98415899791128</v>
       </c>
       <c r="E358" t="n">
-        <v>-40.2174490257181</v>
+        <v>-40.21745480945407</v>
       </c>
       <c r="F358" t="n">
         <v>-84.91312125121274</v>
@@ -15827,7 +15827,7 @@
         <v>-76.75029000000001</v>
       </c>
       <c r="K358" t="n">
-        <v>-23.45282</v>
+        <v>-23.53135</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -15843,16 +15843,16 @@
         <v>44105</v>
       </c>
       <c r="B359" t="n">
-        <v>-90.07187062394723</v>
+        <v>-90.08004785445087</v>
       </c>
       <c r="C359" t="n">
-        <v>-81.38361918138027</v>
+        <v>-81.43457432378571</v>
       </c>
       <c r="D359" t="n">
-        <v>-74.91196833340568</v>
+        <v>-74.92715823820438</v>
       </c>
       <c r="E359" t="n">
-        <v>-31.44827455099354</v>
+        <v>-31.44830876036783</v>
       </c>
       <c r="F359" t="n">
         <v>-82.8923409539663</v>
@@ -15870,7 +15870,7 @@
         <v>-66.86682</v>
       </c>
       <c r="K359" t="n">
-        <v>-15.0791</v>
+        <v>-15.11925</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -15886,16 +15886,16 @@
         <v>44136</v>
       </c>
       <c r="B360" t="n">
-        <v>-76.74601786482054</v>
+        <v>-76.76526506866044</v>
       </c>
       <c r="C360" t="n">
-        <v>-65.62294109055904</v>
+        <v>-65.82971011661466</v>
       </c>
       <c r="D360" t="n">
-        <v>-71.91139211277874</v>
+        <v>-71.91435751736464</v>
       </c>
       <c r="E360" t="n">
-        <v>-12.81470031746895</v>
+        <v>-12.81464798244773</v>
       </c>
       <c r="F360" t="n">
         <v>-75.21974240025891</v>
@@ -15913,7 +15913,7 @@
         <v>-57.11076</v>
       </c>
       <c r="K360" t="n">
-        <v>-16.12161</v>
+        <v>-16.11761</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -15929,16 +15929,16 @@
         <v>44166</v>
       </c>
       <c r="B361" t="n">
-        <v>-74.8297237797896</v>
+        <v>-74.8196791224609</v>
       </c>
       <c r="C361" t="n">
-        <v>-66.31688966844619</v>
+        <v>-66.51976840857982</v>
       </c>
       <c r="D361" t="n">
-        <v>-70.34940691178299</v>
+        <v>-70.34755898795326</v>
       </c>
       <c r="E361" t="n">
-        <v>-17.07747703267301</v>
+        <v>-17.07749976030184</v>
       </c>
       <c r="F361" t="n">
         <v>-75.48766169201052</v>
@@ -15956,7 +15956,7 @@
         <v>-53.24911</v>
       </c>
       <c r="K361" t="n">
-        <v>-13.29787</v>
+        <v>-13.33607</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
